--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="G2" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : every musician's next skill plays twice. Better strokes, louder echo.</t>
+          <t>The 4/4 shape : every musician's next move plays twice. Better strokes, louder echo.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="G4" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : one extra turn for a musician per stroke that lands.</t>
+          <t>The 4/4 shape : two free ATTACKs at the end of the bar per stroke that lands.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G5" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : for one turn per stroke that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays 10 percent of their life.</t>
+          <t>The 4/4 shape : for two turns per stroke that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays 10 percent of their life.</t>
         </is>
       </c>
     </row>
@@ -1470,321 +1470,360 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="67" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>turnsim.txt (--shots turnsim, Core/DebugShots.TurnSim.cs)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="69" t="inlineStr">
-        <is>
-          <t>TACET TURN BATTLE BALANCE  (200 fights per cell, 300 runs per player)</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TACET TURN BATTLE BALANCE, ONE BAR  (200 fights per cell, 300 runs per player)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="69" t="inlineStr">
-        <is>
-          <t>Players : timing spread FLAWLESS 0 / STRONG 0.12 / AVERAGE 0.2 / NEWCOMER 0.3 seconds</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="69" t="inlineStr"/>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Players : timing spread FLAWLESS 0 / EXPERT 0.08 / STRONG 0.12 / AVERAGE 0.2 / NEWCOMER 0.3 seconds</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="69" t="inlineStr">
-        <is>
-          <t>FIGHTS at full life : WIN PERCENT  /  ROUNDS  /  LIFE LOST PERCENT</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FIGHTS at full life (4 musicians, 2 on the field) : WIN PERCENT  /  BARS  /  LIFE LOST PERCENT  /  CALLS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  NORMAL 100%  1.0r   0%    ELITE  100%  2.0r   0%    BOSS   100%  4.0r   0%    </t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 2.0c   LATE  100%  3.0b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  4.9b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  NORMAL 100%  1.5r   0%    ELITE  100%  2.5r   0%    BOSS   100%  4.7r   0%    </t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.1b   0% 2.0c   ELITE 100%  4.0b   0% 2.0c   BOSS  100%  5.7b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  NORMAL 100%  2.0r   0%    ELITE  100%  3.0r   0%    BOSS   100%  5.1r   0%    </t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.0b   0% 2.0c   LATE  100%  4.0b   0% 2.0c   ELITE 100%  4.5b   0% 2.0c   BOSS  100%  6.8b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  NORMAL 100%  1.5r   3%    ELITE  100%  2.6r  11%    BOSS   100%  4.8r  21%    </t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.0b   2% 1.6c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.3b   6% 1.9c   BOSS  100%  5.2b  12% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  NORMAL 100%  2.0r   5%    ELITE  100%  3.0r  17%    BOSS    98%  6.1r  33%    </t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b   8% 2.0c   LATE  100%  3.3b  11% 2.0c   ELITE 100%  4.1b  14% 1.9c   BOSS  100%  6.2b  19% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  NORMAL 100%  2.1r  10%    ELITE  100%  3.8r  24%    BOSS    83%  7.3r  51%    </t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  3.9b  12% 2.0c   LATE  100%  4.8b  14% 2.0c   ELITE 100%  5.2b  22% 2.0c   BOSS   99%  7.6b  29% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  NORMAL 100%  2.0r   8%    ELITE  100%  3.6r  28%    BOSS    80%  7.1r  54%    </t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.1b   6% 1.3c   LATE  100%  3.2b  14% 1.9c   ELITE 100%  3.7b  12% 1.8c   BOSS   98%  5.8b  26% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  NORMAL 100%  2.4r  16%    ELITE   94%  4.7r  51%    BOSS    42%  8.0r  80%    </t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.8b  20% 1.9c   LATE  100%  3.9b  25% 2.0c   ELITE  97%  4.9b  35% 1.9c   BOSS   87%  7.4b  49% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  NORMAL  99%  2.8r  26%    ELITE   70%  5.7r  72%    BOSS    13%  6.9r  94%    </t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.6b  26% 2.0c   LATE   99%  5.6b  38% 2.0c   ELITE  84%  6.3b  59% 2.0c   BOSS   56%  8.5b  76% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  NORMAL 100%  2.6r  15%    ELITE   91%  5.4r  61%    BOSS    38%  8.3r  82%    </t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  12% 1.2c   LATE  100%  3.7b  28% 1.7c   ELITE 100%  4.2b  30% 1.7c   BOSS   79%  6.8b  55% 1.8c   </t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  NORMAL 100%  3.3r  33%    ELITE   29%  5.9r  90%    BOSS     2%  6.6r  99%    </t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  96%  4.7b  42% 1.8c   LATE   70%  5.3b  70% 1.9c   ELITE  50%  5.6b  82% 1.7c   BOSS   19%  6.6b  93% 1.8c   </t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  NORMAL  89%  4.4r  54%    ELITE    5%  5.2r  98%    BOSS     0%  5.0r 100%    </t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  52%  5.8b  80% 1.8c   LATE   16%  4.8b  95% 1.9c   ELITE   4%  4.2b  98% 1.7c   BOSS    1%  4.4b  99% 1.8c   </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="69" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.5b  20% 1.1c   LATE   98%  4.2b  46% 1.6c   ELITE  98%  4.4b  44% 1.7c   BOSS   48%  6.8b  78% 1.7c   </t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="69" t="inlineStr">
-        <is>
-          <t>EACH ENEMY on its own floor (normal floor 2, elite floor 2, boss floor 3), AVERAGE player : WIN PERCENT / ROUNDS</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  67%  5.3b  73% 1.7c   LATE    6%  3.7b  98% 1.4c   ELITE   6%  4.2b  98% 1.5c   BOSS    0%  4.1b  99% 1.4c   </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HUSH                  100%  2.3r</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DEAD AIR              100%  2.5r</t>
-        </is>
-      </c>
-    </row>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   3%  3.4b  99% 1.5c   LATE    0%  2.4b 100% 1.4c   ELITE   0%  2.5b 100% 1.3c   BOSS    0%  2.5b 100% 1.3c   </t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE LULL              100%  2.6r</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3), AVERAGE player : WIN PERCENT / BARS</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STATIC                100%  2.2r</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HUSH                   74%  5.3b</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         97%  4.7r</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DEAD AIR               65%  5.2b</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHITE NOISE            88%  4.5r</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE LULL               75%  5.5b</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REQUIEM                 1%  5.9r</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STATIC                 74%  5.2b</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER    45%  9.8r</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE MUTE CHOIR         68%  6.0b</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  5.2r</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHITE NOISE            33%  5.3b</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="69" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REQUIEM                 0%  3.9b</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="69" t="inlineStr">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE NAMELESS MASTER     1%  5.2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS 100%    0% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    91%    0% / 2% / 6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE    4%    17% / 48% / 30%</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="A34" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER   0%    68% / 31% / 0%</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="69" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="69" t="inlineStr">
-        <is>
-          <t>CONDUCTORS (runs as above) : WIN PERCENT  STRONG / AVERAGE</t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE UNHEARING       88% / 6%</t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG    56%    0% / 12% / 30%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE SHADOWLESS      90% / 3%</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    40% / 59% / 0%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE METRONOME       83% / 4%</t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE HEARTLESS       82% / 1%</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE KING'S BATON    93% / 4%</t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE UNSIGNED        81% / 3%</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EXPERT    11%    9% / 45% / 34%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="69" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG     0%    60% / 39% / 0%</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="69" t="inlineStr">
-        <is>
-          <t>BANDS (runs as above, THE UNHEARING) : WIN PERCENT  STRONG / AVERAGE</t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    100% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ANNA KLARA OTTO     90% / 4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  MALI CHAI NUAN      97% / 10%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  LUKA IRIS BORIS     96% / 14%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNHEARING       58% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE SHADOWLESS      55% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE METRONOME       44% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE HEARTLESS       64% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE KING'S BATON    66% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNSIGNED        45% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8546,12 +8585,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Alpha 7</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>แท็บ Turn Battle / Turn Enemies / Turn Conductors / Turn Sim = การต่อสู้แบบผลัดตา (branch Alpha7, 19 ต.ค.) สร้างจากโค้ดด้วยสคริปต์ ค่าในแท็บอื่นเป็นของดวลเดิม (Alpha6) ที่ยังอยู่ในโค้ดตอนปิด TurnBattleOn</t>
         </is>
@@ -8573,7 +8612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -8605,2226 +8644,2705 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Turn Battle On</t>
         </is>
       </c>
-      <c r="B2" s="68" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TurnBattleOn</t>
         </is>
       </c>
-      <c r="C2" s="68" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="D2" s="68" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>LifeWord</t>
         </is>
       </c>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "LIFE" : "BREATH"</t>
         </is>
       </c>
-      <c r="D3" s="68" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B4" s="68" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>LifeWordLower</t>
         </is>
       </c>
-      <c r="C4" s="68" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "life" : "breath"</t>
         </is>
       </c>
-      <c r="D4" s="68" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>TurnHp</t>
         </is>
       </c>
-      <c r="C5" s="68" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>{ 30, 26, 36 }</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TurnSpeed</t>
         </is>
       </c>
-      <c r="C6" s="68" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>{ 5, 7, 3 }</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>TurnEnemyHp</t>
         </is>
       </c>
-      <c r="C7" s="68" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>{ 50, 120, 250 }</t>
         </is>
       </c>
-      <c r="D7" s="68" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>TurnEnemySpeed</t>
         </is>
       </c>
-      <c r="C8" s="68" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>{ 4, 4, 4 }</t>
         </is>
       </c>
-      <c r="D8" s="68" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>TurnAttackPerPower</t>
         </is>
       </c>
-      <c r="C9" s="68" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>TurnPerfect</t>
         </is>
       </c>
-      <c r="C10" s="68" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>right way, right size, on time</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>TurnGood</t>
         </is>
       </c>
-      <c r="C11" s="68" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="68" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>right way, right size, a little off time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>TurnWrongSize</t>
         </is>
       </c>
-      <c r="C12" s="68" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D12" s="68" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>on time but the wrong size</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="68" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>TurnMiss</t>
         </is>
       </c>
-      <c r="C13" s="68" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D13" s="68" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>the wrong way, too early, too late or no swipe</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TurnAttackScale</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ATTACK : no swipe, it always hits at this</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TurnAttackOffBeat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ATTACK : the OFF-BEAT it adds</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TurnStartBand</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>musicians on the field when a fight starts (FULL STAGE in the ARCHIVE adds 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TurnFieldMost</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>musicians on the field at most, the called ones too</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TurnCallCost</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CALL : BREATH to bring one in from the BENCH, one per bar (NORMAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MaestroTurnCallCost</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MAESTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TurnCallCostStep</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>the second call of a fight and every one after costs this much more</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TurnCutInSpeed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ONE BAR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TurnCutInAfter</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>right after this many of the band's moves</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TurnPackEarly</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{ 1, 2, 3 }</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>an ENCOUNTER in the first half of the floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TurnPackLate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{ 2, 3, 4 }</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>in the second half</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TurnEliteEscort</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{ 0, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ordinary enemies that come with an ELITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TurnBossEscort</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{ 0, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>and with the BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MaestroTurnDamage</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TurnShardsPerEscort</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>shards for each enemy beyond the first</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>TurnFloorLife</t>
         </is>
       </c>
-      <c r="C14" s="68" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>{ 1, 1.3, 1.6 }</t>
         </is>
       </c>
-      <c r="D14" s="68" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="68" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>TurnFloorDamage</t>
         </is>
       </c>
-      <c r="C15" s="68" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>{ 1, 1.2, 1.4 }</t>
         </is>
       </c>
-      <c r="D15" s="68" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="68" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B16" s="68" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>TurnFillsGapsScale</t>
         </is>
       </c>
-      <c r="C16" s="68" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D16" s="68" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>DEAD AIR : a missed note</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B17" s="68" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>TurnLullHeal</t>
         </is>
       </c>
-      <c r="C17" s="68" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D17" s="68" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>THE LULL : life back on its humming turn</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="68" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>TurnLullEvery</t>
         </is>
       </c>
-      <c r="C18" s="68" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="68" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>every this many turns</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>TurnFastGap</t>
         </is>
       </c>
-      <c r="C19" s="68" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D19" s="68" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>REQUIEM : the gap between notes below half life</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="68" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B20" s="68" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>TurnBargainSteal</t>
         </is>
       </c>
-      <c r="C20" s="68" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="68" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING : breath taken by each attack</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="68" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B21" s="68" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>TurnPracticeHp</t>
         </is>
       </c>
-      <c r="C21" s="68" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D21" s="68" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="68" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B22" s="68" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>TurnPracticeSpeed</t>
         </is>
       </c>
-      <c r="C22" s="68" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="68" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="68" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B23" s="68" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>TurnPracticePower</t>
         </is>
       </c>
-      <c r="C23" s="68" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="68" t="inlineStr">
-        <is>
-          <t>each note hits this x TurnNoteDamage (3 life)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="68" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>each note hits this x TurnNoteDamage (4 life)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B24" s="68" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>TurnNotesMin</t>
         </is>
       </c>
-      <c r="C24" s="68" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>{ 1, 2, 3 }</t>
         </is>
       </c>
-      <c r="D24" s="68" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ELITE and BOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>TurnNotesMax</t>
         </is>
       </c>
-      <c r="C25" s="68" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>{ 2, 3, 4 }</t>
         </is>
       </c>
-      <c r="D25" s="68" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B26" s="68" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TurnSmallNotesMin</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{ 1, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ordinary enemies</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Enemy Attack</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TurnSmallNotesMax</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{ 2, 2, 2 }</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Enemy Attack</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>TurnNoteDamage</t>
         </is>
       </c>
-      <c r="C26" s="68" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PARRY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TurnParryGoodKeep</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TurnBreathMax</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TurnBreathStart</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TurnBreathPerAttack</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TurnBreathPerParry</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>for each note parried PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KNOCKED OUT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TurnReviveHp</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>OFF-BEAT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TurnOffBeatMax</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>OFF-BEAT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TurnParryOffBeat</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>each note parried PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>OFF-BEAT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TurnOffBeatScale</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D26" s="68" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="68" t="inlineStr">
-        <is>
-          <t>PARRY</t>
-        </is>
-      </c>
-      <c r="B27" s="68" t="inlineStr">
-        <is>
-          <t>TurnParryGoodKeep</t>
-        </is>
-      </c>
-      <c r="C27" s="68" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>damage against an enemy off the beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>TurnDissonanceMost</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>DISSONANCE stacks no higher</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TurnCrescendoStep</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CRESCENDO : each stack hits this much harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TurnCrescendoMost</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TurnMuteTurns</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MUTE : turns without skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Statuses</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>TurnGuardKeep</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D27" s="68" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="68" t="inlineStr">
-        <is>
-          <t>BREATH</t>
-        </is>
-      </c>
-      <c r="B28" s="68" t="inlineStr">
-        <is>
-          <t>TurnBreathMax</t>
-        </is>
-      </c>
-      <c r="C28" s="68" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GUARD : the share of a hit that gets through</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COUNTER and CADENZA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>TurnCounterScale</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>x the target's attack damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COUNTER and CADENZA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>TurnCadenzaCounter</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COUNTER and CADENZA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>TurnCadenzaEvery</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COUNTER and CADENZA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>TurnCadenzaPower</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>TurnHoldBase</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TurnHoldGain</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TurnRollPerfect</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TurnRollGood</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MaestroTurnRollPerfect</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Skill Notes</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MaestroTurnRollGood</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Conductors</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TurnSignatureNeed</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Conductors</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TurnBeethovenMost</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Conductors</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TurnBoltDamage</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Conductors</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TurnMozartRun</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Conductors</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TurnFeatherPerStroke</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TurnPaganiniLife</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TurnCapricePrice</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TurnCapricePerStroke</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TurnLullyWindow</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TurnSunHeal</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>THE SUN : life back for every musician at full strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TurnFannyScale</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TurnFelixHeal</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>FELIX's voice heals this much more</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TurnFelixCrescendo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>and gives this much more CRESCENDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TurnDuetDamage</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TWO VOICES : damage to every enemy at full strength</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>The other four of the lore</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TurnDuetHeal</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>and life back for every musician</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TurnCountsWindow</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TurnQuietScale</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TurnMomentumMost</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TurnByEarScale</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TurnHeldNoteShare</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TurnStepBetterScale</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TurnFourBarsEvery</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TurnFourBarsScale</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>hits this much harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TurnLateBonus</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TurnThunderSoften</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EchoesPerWin</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>each fight won</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EchoesPerFloor</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D28" s="68" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="68" t="inlineStr">
-        <is>
-          <t>BREATH</t>
-        </is>
-      </c>
-      <c r="B29" s="68" t="inlineStr">
-        <is>
-          <t>TurnBreathStart</t>
-        </is>
-      </c>
-      <c r="C29" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D29" s="68" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="68" t="inlineStr">
-        <is>
-          <t>BREATH</t>
-        </is>
-      </c>
-      <c r="B30" s="68" t="inlineStr">
-        <is>
-          <t>TurnBreathPerAttack</t>
-        </is>
-      </c>
-      <c r="C30" s="68" t="inlineStr">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>each floor cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EchoesRunWon</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>the whole run won</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EchoesMaestro</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MAESTRO pays more</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ArchiveLifePerLevel</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>STRONGER BAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ArchiveBreathPerLevel</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="68" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="68" t="inlineStr">
-        <is>
-          <t>BREATH</t>
-        </is>
-      </c>
-      <c r="B31" s="68" t="inlineStr">
-        <is>
-          <t>TurnBreathPerParry</t>
-        </is>
-      </c>
-      <c r="C31" s="68" t="inlineStr">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DEEP BREATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ArchiveSignaturePerLevel</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>WARM UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ArchiveShardsPerLevel</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SAVINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ArchiveStagePerLevel</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="68" t="inlineStr">
-        <is>
-          <t>for each note parried PERFECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="68" t="inlineStr">
-        <is>
-          <t>KNOCKED OUT</t>
-        </is>
-      </c>
-      <c r="B32" s="68" t="inlineStr">
-        <is>
-          <t>TurnReviveHp</t>
-        </is>
-      </c>
-      <c r="C32" s="68" t="inlineStr">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TurnReedCaseHeal</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>REED CASE : wind players' healing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TurnSpareSticksOffBeat</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TurnPianissimoBreath</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="68" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="68" t="inlineStr">
-        <is>
-          <t>OFF-BEAT</t>
-        </is>
-      </c>
-      <c r="B33" s="68" t="inlineStr">
-        <is>
-          <t>TurnOffBeatMax</t>
-        </is>
-      </c>
-      <c r="C33" s="68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D33" s="68" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="68" t="inlineStr">
-        <is>
-          <t>OFF-BEAT</t>
-        </is>
-      </c>
-      <c r="B34" s="68" t="inlineStr">
-        <is>
-          <t>TurnPerfectOffBeat</t>
-        </is>
-      </c>
-      <c r="C34" s="68" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D34" s="68" t="inlineStr">
-        <is>
-          <t>a PERFECT attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="68" t="inlineStr">
-        <is>
-          <t>OFF-BEAT</t>
-        </is>
-      </c>
-      <c r="B35" s="68" t="inlineStr">
-        <is>
-          <t>TurnParryOffBeat</t>
-        </is>
-      </c>
-      <c r="C35" s="68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D35" s="68" t="inlineStr">
-        <is>
-          <t>each note parried PERFECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="68" t="inlineStr">
-        <is>
-          <t>OFF-BEAT</t>
-        </is>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
-        <is>
-          <t>TurnOffBeatScale</t>
-        </is>
-      </c>
-      <c r="C36" s="68" t="inlineStr">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TurnBreathMarkStart</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BREATH MARK : more breath at the start of a fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TurnTuttiScale</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TUTTI : skills that reach everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TurnRubatoMiss</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TurnCrescendoStart</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CRESCENDO : stacks on every musician at the start</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TurnSforzandoScale</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SFORZANDO : a PERFECT f note</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TurnOvertureScale</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OVERTURE : the band's first hit of a fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TurnCounterpointScale</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>COUNTERPOINT : the COUNTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TurnAccelerandoShakes</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TurnGraceTimes</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TurnMarcatoOffBeat</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TurnConBrioNeed</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TurnCodaBelow</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>CODA : an enemy under this share of its life</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TurnCodaScale</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D36" s="68" t="inlineStr">
-        <is>
-          <t>damage against an enemy off the beat</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="68" t="inlineStr">
-        <is>
-          <t>Statuses</t>
-        </is>
-      </c>
-      <c r="B37" s="68" t="inlineStr">
-        <is>
-          <t>TurnDissonanceMost</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D37" s="68" t="inlineStr">
-        <is>
-          <t>DISSONANCE stacks no higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="68" t="inlineStr">
-        <is>
-          <t>Statuses</t>
-        </is>
-      </c>
-      <c r="B38" s="68" t="inlineStr">
-        <is>
-          <t>TurnCrescendoStep</t>
-        </is>
-      </c>
-      <c r="C38" s="68" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="D38" s="68" t="inlineStr">
-        <is>
-          <t>CRESCENDO : each stack hits this much harder</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="68" t="inlineStr">
-        <is>
-          <t>Statuses</t>
-        </is>
-      </c>
-      <c r="B39" s="68" t="inlineStr">
-        <is>
-          <t>TurnCrescendoMost</t>
-        </is>
-      </c>
-      <c r="C39" s="68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D39" s="68" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="68" t="inlineStr">
-        <is>
-          <t>Statuses</t>
-        </is>
-      </c>
-      <c r="B40" s="68" t="inlineStr">
-        <is>
-          <t>TurnMuteTurns</t>
-        </is>
-      </c>
-      <c r="C40" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" s="68" t="inlineStr">
-        <is>
-          <t>MUTE : turns without skills</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="68" t="inlineStr">
-        <is>
-          <t>Statuses</t>
-        </is>
-      </c>
-      <c r="B41" s="68" t="inlineStr">
-        <is>
-          <t>TurnGuardKeep</t>
-        </is>
-      </c>
-      <c r="C41" s="68" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D41" s="68" t="inlineStr">
-        <is>
-          <t>GUARD : the share of a hit that gets through</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="68" t="inlineStr">
-        <is>
-          <t>COUNTER and CADENZA</t>
-        </is>
-      </c>
-      <c r="B42" s="68" t="inlineStr">
-        <is>
-          <t>TurnCounterScale</t>
-        </is>
-      </c>
-      <c r="C42" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" s="68" t="inlineStr">
-        <is>
-          <t>x the target's attack damage</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="68" t="inlineStr">
-        <is>
-          <t>COUNTER and CADENZA</t>
-        </is>
-      </c>
-      <c r="B43" s="68" t="inlineStr">
-        <is>
-          <t>TurnCadenzaCounter</t>
-        </is>
-      </c>
-      <c r="C43" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D43" s="68" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="68" t="inlineStr">
-        <is>
-          <t>COUNTER and CADENZA</t>
-        </is>
-      </c>
-      <c r="B44" s="68" t="inlineStr">
-        <is>
-          <t>TurnCadenzaEvery</t>
-        </is>
-      </c>
-      <c r="C44" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D44" s="68" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="68" t="inlineStr">
-        <is>
-          <t>COUNTER and CADENZA</t>
-        </is>
-      </c>
-      <c r="B45" s="68" t="inlineStr">
-        <is>
-          <t>TurnCadenzaPower</t>
-        </is>
-      </c>
-      <c r="C45" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D45" s="68" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B46" s="68" t="inlineStr">
-        <is>
-          <t>TurnHoldBase</t>
-        </is>
-      </c>
-      <c r="C46" s="68" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D46" s="68" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B47" s="68" t="inlineStr">
-        <is>
-          <t>TurnHoldGain</t>
-        </is>
-      </c>
-      <c r="C47" s="68" t="inlineStr">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>takes this much more</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TurnRingTime</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>from a note showing to the moment to swipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MaestroTurnRingTime</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D47" s="68" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B48" s="68" t="inlineStr">
-        <is>
-          <t>TurnRollPerfect</t>
-        </is>
-      </c>
-      <c r="C48" s="68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D48" s="68" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B49" s="68" t="inlineStr">
-        <is>
-          <t>TurnRollGood</t>
-        </is>
-      </c>
-      <c r="C49" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D49" s="68" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B50" s="68" t="inlineStr">
-        <is>
-          <t>MaestroTurnRollPerfect</t>
-        </is>
-      </c>
-      <c r="C50" s="68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D50" s="68" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="68" t="inlineStr">
-        <is>
-          <t>Skill Notes</t>
-        </is>
-      </c>
-      <c r="B51" s="68" t="inlineStr">
-        <is>
-          <t>MaestroTurnRollGood</t>
-        </is>
-      </c>
-      <c r="C51" s="68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D51" s="68" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="68" t="inlineStr">
-        <is>
-          <t>Conductors</t>
-        </is>
-      </c>
-      <c r="B52" s="68" t="inlineStr">
-        <is>
-          <t>TurnSignatureNeed</t>
-        </is>
-      </c>
-      <c r="C52" s="68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D52" s="68" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="68" t="inlineStr">
-        <is>
-          <t>Conductors</t>
-        </is>
-      </c>
-      <c r="B53" s="68" t="inlineStr">
-        <is>
-          <t>TurnBeethovenMost</t>
-        </is>
-      </c>
-      <c r="C53" s="68" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D53" s="68" t="inlineStr">
-        <is>
-          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="68" t="inlineStr">
-        <is>
-          <t>Conductors</t>
-        </is>
-      </c>
-      <c r="B54" s="68" t="inlineStr">
-        <is>
-          <t>TurnBoltDamage</t>
-        </is>
-      </c>
-      <c r="C54" s="68" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D54" s="68" t="inlineStr">
-        <is>
-          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="68" t="inlineStr">
-        <is>
-          <t>Conductors</t>
-        </is>
-      </c>
-      <c r="B55" s="68" t="inlineStr">
-        <is>
-          <t>TurnMozartRun</t>
-        </is>
-      </c>
-      <c r="C55" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D55" s="68" t="inlineStr">
-        <is>
-          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B56" s="68" t="inlineStr">
-        <is>
-          <t>TurnPaganiniLife</t>
-        </is>
-      </c>
-      <c r="C56" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D56" s="68" t="inlineStr">
-        <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B57" s="68" t="inlineStr">
-        <is>
-          <t>TurnCapricePrice</t>
-        </is>
-      </c>
-      <c r="C57" s="68" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="D57" s="68" t="inlineStr">
-        <is>
-          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B58" s="68" t="inlineStr">
-        <is>
-          <t>TurnLullyWindow</t>
-        </is>
-      </c>
-      <c r="C58" s="68" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="D58" s="68" t="inlineStr">
-        <is>
-          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B59" s="68" t="inlineStr">
-        <is>
-          <t>TurnSunHeal</t>
-        </is>
-      </c>
-      <c r="C59" s="68" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D59" s="68" t="inlineStr">
-        <is>
-          <t>THE SUN : life back for every musician at full strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B60" s="68" t="inlineStr">
-        <is>
-          <t>TurnFannyScale</t>
-        </is>
-      </c>
-      <c r="C60" s="68" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="D60" s="68" t="inlineStr">
-        <is>
-          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B61" s="68" t="inlineStr">
-        <is>
-          <t>TurnFelixHeal</t>
-        </is>
-      </c>
-      <c r="C61" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D61" s="68" t="inlineStr">
-        <is>
-          <t>FELIX's voice heals this much more</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B62" s="68" t="inlineStr">
-        <is>
-          <t>TurnFelixCrescendo</t>
-        </is>
-      </c>
-      <c r="C62" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D62" s="68" t="inlineStr">
-        <is>
-          <t>and gives this much more CRESCENDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B63" s="68" t="inlineStr">
-        <is>
-          <t>TurnDuetDamage</t>
-        </is>
-      </c>
-      <c r="C63" s="68" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>TWO VOICES : damage to every enemy at full strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="68" t="inlineStr">
-        <is>
-          <t>The other four of the lore</t>
-        </is>
-      </c>
-      <c r="B64" s="68" t="inlineStr">
-        <is>
-          <t>TurnDuetHeal</t>
-        </is>
-      </c>
-      <c r="C64" s="68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D64" s="68" t="inlineStr">
-        <is>
-          <t>and life back for every musician</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B65" s="68" t="inlineStr">
-        <is>
-          <t>TurnCountsWindow</t>
-        </is>
-      </c>
-      <c r="C65" s="68" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="D65" s="68" t="inlineStr">
-        <is>
-          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B66" s="68" t="inlineStr">
-        <is>
-          <t>TurnQuietScale</t>
-        </is>
-      </c>
-      <c r="C66" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D66" s="68" t="inlineStr">
-        <is>
-          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B67" s="68" t="inlineStr">
-        <is>
-          <t>TurnMomentumMost</t>
-        </is>
-      </c>
-      <c r="C67" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D67" s="68" t="inlineStr">
-        <is>
-          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B68" s="68" t="inlineStr">
-        <is>
-          <t>TurnByEarScale</t>
-        </is>
-      </c>
-      <c r="C68" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D68" s="68" t="inlineStr">
-        <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B69" s="68" t="inlineStr">
-        <is>
-          <t>TurnHeldNoteShare</t>
-        </is>
-      </c>
-      <c r="C69" s="68" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D69" s="68" t="inlineStr">
-        <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B70" s="68" t="inlineStr">
-        <is>
-          <t>TurnStepBetterScale</t>
-        </is>
-      </c>
-      <c r="C70" s="68" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D70" s="68" t="inlineStr">
-        <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B71" s="68" t="inlineStr">
-        <is>
-          <t>TurnFourBarsEvery</t>
-        </is>
-      </c>
-      <c r="C71" s="68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D71" s="68" t="inlineStr">
-        <is>
-          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B72" s="68" t="inlineStr">
-        <is>
-          <t>TurnFourBarsScale</t>
-        </is>
-      </c>
-      <c r="C72" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D72" s="68" t="inlineStr">
-        <is>
-          <t>hits this much harder</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B73" s="68" t="inlineStr">
-        <is>
-          <t>TurnLateBonus</t>
-        </is>
-      </c>
-      <c r="C73" s="68" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="D73" s="68" t="inlineStr">
-        <is>
-          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="68" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B74" s="68" t="inlineStr">
-        <is>
-          <t>TurnThunderSoften</t>
-        </is>
-      </c>
-      <c r="C74" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D74" s="68" t="inlineStr">
-        <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B75" s="68" t="inlineStr">
-        <is>
-          <t>EchoesPerWin</t>
-        </is>
-      </c>
-      <c r="C75" s="68" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D75" s="68" t="inlineStr">
-        <is>
-          <t>each fight won</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B76" s="68" t="inlineStr">
-        <is>
-          <t>EchoesPerFloor</t>
-        </is>
-      </c>
-      <c r="C76" s="68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D76" s="68" t="inlineStr">
-        <is>
-          <t>each floor cleared</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B77" s="68" t="inlineStr">
-        <is>
-          <t>EchoesRunWon</t>
-        </is>
-      </c>
-      <c r="C77" s="68" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D77" s="68" t="inlineStr">
-        <is>
-          <t>the whole run won</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B78" s="68" t="inlineStr">
-        <is>
-          <t>EchoesMaestro</t>
-        </is>
-      </c>
-      <c r="C78" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D78" s="68" t="inlineStr">
-        <is>
-          <t>MAESTRO pays more</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B79" s="68" t="inlineStr">
-        <is>
-          <t>ArchiveLifePerLevel</t>
-        </is>
-      </c>
-      <c r="C79" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D79" s="68" t="inlineStr">
-        <is>
-          <t>STRONGER BAND</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B80" s="68" t="inlineStr">
-        <is>
-          <t>ArchiveBreathPerLevel</t>
-        </is>
-      </c>
-      <c r="C80" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D80" s="68" t="inlineStr">
-        <is>
-          <t>DEEP BREATH</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B81" s="68" t="inlineStr">
-        <is>
-          <t>ArchiveSignaturePerLevel</t>
-        </is>
-      </c>
-      <c r="C81" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D81" s="68" t="inlineStr">
-        <is>
-          <t>WARM UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="68" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B82" s="68" t="inlineStr">
-        <is>
-          <t>ArchiveShardsPerLevel</t>
-        </is>
-      </c>
-      <c r="C82" s="68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D82" s="68" t="inlineStr">
-        <is>
-          <t>SAVINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B83" s="68" t="inlineStr">
-        <is>
-          <t>TurnReedCaseHeal</t>
-        </is>
-      </c>
-      <c r="C83" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D83" s="68" t="inlineStr">
-        <is>
-          <t>REED CASE : wind players' healing</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B84" s="68" t="inlineStr">
-        <is>
-          <t>TurnSpareSticksOffBeat</t>
-        </is>
-      </c>
-      <c r="C84" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D84" s="68" t="inlineStr">
-        <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B85" s="68" t="inlineStr">
-        <is>
-          <t>TurnPianissimoBreath</t>
-        </is>
-      </c>
-      <c r="C85" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D85" s="68" t="inlineStr">
-        <is>
-          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B86" s="68" t="inlineStr">
-        <is>
-          <t>TurnBreathMarkStart</t>
-        </is>
-      </c>
-      <c r="C86" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D86" s="68" t="inlineStr">
-        <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B87" s="68" t="inlineStr">
-        <is>
-          <t>TurnTuttiScale</t>
-        </is>
-      </c>
-      <c r="C87" s="68" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="D87" s="68" t="inlineStr">
-        <is>
-          <t>TUTTI : skills that reach everyone</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B88" s="68" t="inlineStr">
-        <is>
-          <t>TurnRubatoMiss</t>
-        </is>
-      </c>
-      <c r="C88" s="68" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D88" s="68" t="inlineStr">
-        <is>
-          <t>RUBATO : a MISS hits at this instead of TurnMiss</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B89" s="68" t="inlineStr">
-        <is>
-          <t>TurnCrescendoStart</t>
-        </is>
-      </c>
-      <c r="C89" s="68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D89" s="68" t="inlineStr">
-        <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B90" s="68" t="inlineStr">
-        <is>
-          <t>TurnSforzandoScale</t>
-        </is>
-      </c>
-      <c r="C90" s="68" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D90" s="68" t="inlineStr">
-        <is>
-          <t>SFORZANDO : a PERFECT f note</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B91" s="68" t="inlineStr">
-        <is>
-          <t>TurnOvertureScale</t>
-        </is>
-      </c>
-      <c r="C91" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D91" s="68" t="inlineStr">
-        <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B92" s="68" t="inlineStr">
-        <is>
-          <t>TurnCounterpointScale</t>
-        </is>
-      </c>
-      <c r="C92" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D92" s="68" t="inlineStr">
-        <is>
-          <t>COUNTERPOINT : the COUNTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B93" s="68" t="inlineStr">
-        <is>
-          <t>TurnAccelerandoShakes</t>
-        </is>
-      </c>
-      <c r="C93" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D93" s="68" t="inlineStr">
-        <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B94" s="68" t="inlineStr">
-        <is>
-          <t>TurnGraceTimes</t>
-        </is>
-      </c>
-      <c r="C94" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D94" s="68" t="inlineStr">
-        <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B95" s="68" t="inlineStr">
-        <is>
-          <t>TurnMarcatoOffBeat</t>
-        </is>
-      </c>
-      <c r="C95" s="68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D95" s="68" t="inlineStr">
-        <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B96" s="68" t="inlineStr">
-        <is>
-          <t>TurnConBrioNeed</t>
-        </is>
-      </c>
-      <c r="C96" s="68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D96" s="68" t="inlineStr">
-        <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B97" s="68" t="inlineStr">
-        <is>
-          <t>TurnCodaBelow</t>
-        </is>
-      </c>
-      <c r="C97" s="68" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="D97" s="68" t="inlineStr">
-        <is>
-          <t>CODA : an enemy under this share of its life</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="68" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B98" s="68" t="inlineStr">
-        <is>
-          <t>TurnCodaScale</t>
-        </is>
-      </c>
-      <c r="C98" s="68" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D98" s="68" t="inlineStr">
-        <is>
-          <t>takes this much more</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="68" t="inlineStr">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>MAESTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B99" s="68" t="inlineStr">
-        <is>
-          <t>TurnRingTime</t>
-        </is>
-      </c>
-      <c r="C99" s="68" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D99" s="68" t="inlineStr">
-        <is>
-          <t>from a note showing to the moment to swipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="68" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TurnNoteGap</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>between the notes of one enemy attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B100" s="68" t="inlineStr">
-        <is>
-          <t>MaestroTurnRingTime</t>
-        </is>
-      </c>
-      <c r="C100" s="68" t="inlineStr">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TurnPause</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D100" s="68" t="inlineStr">
-        <is>
-          <t>MAESTRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="68" t="inlineStr">
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>after a turn, before the next one starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B101" s="68" t="inlineStr">
-        <is>
-          <t>TurnNoteGap</t>
-        </is>
-      </c>
-      <c r="C101" s="68" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D101" s="68" t="inlineStr">
-        <is>
-          <t>between the notes of one enemy attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="68" t="inlineStr">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TurnHitStop</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B102" s="68" t="inlineStr">
-        <is>
-          <t>TurnPause</t>
-        </is>
-      </c>
-      <c r="C102" s="68" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TurnStrikeTime</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TurnStrikeImpact</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>when in it the hit lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TurnStrikeStop</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>the freeze when it lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D102" s="68" t="inlineStr">
-        <is>
-          <t>after a turn, before the next one starts</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="68" t="inlineStr">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B103" s="68" t="inlineStr">
-        <is>
-          <t>TurnHitStop</t>
-        </is>
-      </c>
-      <c r="C103" s="68" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="D103" s="68" t="inlineStr">
-        <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="68" t="inlineStr">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TurnHoldStill</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>pixels per second the baton may drift and still count as still</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B104" s="68" t="inlineStr">
-        <is>
-          <t>TurnEndTime</t>
-        </is>
-      </c>
-      <c r="C104" s="68" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="D104" s="68" t="inlineStr">
-        <is>
-          <t>the win or lose banner stays this long</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="68" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B105" s="68" t="inlineStr">
-        <is>
-          <t>TurnSparkGap</t>
-        </is>
-      </c>
-      <c r="C105" s="68" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="D105" s="68" t="inlineStr">
-        <is>
-          <t>a spark comes this soon after the note before it</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="68" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B106" s="68" t="inlineStr">
-        <is>
-          <t>TurnHoldTime</t>
-        </is>
-      </c>
-      <c r="C106" s="68" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D106" s="68" t="inlineStr">
-        <is>
-          <t>how long a HOLD note wants holding</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="68" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B107" s="68" t="inlineStr">
-        <is>
-          <t>TurnHoldStill</t>
-        </is>
-      </c>
-      <c r="C107" s="68" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="D107" s="68" t="inlineStr">
-        <is>
-          <t>pixels per second the baton may drift and still count as still</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="68" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B108" s="68" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C108" s="68" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D108" s="68" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -10841,7 +11359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="33" min="1" max="1"/>
@@ -10895,388 +11413,396 @@
           <t>Trait in the turn battle</t>
         </is>
       </c>
+      <c r="I1" s="67" t="inlineStr">
+        <is>
+          <t>CUT IN (speed 5 or more)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="68" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>HUSH</t>
         </is>
       </c>
-      <c r="B2" s="68" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C2" s="68" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D2" s="68" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E2" s="68" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="68" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Dp Up, Lp Rp Dp</t>
         </is>
       </c>
-      <c r="G2" s="68" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ECHO FADES (2)</t>
         </is>
       </c>
-      <c r="H2" s="68" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Each note that gets through adds 1 DISSONANCE.</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>DEAD AIR</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D3" s="68" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="68" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="68" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lmf Rmf, Dmf Dmf Umf</t>
         </is>
       </c>
-      <c r="G3" s="68" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>FILLS THE GAPS (2)</t>
         </is>
       </c>
-      <c r="H3" s="68" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>A note you miss hits 50 percent harder.</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>THE LULL</t>
         </is>
       </c>
-      <c r="B4" s="68" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C4" s="68" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="68" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="68" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="68" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Dp Dp, Up Dp Up</t>
         </is>
       </c>
-      <c r="G4" s="68" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>LULLABY (2)</t>
         </is>
       </c>
-      <c r="H4" s="68" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Every third turn it hums instead of attacking and gets back 12 life.</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C5" s="68" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E5" s="68" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="68" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lf Rp, Umf Df Lp</t>
         </is>
       </c>
-      <c r="G5" s="68" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>FALSE NOTES (2)</t>
         </is>
       </c>
-      <c r="H5" s="68" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>One note of each attack shows the wrong size.</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="68" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>THE MUTE CHOIR</t>
         </is>
       </c>
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C6" s="68" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D6" s="68" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="68" t="n">
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="68" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Df Df Uf, Lmf Rmf Lmf Rmf</t>
         </is>
       </c>
-      <c r="G6" s="68" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SILENT MOUTHS (1)</t>
         </is>
       </c>
-      <c r="H6" s="68" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>A note that gets through takes the target's skills away for a turn.</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="68" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>WHITE NOISE</t>
         </is>
       </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C7" s="68" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" s="68" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="68" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="68" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lp Rp Lp Rp, Up Dp Up Dp</t>
         </is>
       </c>
-      <c r="G7" s="68" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>NO REST (1)</t>
         </is>
       </c>
-      <c r="H7" s="68" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>One note more in every attack, and parrying it gives no BREATH.</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>REQUIEM</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C8" s="68" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D8" s="68" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E8" s="68" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="68" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Df Lmf Rmf Uf, Lf Rf Lf Rf</t>
         </is>
       </c>
-      <c r="G8" s="68" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>UNFINISHED (1)</t>
         </is>
       </c>
-      <c r="H8" s="68" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Below half life it swaps left and right and plays faster.</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="68" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>THE NAMELESS MASTER</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C9" s="68" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" s="68" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="68" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="68" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Dmf Umf Lmf, Rf Lf Dp Up</t>
         </is>
       </c>
-      <c r="G9" s="68" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ANSWER BETTER (1)</t>
         </is>
       </c>
-      <c r="H9" s="68" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>It answers with the notes of the last skill your band played.</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING</t>
         </is>
       </c>
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C10" s="68" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D10" s="68" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="68" t="n">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="68" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Rf Rf Lf, Uf Df Uf Df</t>
         </is>
       </c>
-      <c r="G10" s="68" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>THE BARGAIN (1)</t>
         </is>
       </c>
-      <c r="H10" s="68" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Each of its attacks steals 1 BREATH.</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="68" t="inlineStr">
-        <is>
-          <t>PRACTICE</t>
-        </is>
-      </c>
-      <c r="B11" s="68" t="inlineStr"/>
-      <c r="C11" s="68" t="inlineStr">
-        <is>
-          <t>BattleRules.TurnPracticeHp</t>
-        </is>
-      </c>
-      <c r="D11" s="68" t="inlineStr">
-        <is>
-          <t>BattleRules.TurnPracticeSpeed</t>
-        </is>
-      </c>
-      <c r="E11" s="68" t="inlineStr"/>
-      <c r="F11" s="68" t="inlineStr"/>
-      <c r="G11" s="68" t="inlineStr"/>
-      <c r="H11" s="68" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1470,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
@@ -1508,105 +1508,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 2.0c   LATE  100%  3.0b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  4.9b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 1.8c   LATE  100%  2.9b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  4.9b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.1b   0% 2.0c   ELITE 100%  4.0b   0% 2.0c   BOSS  100%  5.7b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.2b   0% 2.0c   ELITE 100%  3.9b   0% 2.0c   BOSS  100%  5.7b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.0b   0% 2.0c   LATE  100%  4.0b   0% 2.0c   ELITE 100%  4.5b   0% 2.0c   BOSS  100%  6.8b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  3.9b   0% 2.0c   LATE  100%  4.2b   0% 2.0c   ELITE 100%  4.4b   0% 2.0c   BOSS  100%  6.9b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.0b   2% 1.6c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.3b   6% 1.9c   BOSS  100%  5.2b  12% 1.9c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.0b   2% 1.5c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.4b   5% 2.0c   BOSS  100%  5.1b  11% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b   8% 2.0c   LATE  100%  3.3b  11% 2.0c   ELITE 100%  4.1b  14% 1.9c   BOSS  100%  6.2b  19% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.3b   8% 2.0c   LATE  100%  3.5b  11% 2.0c   ELITE 100%  4.1b  14% 2.0c   BOSS  100%  6.3b  19% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  3.9b  12% 2.0c   LATE  100%  4.8b  14% 2.0c   ELITE 100%  5.2b  22% 2.0c   BOSS   99%  7.6b  29% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.1b  13% 2.0c   LATE  100%  4.8b  15% 2.0c   ELITE 100%  5.2b  19% 2.0c   BOSS   99%  7.7b  31% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.1b   6% 1.3c   LATE  100%  3.2b  14% 1.9c   ELITE 100%  3.7b  12% 1.8c   BOSS   98%  5.8b  26% 1.9c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.2b   6% 1.4c   LATE  100%  3.1b  11% 2.0c   ELITE 100%  3.7b  12% 1.9c   BOSS  100%  5.6b  24% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.8b  20% 1.9c   LATE  100%  3.9b  25% 2.0c   ELITE  97%  4.9b  35% 1.9c   BOSS   87%  7.4b  49% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.6b  17% 2.0c   LATE  100%  4.1b  25% 2.0c   ELITE 100%  4.7b  28% 2.0c   BOSS   87%  7.4b  50% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.6b  26% 2.0c   LATE   99%  5.6b  38% 2.0c   ELITE  84%  6.3b  59% 2.0c   BOSS   56%  8.5b  76% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.7b  29% 2.0c   LATE  100%  5.7b  39% 2.0c   ELITE  89%  6.5b  55% 2.0c   BOSS   56%  8.4b  75% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  12% 1.2c   LATE  100%  3.7b  28% 1.7c   ELITE 100%  4.2b  30% 1.7c   BOSS   79%  6.8b  55% 1.8c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  10% 1.3c   LATE  100%  3.6b  23% 1.9c   ELITE 100%  4.2b  26% 1.9c   BOSS   84%  6.8b  53% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  96%  4.7b  42% 1.8c   LATE   70%  5.3b  70% 1.9c   ELITE  50%  5.6b  82% 1.7c   BOSS   19%  6.6b  93% 1.8c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  4.5b  37% 1.9c   LATE   77%  5.2b  65% 1.9c   ELITE  62%  5.8b  74% 1.9c   BOSS   21%  6.7b  91% 1.8c   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  52%  5.8b  80% 1.8c   LATE   16%  4.8b  95% 1.9c   ELITE   4%  4.2b  98% 1.7c   BOSS    1%  4.4b  99% 1.8c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  56%  5.4b  76% 1.8c   LATE   16%  4.1b  95% 1.6c   ELITE   7%  4.4b  98% 1.6c   BOSS    1%  4.4b  99% 1.6c   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.5b  20% 1.1c   LATE   98%  4.2b  46% 1.6c   ELITE  98%  4.4b  44% 1.7c   BOSS   48%  6.8b  78% 1.7c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.4b  15% 1.2c   LATE  100%  4.0b  34% 1.8c   ELITE  98%  4.5b  41% 1.9c   BOSS   47%  6.9b  78% 1.8c   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  67%  5.3b  73% 1.7c   LATE    6%  3.7b  98% 1.4c   ELITE   6%  4.2b  98% 1.5c   BOSS    0%  4.1b  99% 1.4c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  86%  5.1b  62% 1.9c   LATE   18%  4.4b  94% 1.5c   ELITE   8%  4.6b  97% 1.7c   BOSS    0%  4.5b  99% 1.6c   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   3%  3.4b  99% 1.5c   LATE    0%  2.4b 100% 1.4c   ELITE   0%  2.5b 100% 1.3c   BOSS    0%  2.5b 100% 1.3c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   2%  3.3b  98% 1.4c   LATE    0%  2.1b 100% 1.0c   ELITE   0%  2.4b 100% 1.2c   BOSS    0%  2.3b 100% 1.1c   </t>
         </is>
       </c>
     </row>
@@ -1621,49 +1621,49 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   74%  5.3b</t>
+          <t xml:space="preserve">  HUSH                   77%  5.2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               65%  5.2b</t>
+          <t xml:space="preserve">  DEAD AIR               74%  5.1b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               75%  5.5b</t>
+          <t xml:space="preserve">  THE LULL               79%  5.5b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 74%  5.2b</t>
+          <t xml:space="preserve">  STATIC                 79%  5.1b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         68%  6.0b</t>
+          <t xml:space="preserve">  THE MUTE CHOIR         72%  6.1b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            33%  5.3b</t>
+          <t xml:space="preserve">  WHITE NOISE            47%  5.7b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  3.9b</t>
+          <t xml:space="preserve">  REQUIEM                 0%  3.8b</t>
         </is>
       </c>
     </row>
@@ -1677,153 +1677,188 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROOM TONE              81%  5.5b</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
+          <t xml:space="preserve">  THE CUE                87%  5.3b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NORMAL</t>
+          <t xml:space="preserve">  THE DAMPER             68%  5.5b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  STUTTER                85%  5.2b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    STRONG    56%    0% / 12% / 30%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  THE ROUND              68%  6.2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    40% / 59% / 0%</t>
+          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
+          <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MAESTRO</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    11%    9% / 45% / 34%</t>
+          <t xml:space="preserve">    STRONG    50%    0% / 10% / 38%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    60% / 39% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    30% / 68% / 0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    100% / 0% / 0%</t>
+          <t xml:space="preserve">    NEWCOMER   0%    80% / 19% / 0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+          <t xml:space="preserve">  MAESTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
+          <t xml:space="preserve">    EXPERT    79%    0% / 3% / 17%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       58% / 0%</t>
+          <t xml:space="preserve">    STRONG     0%    15% / 72% / 12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE SHADOWLESS      55% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    94% / 5% / 0%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       44% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE HEARTLESS       64% / 0%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE KING'S BATON    66% / 0%</t>
+          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNSIGNED        45% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
+          <t xml:space="preserve">  THE UNHEARING       58% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE SHADOWLESS      51% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE METRONOME       51% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE HEARTLESS       65% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE KING'S BATON    63% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNSIGNED        50% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8612,7 +8647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -9344,134 +9379,144 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TurnPracticeHp</t>
+          <t>TurnRoomToneKeep</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TurnPracticeSpeed</t>
+          <t>TurnFeltHandCall</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>THE DAMPER : a CALL costs this much more while it stands (2 left the sim's STRONG player at 23 percent against it)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TurnPracticePower</t>
+          <t>TurnTwiceFirst</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>each note hits this x TurnNoteDamage (4 life)</t>
+          <t>STUTTER : cuts in after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TurnNotesMin</t>
+          <t>TurnTwiceSecond</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ELITE and BOSS</t>
+          <t>and again after this many</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TurnNotesMax</t>
+          <t>TurnPracticeHp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>160</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMin</t>
+          <t>TurnPracticeSpeed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{ 1, 1, 2 }</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ordinary enemies</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMax</t>
+          <t>TurnPracticePower</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{ 2, 2, 2 }</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
@@ -9483,268 +9528,263 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TurnNoteDamage</t>
+          <t>TurnNotesMin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>{ 1, 2, 3 }</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
+          <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PARRY</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TurnParryGoodKeep</t>
+          <t>TurnNotesMax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TurnBreathMax</t>
+          <t>TurnSmallNotesMin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>{ 1, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ordinary enemies</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TurnBreathStart</t>
+          <t>TurnSmallNotesMax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TurnBreathPerAttack</t>
+          <t>TurnNoteDamage</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>PARRY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TurnBreathPerParry</t>
+          <t>TurnParryGoodKeep</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>for each note parried PERFECT</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KNOCKED OUT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TurnReviveHp</t>
+          <t>TurnBreathMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TurnOffBeatMax</t>
+          <t>TurnBreathStart</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TurnParryOffBeat</t>
+          <t>TurnBreathPerAttack</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>each note parried PERFECT</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TurnOffBeatScale</t>
+          <t>TurnBreathPerParry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>damage against an enemy off the beat</t>
+          <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>KNOCKED OUT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TurnDissonanceMost</t>
+          <t>TurnReviveHp</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>DISSONANCE stacks no higher</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TurnCrescendoStep</t>
+          <t>TurnOffBeatMax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>CRESCENDO : each stack hits this much harder</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TurnCrescendoMost</t>
+          <t>TurnParryOffBeat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TurnMuteTurns</t>
+          <t>TurnOffBeatScale</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>MUTE : turns without skills</t>
+          <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
@@ -9756,158 +9796,173 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TurnGuardKeep</t>
+          <t>TurnDissonanceMost</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>GUARD : the share of a hit that gets through</t>
+          <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TurnCounterScale</t>
+          <t>TurnCrescendoStep</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>x the target's attack damage</t>
+          <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TurnCadenzaCounter</t>
+          <t>TurnCrescendoMost</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TurnCadenzaEvery</t>
+          <t>TurnMuteTurns</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TurnCadenzaPower</t>
+          <t>TurnGuardKeep</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TurnHoldBase</t>
+          <t>TurnCounterScale</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TurnHoldGain</t>
+          <t>TurnCadenzaCounter</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TurnRollPerfect</t>
+          <t>TurnCadenzaEvery</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TurnRollGood</t>
+          <t>TurnCadenzaPower</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -9919,12 +9974,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MaestroTurnRollPerfect</t>
+          <t>TurnHoldBase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -9936,95 +9991,80 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MaestroTurnRollGood</t>
+          <t>TurnHoldGain</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TurnSignatureNeed</t>
+          <t>TurnRollPerfect</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TurnBeethovenMost</t>
+          <t>TurnRollGood</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TurnBoltDamage</t>
+          <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TurnMozartRun</t>
+          <t>MaestroTurnRollGood</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -10036,105 +10076,100 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TurnFeatherPerStroke</t>
+          <t>TurnSignatureNeed</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TurnPaganiniLife</t>
+          <t>TurnBeethovenMost</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
+          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TurnCapricePrice</t>
+          <t>TurnBoltDamage</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1)</t>
+          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TurnCapricePerStroke</t>
+          <t>TurnMozartRun</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
+          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TurnLullyWindow</t>
+          <t>TurnFeatherPerStroke</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
+          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
@@ -10146,17 +10181,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TurnSunHeal</t>
+          <t>TurnFugueScale</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>THE SUN : life back for every musician at full strength</t>
+          <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
         </is>
       </c>
     </row>
@@ -10168,17 +10203,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TurnFannyScale</t>
+          <t>TurnPaganiniLife</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
         </is>
       </c>
     </row>
@@ -10190,17 +10225,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TurnFelixHeal</t>
+          <t>TurnCapricePrice</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FELIX's voice heals this much more</t>
+          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
         </is>
       </c>
     </row>
@@ -10212,17 +10247,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TurnFelixCrescendo</t>
+          <t>TurnCapricePerStroke</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>and gives this much more CRESCENDO</t>
+          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10269,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TurnDuetDamage</t>
+          <t>TurnLullyWindow</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TWO VOICES : damage to every enemy at full strength</t>
+          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
         </is>
       </c>
     </row>
@@ -10256,51 +10291,51 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TurnDuetHeal</t>
+          <t>TurnSunHeal</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>and life back for every musician</t>
+          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TurnCountsWindow</t>
+          <t>TurnFannyScale</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
+          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TurnQuietScale</t>
+          <t>TurnFelixHeal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10310,73 +10345,73 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
+          <t>FELIX's voice heals this much more</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TurnMomentumMost</t>
+          <t>TurnFelixCrescendo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
+          <t>and gives this much more CRESCENDO</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnDuetDamage</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, THE UNSIGNED 46 percent)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnDuetHeal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>and life back for every musician</t>
         </is>
       </c>
     </row>
@@ -10388,17 +10423,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnCountsWindow</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
+          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
         </is>
       </c>
     </row>
@@ -10410,17 +10445,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TurnFourBarsEvery</t>
+          <t>TurnQuietScale</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
+          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
         </is>
       </c>
     </row>
@@ -10432,17 +10467,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TurnFourBarsScale</t>
+          <t>TurnMomentumMost</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>hits this much harder</t>
+          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
         </is>
       </c>
     </row>
@@ -10454,17 +10489,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TurnLateBonus</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -10476,117 +10511,117 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>TurnFourBarsEvery</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>TurnFourBarsScale</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>TurnLateBonus</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10596,7 +10631,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
@@ -10608,17 +10643,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
@@ -10630,17 +10665,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
@@ -10652,17 +10687,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -10674,127 +10709,127 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ArchiveStagePerLevel</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>ArchiveStagePerLevel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
         </is>
       </c>
     </row>
@@ -10806,17 +10841,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -10828,17 +10863,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -10850,17 +10885,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>SFORZANDO : a PERFECT f note</t>
+          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10907,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10882,7 +10917,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -10894,17 +10929,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -10916,17 +10951,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -10938,17 +10973,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -10960,17 +10995,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>SFORZANDO : a PERFECT f note</t>
         </is>
       </c>
     </row>
@@ -10982,17 +11017,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -11004,17 +11039,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -11026,215 +11061,215 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>ENTRANCE : a called musician's moves in their first bar</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>GREEN ROOM : life back for each musician on the BENCH at the end of a bar</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -11246,17 +11281,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -11268,17 +11303,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -11290,17 +11325,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -11312,17 +11347,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnHoldStill</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>pixels per second the baton may drift and still count as still</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -11334,15 +11369,213 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>TurnHitStop</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TurnStrikeTime</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TurnStrikeImpact</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>when in it the hit lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TurnStrikeStop</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>the freeze when it lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TurnHoldStill</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>pixels per second the baton may drift and still count as still</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -11359,7 +11592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="33" min="1" max="1"/>
@@ -11804,6 +12037,219 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ROOM TONE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dp, Up Dp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HOLDS THE ROOM (2)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>While it stands, the other enemies take 30 percent less.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>THE CUE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rmf Lmf, Uf</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ON CUE (2)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>It always strikes the musician who was CALLED in last.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>THE DAMPER</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dmf Dp, Lmf Rmf</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FELT HAND (2)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>While it stands, a CALL costs 1 more BREATH.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STUTTER</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lp, Rp, Up</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TWICE A BAR (2)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>It cuts in twice a bar, after the 1st and the 3rd move, one note each time.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>THE ROUND</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Df Dmf Df, Lmf Rmf Lf Rf</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FIRST IN LINE (1)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>It always strikes the musician who plays first in the bar.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1470,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
@@ -1508,105 +1508,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 1.8c   LATE  100%  2.9b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  4.9b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 1.8c   LATE  100%  2.9b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  5.0b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.2b   0% 2.0c   ELITE 100%  3.9b   0% 2.0c   BOSS  100%  5.7b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.2b   0% 2.0c   ELITE 100%  3.9b   0% 2.0c   BOSS  100%  5.9b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  3.9b   0% 2.0c   LATE  100%  4.2b   0% 2.0c   ELITE 100%  4.4b   0% 2.0c   BOSS  100%  6.9b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  3.8b   0% 2.0c   LATE  100%  4.2b   0% 2.0c   ELITE 100%  4.4b   0% 2.0c   BOSS  100%  7.0b   1% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.0b   2% 1.5c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.4b   5% 2.0c   BOSS  100%  5.1b  11% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.1b   2% 1.5c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.4b   5% 2.0c   BOSS  100%  5.1b  12% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.3b   8% 2.0c   LATE  100%  3.5b  11% 2.0c   ELITE 100%  4.1b  14% 2.0c   BOSS  100%  6.3b  19% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b   8% 1.9c   LATE  100%  3.6b  11% 2.0c   ELITE 100%  4.2b  14% 2.0c   BOSS  100%  6.2b  20% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.1b  13% 2.0c   LATE  100%  4.8b  15% 2.0c   ELITE 100%  5.2b  19% 2.0c   BOSS   99%  7.7b  31% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.0b  12% 2.0c   LATE  100%  4.8b  15% 2.0c   ELITE 100%  5.1b  19% 2.0c   BOSS  100%  7.7b  29% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.2b   6% 1.4c   LATE  100%  3.1b  11% 2.0c   ELITE 100%  3.7b  12% 1.9c   BOSS  100%  5.6b  24% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.1b   5% 1.4c   LATE  100%  3.2b  11% 2.0c   ELITE 100%  3.7b  12% 1.9c   BOSS  100%  5.6b  25% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.6b  17% 2.0c   LATE  100%  4.1b  25% 2.0c   ELITE 100%  4.7b  28% 2.0c   BOSS   87%  7.4b  50% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.8b  18% 1.9c   LATE  100%  4.2b  23% 2.0c   ELITE 100%  4.8b  28% 2.0c   BOSS   91%  7.3b  51% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.7b  29% 2.0c   LATE  100%  5.7b  39% 2.0c   ELITE  89%  6.5b  55% 2.0c   BOSS   56%  8.4b  75% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.8b  28% 2.0c   LATE   98%  5.7b  40% 2.0c   ELITE  88%  6.5b  56% 2.0c   BOSS   53%  8.2b  78% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  10% 1.3c   LATE  100%  3.6b  23% 1.9c   ELITE 100%  4.2b  26% 1.9c   BOSS   84%  6.8b  53% 2.0c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  10% 1.3c   LATE  100%  3.5b  22% 1.9c   ELITE 100%  4.1b  24% 1.9c   BOSS   87%  7.1b  62% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  4.5b  37% 1.9c   LATE   77%  5.2b  65% 1.9c   ELITE  62%  5.8b  74% 1.9c   BOSS   21%  6.7b  91% 1.8c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  98%  4.4b  39% 1.9c   LATE   78%  5.4b  67% 1.9c   ELITE  67%  5.9b  73% 1.9c   BOSS   13%  6.2b  95% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  56%  5.4b  76% 1.8c   LATE   16%  4.1b  95% 1.6c   ELITE   7%  4.4b  98% 1.6c   BOSS    1%  4.4b  99% 1.6c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  52%  5.3b  80% 1.8c   LATE   17%  4.3b  93% 1.6c   ELITE   6%  4.4b  98% 1.6c   BOSS    1%  3.9b  99% 1.7c   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.4b  15% 1.2c   LATE  100%  4.0b  34% 1.8c   ELITE  98%  4.5b  41% 1.9c   BOSS   47%  6.9b  78% 1.8c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.4b  16% 1.2c   LATE   99%  3.9b  35% 1.7c   ELITE  99%  4.5b  39% 1.9c   BOSS   42%  7.2b  84% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  86%  5.1b  62% 1.9c   LATE   18%  4.4b  94% 1.5c   ELITE   8%  4.6b  97% 1.7c   BOSS    0%  4.5b  99% 1.6c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  90%  5.3b  62% 1.9c   LATE   11%  4.1b  96% 1.5c   ELITE   9%  4.8b  97% 1.8c   BOSS    0%  4.2b  99% 1.7c   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   2%  3.3b  98% 1.4c   LATE    0%  2.1b 100% 1.0c   ELITE   0%  2.4b 100% 1.2c   BOSS    0%  2.3b 100% 1.1c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   4%  3.5b  99% 1.4c   LATE    0%  2.2b 100% 1.0c   ELITE   0%  2.4b 100% 1.2c   BOSS    0%  2.3b 100% 1.2c   </t>
         </is>
       </c>
     </row>
@@ -1614,251 +1614,272 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3), AVERAGE player : WIN PERCENT / BARS</t>
+          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   77%  5.2b</t>
+          <t xml:space="preserve">  HUSH                   80%  5.1b    100%  4.0b    </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               74%  5.1b</t>
+          <t xml:space="preserve">  DEAD AIR               74%  5.1b     99%  4.0b    </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               79%  5.5b</t>
+          <t xml:space="preserve">  THE LULL               81%  5.7b    100%  4.2b    </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 79%  5.1b</t>
+          <t xml:space="preserve">  STATIC                 78%  5.4b    100%  4.0b    </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         72%  6.1b</t>
+          <t xml:space="preserve">  THE MUTE CHOIR         70%  6.1b     99%  4.7b    </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            47%  5.7b</t>
+          <t xml:space="preserve">  WHITE NOISE            40%  5.5b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  3.8b</t>
+          <t xml:space="preserve">  REQUIEM                 0%  4.2b     50%  8.4b    </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     1%  5.2b</t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     2%  5.1b     92%  8.6b    </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.6b</t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.5b     30%  8.1b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              81%  5.5b</t>
+          <t xml:space="preserve">  ROOM TONE              84%  5.4b    100%  4.1b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                87%  5.3b</t>
+          <t xml:space="preserve">  THE CUE                85%  5.3b    100%  4.1b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             68%  5.5b</t>
+          <t xml:space="preserve">  THE DAMPER             64%  5.4b    100%  4.4b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                85%  5.2b</t>
+          <t xml:space="preserve">  STUTTER                85%  5.0b    100%  3.9b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              68%  6.2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
+          <t xml:space="preserve">  THE ROUND              68%  6.3b    100%  4.7b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  3.8b     62%  8.8b    </t>
+        </is>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
+          <t xml:space="preserve">  THE STAFF               0%  4.1b     44%  8.6b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.2b     57%  8.4b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
+          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    50%    0% / 10% / 38%</t>
+          <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    30% / 68% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    80% / 19% / 0%</t>
+          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MAESTRO</t>
+          <t xml:space="preserve">    STRONG    61%    0% / 10% / 27%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    31% / 68% / 0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    79%    0% / 3% / 17%</t>
+          <t xml:space="preserve">    NEWCOMER   0%    88% / 12% / 0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    15% / 72% / 12%</t>
+          <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    94% / 5% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
+          <t xml:space="preserve">    EXPERT    76%    0% / 4% / 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG     0%    15% / 73% / 11%</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
+          <t xml:space="preserve">    AVERAGE    0%    94% / 5% / 0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       58% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE SHADOWLESS      51% / 0%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       51% / 0%</t>
+          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE HEARTLESS       65% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       52% / 0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE KING'S BATON    63% / 0%</t>
+          <t xml:space="preserve">  THE SHADOWLESS      52% / 0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNSIGNED        50% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
+          <t xml:space="preserve">  THE METRONOME       47% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE HEARTLESS       52% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE KING'S BATON    60% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNSIGNED        49% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8647,7 +8668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -9467,565 +9488,590 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TurnPracticeHp</t>
+          <t>TurnByTouchMost</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TurnPracticeSpeed</t>
+          <t>TurnCourtKeep</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TurnPracticePower</t>
+          <t>TurnStaffEvery</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>each note hits this x TurnNoteDamage (4 life)</t>
+          <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TurnNotesMin</t>
+          <t>TurnStaffPower</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELITE and BOSS</t>
+          <t>that one note hits everyone this much harder</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TurnNotesMax</t>
+          <t>TurnThorns</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMin</t>
+          <t>TurnPracticeHp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{ 1, 1, 2 }</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ordinary enemies</t>
+          <t>160</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMax</t>
+          <t>TurnPracticeSpeed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{ 2, 2, 2 }</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TurnNoteDamage</t>
+          <t>TurnPracticePower</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
+          <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PARRY</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TurnParryGoodKeep</t>
+          <t>TurnNotesMin</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>{ 1, 2, 3 }</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TurnBreathMax</t>
+          <t>TurnNotesMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TurnBreathStart</t>
+          <t>TurnSmallNotesMin</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>{ 1, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ordinary enemies</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TurnBreathPerAttack</t>
+          <t>TurnSmallNotesMax</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TurnBreathPerParry</t>
+          <t>TurnNoteDamage</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>for each note parried PERFECT</t>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KNOCKED OUT</t>
+          <t>PARRY</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TurnReviveHp</t>
+          <t>TurnParryGoodKeep</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TurnOffBeatMax</t>
+          <t>TurnBreathMax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TurnParryOffBeat</t>
+          <t>TurnBreathStart</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>each note parried PERFECT</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TurnOffBeatScale</t>
+          <t>TurnBreathPerAttack</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>damage against an enemy off the beat</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TurnDissonanceMost</t>
+          <t>TurnBreathPerParry</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DISSONANCE stacks no higher</t>
+          <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>KNOCKED OUT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TurnCrescendoStep</t>
+          <t>TurnReviveHp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>CRESCENDO : each stack hits this much harder</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TurnCrescendoMost</t>
+          <t>TurnOffBeatMax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TurnMuteTurns</t>
+          <t>TurnParryOffBeat</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MUTE : turns without skills</t>
+          <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TurnGuardKeep</t>
+          <t>TurnOffBeatScale</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GUARD : the share of a hit that gets through</t>
+          <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TurnCounterScale</t>
+          <t>TurnDissonanceMost</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>x the target's attack damage</t>
+          <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TurnCadenzaCounter</t>
+          <t>TurnCrescendoStep</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TurnCadenzaEvery</t>
+          <t>TurnCrescendoMost</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TurnCadenzaPower</t>
+          <t>TurnMuteTurns</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TurnHoldBase</t>
+          <t>TurnGuardKeep</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TurnHoldGain</t>
+          <t>TurnCounterScale</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TurnRollPerfect</t>
+          <t>TurnCadenzaCounter</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TurnRollGood</t>
+          <t>TurnCadenzaEvery</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10037,17 +10083,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MaestroTurnRollPerfect</t>
+          <t>TurnCadenzaPower</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -10059,227 +10105,202 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MaestroTurnRollGood</t>
+          <t>TurnHoldBase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TurnSignatureNeed</t>
+          <t>TurnHoldGain</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TurnBeethovenMost</t>
+          <t>TurnRollPerfect</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TurnBoltDamage</t>
+          <t>TurnRollGood</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TurnMozartRun</t>
+          <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TurnFeatherPerStroke</t>
+          <t>MaestroTurnRollGood</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TurnFugueScale</t>
+          <t>TurnSignatureNeed</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TurnPaganiniLife</t>
+          <t>TurnBeethovenMost</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
+          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TurnCapricePrice</t>
+          <t>TurnBoltDamage</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
+          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TurnCapricePerStroke</t>
+          <t>TurnMozartRun</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
+          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TurnLullyWindow</t>
+          <t>TurnFeatherPerStroke</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
+          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
@@ -10291,17 +10312,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TurnSunHeal</t>
+          <t>TurnFugueScale</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent)</t>
+          <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
         </is>
       </c>
     </row>
@@ -10313,17 +10334,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TurnFannyScale</t>
+          <t>TurnPaganiniLife</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
         </is>
       </c>
     </row>
@@ -10335,17 +10356,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TurnFelixHeal</t>
+          <t>TurnCapricePrice</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FELIX's voice heals this much more</t>
+          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
         </is>
       </c>
     </row>
@@ -10357,17 +10378,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TurnFelixCrescendo</t>
+          <t>TurnCapricePerStroke</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>and gives this much more CRESCENDO</t>
+          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
         </is>
       </c>
     </row>
@@ -10379,17 +10400,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TurnDuetDamage</t>
+          <t>TurnLullyWindow</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, THE UNSIGNED 46 percent)</t>
+          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10422,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TurnDuetHeal</t>
+          <t>TurnSunHeal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -10411,41 +10432,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>and life back for every musician</t>
+          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TurnCountsWindow</t>
+          <t>TurnFannyScale</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
+          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TurnQuietScale</t>
+          <t>TurnFelixHeal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10455,73 +10476,73 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
+          <t>FELIX's voice heals this much more</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TurnMomentumMost</t>
+          <t>TurnFelixCrescendo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
+          <t>and gives this much more CRESCENDO</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnDuetDamage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, THE UNSIGNED 46 percent)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnDuetHeal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>and life back for every musician</t>
         </is>
       </c>
     </row>
@@ -10533,17 +10554,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnCountsWindow</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
+          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
         </is>
       </c>
     </row>
@@ -10555,17 +10576,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TurnFourBarsEvery</t>
+          <t>TurnQuietScale</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
+          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10598,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TurnFourBarsScale</t>
+          <t>TurnMomentumMost</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>hits this much harder</t>
+          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
         </is>
       </c>
     </row>
@@ -10599,17 +10620,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TurnLateBonus</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -10621,117 +10642,117 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>TurnFourBarsEvery</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>TurnFourBarsScale</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>TurnLateBonus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10741,7 +10762,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
@@ -10753,17 +10774,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
@@ -10775,17 +10796,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
@@ -10797,17 +10818,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -10819,127 +10840,127 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ArchiveStagePerLevel</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>ArchiveStagePerLevel</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
         </is>
       </c>
     </row>
@@ -10951,17 +10972,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -10973,17 +10994,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -10995,17 +11016,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SFORZANDO : a PERFECT f note</t>
+          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11038,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11027,7 +11048,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -11039,17 +11060,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -11061,17 +11082,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -11083,17 +11104,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -11105,17 +11126,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>SFORZANDO : a PERFECT f note</t>
         </is>
       </c>
     </row>
@@ -11127,17 +11148,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -11149,17 +11170,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -11171,51 +11192,51 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -11225,161 +11246,161 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ENTRANCE : a called musician's moves in their first bar</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>GREEN ROOM : life back for each musician on the BENCH at the end of a bar</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>ENTRANCE : a called musician's moves in their first bar</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>GREEN ROOM : life back for each musician on the BENCH at the end of a bar</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11412,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -11413,17 +11434,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -11435,17 +11456,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -11457,17 +11478,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -11479,17 +11500,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11522,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
         </is>
       </c>
     </row>
@@ -11523,17 +11544,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -11545,17 +11566,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnHoldStill</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>pixels per second the baton may drift and still count as still</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -11567,15 +11588,125 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TurnHoldStill</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>pixels per second the baton may drift and still count as still</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -11592,7 +11723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="33" min="1" max="1"/>
@@ -12250,6 +12381,133 @@
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>THE DEAF CROWN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Uf Uf Uf Df, Lf Rf Df</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DECREE (1)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Each bar it forbids SKILLS or ATTACKS, and breaking it hurts. It never takes a COUNTER.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>THE STAFF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Df Dmf Df, Dmf Lmf Dmf Rmf</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>THE COURT (1)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>While its court stands it takes half. Every third attack it strikes the floor and hits everyone.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>THE BLIND CANTOR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Df Umf Df Umf, Lmf Rmf Lp Rp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>BY TOUCH (1)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>It strikes the seats in turn, front to back. A note you miss comes back in its next attack.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G5" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : for two turns per stroke that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays 10 percent of their life.</t>
+          <t xml:space="preserve">The 4/4 shape : for two turns per stroke that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays </t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
@@ -1508,378 +1508,385 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0% 1.8c   LATE  100%  2.9b   0% 2.0c   ELITE 100%  3.0b   0% 1.9c   BOSS  100%  5.0b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.0b   0% 2.0c   ELITE 100%  4.0b   0% 2.0c   BOSS  100%  6.9b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.2b   0% 2.0c   ELITE 100%  3.9b   0% 2.0c   BOSS  100%  5.9b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.5b   0% 2.0c   LATE  100%  4.6b   0% 2.0c   ELITE 100%  5.1b   0% 2.0c   BOSS  100%  8.6b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  3.8b   0% 2.0c   LATE  100%  4.2b   0% 2.0c   ELITE 100%  4.4b   0% 2.0c   BOSS  100%  7.0b   1% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.3b   0% 2.0c   LATE  100%  6.5b   0% 2.0c   ELITE 100%  7.0b   0% 2.0c   BOSS  100% 11.5b   0% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.1b   2% 1.5c   LATE  100%  3.0b   5% 2.0c   ELITE 100%  3.4b   5% 2.0c   BOSS  100%  5.1b  12% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  3.0b   3% 2.0c   LATE  100%  3.5b   5% 2.0c   ELITE 100%  4.2b   4% 2.0c   BOSS  100%  7.1b   8% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b   8% 1.9c   LATE  100%  3.6b  11% 2.0c   ELITE 100%  4.2b  14% 2.0c   BOSS  100%  6.2b  20% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.2b   8% 2.0c   LATE  100%  5.2b  11% 2.0c   ELITE 100%  5.7b  13% 2.0c   BOSS  100%  9.2b  19% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.0b  12% 2.0c   LATE  100%  4.8b  15% 2.0c   ELITE 100%  5.1b  19% 2.0c   BOSS  100%  7.7b  29% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.0b  12% 2.0c   LATE  100%  7.0b  15% 2.0c   ELITE 100%  8.0b  21% 2.0c   BOSS   98% 12.5b  31% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.1b   5% 1.4c   LATE  100%  3.2b  11% 2.0c   ELITE 100%  3.7b  12% 1.9c   BOSS  100%  5.6b  25% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  3.1b   6% 2.0c   LATE  100%  4.0b  13% 2.0c   ELITE 100%  4.7b  11% 2.0c   BOSS  100%  7.9b  22% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.8b  18% 1.9c   LATE  100%  4.2b  23% 2.0c   ELITE 100%  4.8b  28% 2.0c   BOSS   91%  7.3b  51% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.8b  16% 2.0c   LATE  100%  6.0b  21% 2.0c   ELITE 100%  6.9b  29% 2.0c   BOSS   85% 10.7b  50% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  4.8b  28% 2.0c   LATE   98%  5.7b  40% 2.0c   ELITE  88%  6.5b  56% 2.0c   BOSS   53%  8.2b  78% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.2b  26% 2.0c   LATE   99%  8.6b  35% 2.0c   ELITE  80%  9.7b  61% 2.0c   BOSS   32% 11.9b  86% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.3b  10% 1.3c   LATE  100%  3.5b  22% 1.9c   ELITE 100%  4.1b  24% 1.9c   BOSS   87%  7.1b  62% 2.0c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.5b  11% 2.0c   LATE  100%  5.2b  24% 2.0c   ELITE 100%  6.0b  26% 2.0c   BOSS   74% 10.4b  63% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  98%  4.4b  39% 1.9c   LATE   78%  5.4b  67% 1.9c   ELITE  67%  5.9b  73% 1.9c   BOSS   13%  6.2b  95% 1.9c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  96%  6.8b  43% 2.0c   LATE   68%  8.0b  71% 2.0c   ELITE  37%  8.4b  89% 2.0c   BOSS    7%  8.0b  96% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  52%  5.3b  80% 1.8c   LATE   17%  4.3b  93% 1.6c   ELITE   6%  4.4b  98% 1.6c   BOSS    1%  3.9b  99% 1.7c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  38%  8.4b  86% 2.0c   LATE    3%  5.4b  98% 1.8c   ELITE   1%  5.4b  99% 1.9c   BOSS    0%  4.8b 100% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.4b  16% 1.2c   LATE   99%  3.9b  35% 1.7c   ELITE  99%  4.5b  39% 1.9c   BOSS   42%  7.2b  84% 1.9c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.0b  18% 2.0c   LATE   98%  6.9b  46% 2.0c   ELITE  94%  8.1b  53% 2.0c   BOSS   19% 10.0b  92% 2.0c   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  90%  5.3b  62% 1.9c   LATE   11%  4.1b  96% 1.5c   ELITE   9%  4.8b  97% 1.8c   BOSS    0%  4.2b  99% 1.7c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  54%  8.1b  79% 2.0c   LATE    1%  5.2b  99% 1.8c   ELITE   1%  5.6b  99% 1.9c   BOSS    0%  4.6b 100% 1.9c   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   4%  3.5b  99% 1.4c   LATE    0%  2.2b 100% 1.0c   ELITE   0%  2.4b 100% 1.2c   BOSS    0%  2.3b 100% 1.2c   </t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   0%  4.2b 100% 1.8c   LATE    0%  2.8b 100% 1.5c   ELITE   0%  3.1b 100% 1.8c   BOSS    0%  2.9b 100% 1.6c   </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 36%  SKILLS 63%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   80%  5.1b    100%  4.0b    </t>
+          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               74%  5.1b     99%  4.0b    </t>
+          <t xml:space="preserve">  HUSH                   61%  7.7b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               81%  5.7b    100%  4.2b    </t>
+          <t xml:space="preserve">  DEAD AIR               56%  7.7b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 78%  5.4b    100%  4.0b    </t>
+          <t xml:space="preserve">  THE LULL               74%  8.8b    100%  6.3b    </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         70%  6.1b     99%  4.7b    </t>
+          <t xml:space="preserve">  STATIC                 67%  8.0b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            40%  5.5b    100%  5.0b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         50%  8.7b    100%  6.7b    </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  4.2b     50%  8.4b    </t>
+          <t xml:space="preserve">  WHITE NOISE            21%  7.6b     99%  7.2b    </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     2%  5.1b     92%  8.6b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  4.6b     25%  12.0b    </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.5b     30%  8.1b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  6.5b     81%  13.5b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              84%  5.4b    100%  4.1b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.1b      6%  10.3b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                85%  5.3b    100%  4.1b    </t>
+          <t xml:space="preserve">  ROOM TONE              73%  8.2b    100%  6.2b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             64%  5.4b    100%  4.4b    </t>
+          <t xml:space="preserve">  THE CUE                74%  8.2b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                85%  5.0b    100%  3.9b    </t>
+          <t xml:space="preserve">  THE DAMPER             51%  7.8b    100%  6.4b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              68%  6.3b    100%  4.7b    </t>
+          <t xml:space="preserve">  STUTTER                75%  7.8b    100%  5.6b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  3.8b     62%  8.8b    </t>
+          <t xml:space="preserve">  THE ROUND              43%  8.9b     99%  6.9b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  4.1b     44%  8.6b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  4.4b     20%  12.9b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.2b     57%  8.4b    </t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  THE STAFF               0%  4.4b     28%  11.6b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.5b     29%  11.3b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NORMAL</t>
+          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    61%    0% / 10% / 27%</t>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    31% / 68% / 0%</t>
+          <t xml:space="preserve">    STRONG    55%    2% / 5% / 37%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    88% / 12% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    57% / 43% / 0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MAESTRO</t>
+          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    76%    0% / 4% / 20%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    15% / 73% / 11%</t>
+          <t xml:space="preserve">    EXPERT    73%    1% / 2% / 23%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    94% / 5% / 0%</t>
+          <t xml:space="preserve">    STRONG     0%    28% / 64% / 7%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t xml:space="preserve">    AVERAGE    0%    99% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
-        </is>
-      </c>
-    </row>
+    <row r="55"/>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       52% / 0%</t>
+          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE SHADOWLESS      52% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       62% / 0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       47% / 0%</t>
+          <t xml:space="preserve">  THE SHADOWLESS      53% / 0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE HEARTLESS       52% / 0%</t>
+          <t xml:space="preserve">  THE METRONOME       52% / 0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE KING'S BATON    60% / 0%</t>
+          <t xml:space="preserve">  THE HEARTLESS       62% / 0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNSIGNED        49% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
+          <t xml:space="preserve">  THE KING'S BATON    55% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNSIGNED        54% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8936,12 +8943,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATTACK : no swipe, it always hits at this</t>
+          <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8992,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>musicians on the field when a fight starts (FULL STAGE in the ARCHIVE adds 1)</t>
+          <t>seats on stage a run starts with (FULL STAGE in the ARCHIVE adds 1, EXTRA SEAT in the shop 1 each).</t>
         </is>
       </c>
     </row>
@@ -9222,7 +9229,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -9266,7 +9273,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{ 1, 1.3, 1.6 }</t>
+          <t>{ 1.6, 2.1, 2.7 }</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9620,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
         </is>
       </c>
     </row>
@@ -9742,12 +9759,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent)</t>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9832,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
         </is>
       </c>
     </row>
@@ -10339,12 +10361,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of</t>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now)</t>
         </is>
       </c>
     </row>
@@ -10427,12 +10449,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent)</t>
+          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent. Step 15 : 8 -&gt; 6)</t>
         </is>
       </c>
     </row>
@@ -11987,7 +12009,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A note that gets through takes the target's skills away for a turn.</t>
+          <t>A note you miss takes the target's skills away for a turn.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -946,7 +946,7 @@
     <row r="12" ht="15" customHeight="1" s="33">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>Seats on Stage at Start</t>
+          <t>Band Size (picked at the start)</t>
         </is>
       </c>
       <c r="B12" s="36" t="n">
@@ -954,70 +954,78 @@
       </c>
       <c r="C12" s="35" t="inlineStr">
         <is>
-          <t>RunState.Seats</t>
+          <t>BandSize</t>
         </is>
       </c>
       <c r="D12" s="35" t="inlineStr">
         <is>
-          <t>ซื้อเพิ่มที่ร้านได้ (สูงสุด 9 ที่)</t>
+          <t>ต้นรันเลือก 3 จาก 5 คน ทุกคนลงทุกไฟต์ ไม่มีม้านั่ง (29 ต.ค.)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="33">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>Bench Size</t>
+          <t>Weapon Tier Power</t>
         </is>
       </c>
       <c r="B13" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="35" t="inlineStr">
         <is>
-          <t>BenchSize</t>
+          <t>WeaponTierPower</t>
         </is>
       </c>
       <c r="D13" s="35" t="inlineStr">
         <is>
-          <t>นักดนตรีที่นั่งพักได้ (ไม่ขึ้นเวที)</t>
+          <t>อาวุธขั้นละ +2 พลัง ขั้น I II III (29 ต.ค.)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="33">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>Recruits at First Floor</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n">
-        <v>3</v>
+          <t>Band Life (strings / winds / percussion)</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>45 / 39 / 54</t>
+        </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
         <is>
-          <t>FirstFloorRecruits</t>
+          <t>TurnHp</t>
         </is>
       </c>
       <c r="D14" s="35" t="inlineStr">
         <is>
-          <t>คนที่ได้ตอนเปิดชั้น 1</t>
+          <t>x1.5 ตอนเอา CALL ออก (29 ต.ค.)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="33">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>Recruits at Later Floors</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="n">
-        <v>1</v>
+          <t>Rank Shards (S / A / B / C)</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>2 / 1.5 / 1.25 / 1</t>
+        </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>LaterFloorRecruits</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n"/>
+          <t>RankShards</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>เงินจากไฟต์คูณตามอันดับ (29 ต.ค.)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="33">
       <c r="A16" s="35" t="inlineStr">
@@ -1455,7 +1463,7 @@
       </c>
       <c r="G7" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : FANNY strikes every enemy while FELIX heals every musician.</t>
+          <t>The 4/4 shape : FANNY strikes every enemy while ??? heals every musician.</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
@@ -1501,119 +1509,119 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FIGHTS at full life (4 musicians, 2 on the field) : WIN PERCENT  /  BARS  /  LIFE LOST PERCENT  /  CALLS</t>
+          <t>FIGHTS at full life (the band of three) : WIN PERCENT  /  BARS  /  LIFE LOST PERCENT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  3.0b   0% 2.0c   LATE  100%  3.0b   0% 2.0c   ELITE 100%  4.0b   0% 2.0c   BOSS  100%  6.9b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.8b   0%   BOSS  100%  7.0b   0%   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.5b   0% 2.0c   LATE  100%  4.6b   0% 2.0c   ELITE 100%  5.1b   0% 2.0c   BOSS  100%  8.6b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.6b   0%   LATE  100%  4.2b   0%   ELITE 100%  5.3b   0%   BOSS  100%  9.6b   0%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.3b   0% 2.0c   LATE  100%  6.5b   0% 2.0c   ELITE 100%  7.0b   0% 2.0c   BOSS  100% 11.5b   0% 2.0c   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.5b   0%   LATE  100%  6.6b   0%   ELITE 100%  7.8b   0%   BOSS  100% 13.0b   0%   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  3.0b   3% 2.0c   LATE  100%  3.5b   5% 2.0c   ELITE 100%  4.2b   4% 2.0c   BOSS  100%  7.1b   8% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.2b   1%   LATE  100%  3.2b   4%   ELITE 100%  4.1b   4%   BOSS  100%  7.6b  11%   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.2b   8% 2.0c   LATE  100%  5.2b  11% 2.0c   ELITE 100%  5.7b  13% 2.0c   BOSS  100%  9.2b  19% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.8b   6%   LATE  100%  5.2b  10%   ELITE 100%  5.9b  13%   BOSS  100% 10.5b  22%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.0b  12% 2.0c   LATE  100%  7.0b  15% 2.0c   ELITE 100%  8.0b  21% 2.0c   BOSS   98% 12.5b  31% 2.0c   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.2b  13%   LATE  100%  7.3b  16%   ELITE 100%  8.8b  21%   BOSS   99% 14.7b  33%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  3.1b   6% 2.0c   LATE  100%  4.0b  13% 2.0c   ELITE 100%  4.7b  11% 2.0c   BOSS  100%  7.9b  22% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.4b   4%   LATE  100%  3.7b  10%   ELITE 100%  4.5b  11%   BOSS  100%  8.6b  22%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.8b  16% 2.0c   LATE  100%  6.0b  21% 2.0c   ELITE 100%  6.9b  29% 2.0c   BOSS   85% 10.7b  50% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.5b  15%   LATE  100%  6.3b  23%   ELITE 100%  7.3b  29%   BOSS   85% 12.5b  55%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.2b  26% 2.0c   LATE   99%  8.6b  35% 2.0c   ELITE  80%  9.7b  61% 2.0c   BOSS   32% 11.9b  86% 2.0c   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.5b  26%   LATE  100%  9.3b  31%   ELITE  84% 11.6b  58%   BOSS   39% 14.3b  82%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.5b  11% 2.0c   LATE  100%  5.2b  24% 2.0c   ELITE 100%  6.0b  26% 2.0c   BOSS   74% 10.4b  63% 2.0c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.0b  10%   LATE  100%  5.1b  25%   ELITE 100%  6.2b  27%   BOSS   69% 11.9b  67%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  96%  6.8b  43% 2.0c   LATE   68%  8.0b  71% 2.0c   ELITE  37%  8.4b  89% 2.0c   BOSS    7%  8.0b  96% 2.0c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.4b  38%   LATE   79%  8.9b  62%   ELITE  38%  9.8b  87%   BOSS    4%  9.0b  98%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  38%  8.4b  86% 2.0c   LATE    3%  5.4b  98% 1.8c   ELITE   1%  5.4b  99% 1.9c   BOSS    0%  4.8b 100% 1.9c   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  51%  9.3b  80%   LATE   12%  7.6b  96%   ELITE   0%  6.0b 100%   BOSS    0%  5.2b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.0b  18% 2.0c   LATE   98%  6.9b  46% 2.0c   ELITE  94%  8.1b  53% 2.0c   BOSS   19% 10.0b  92% 2.0c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  3.7b  17%   LATE   98%  6.8b  44%   ELITE  90%  8.8b  59%   BOSS   17% 10.8b  92%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  54%  8.1b  79% 2.0c   LATE    1%  5.2b  99% 1.8c   ELITE   1%  5.6b  99% 1.9c   BOSS    0%  4.6b 100% 1.9c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  67%  8.8b  75%   LATE    4%  6.2b  99%   ELITE   0%  6.0b  99%   BOSS    0%  5.1b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   0%  4.2b 100% 1.8c   LATE    0%  2.8b 100% 1.5c   ELITE   0%  3.1b 100% 1.8c   BOSS    0%  2.9b 100% 1.6c   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.0b  99%   LATE    0%  3.5b 100%   ELITE   0%  3.5b 100%   BOSS    0%  3.3b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 36%  SKILLS 63%</t>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 31%  SKILLS 68%</t>
         </is>
       </c>
     </row>
@@ -1621,272 +1629,294 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
+          <t>RANKS of the won fights above : S / A / B / C PERCENT  /  SHARDS SCALE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   61%  7.7b    100%  6.0b    </t>
+          <t xml:space="preserve">  FLAWLESS 100 /   0 /   0 /   0   x2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               56%  7.7b    100%  6.0b    </t>
+          <t xml:space="preserve">  EXPERT    43 /  50 /   6 /   0   x1.70</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               74%  8.8b    100%  6.3b    </t>
+          <t xml:space="preserve">  STRONG     6 /  36 /  49 /   7   x1.37</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 67%  8.0b    100%  5.9b    </t>
+          <t xml:space="preserve">  AVERAGE    0 /   6 /  43 /  49   x1.15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         50%  8.7b    100%  6.7b    </t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHITE NOISE            21%  7.6b     99%  7.2b    </t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  NEWCOMER   0 /   1 /  18 /  80   x1.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  4.6b     25%  12.0b    </t>
+          <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     0%  6.5b     81%  13.5b    </t>
+          <t xml:space="preserve">  HUSH                   78%  8.5b    100%  6.1b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.1b      6%  10.3b    </t>
+          <t xml:space="preserve">  DEAD AIR               76%  8.7b    100%  6.2b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              73%  8.2b    100%  6.2b    </t>
+          <t xml:space="preserve">  THE LULL               87%  10.0b    100%  6.5b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                74%  8.2b    100%  6.0b    </t>
+          <t xml:space="preserve">  STATIC                 84%  8.7b    100%  6.1b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             51%  7.8b    100%  6.4b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         52%  10.0b    100%  7.1b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                75%  7.8b    100%  5.6b    </t>
+          <t xml:space="preserve">  WHITE NOISE            33%  8.7b    100%  7.2b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              43%  8.9b     99%  6.9b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  4.9b     20%  13.7b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  4.4b     20%  12.9b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  7.8b     85%  16.3b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  4.4b     28%  11.6b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.5b      5%  11.4b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.5b     29%  11.3b    </t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+          <t xml:space="preserve">  ROOM TONE              83%  9.1b    100%  6.2b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE CUE                86%  9.2b    100%  6.3b    </t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
+          <t xml:space="preserve">  THE DAMPER             75%  8.7b    100%  6.1b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NORMAL</t>
+          <t xml:space="preserve">  STUTTER                87%  8.3b    100%  5.8b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  THE ROUND              30%  10.6b    100%  7.5b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.1b     15%  15.5b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    55%    2% / 5% / 37%</t>
+          <t xml:space="preserve">  THE STAFF               0%  5.4b     42%  15.3b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    57% / 43% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.4b     34%  13.5b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MAESTRO</t>
+          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    73%    1% / 2% / 23%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    28% / 64% / 7%</t>
+          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    99% / 0% / 0%</t>
+          <t xml:space="preserve">    STRONG    46%    0% / 8% / 45%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
+          <t xml:space="preserve">    AVERAGE    0%    35% / 64% / 1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
+          <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       62% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE SHADOWLESS      53% / 0%</t>
+          <t xml:space="preserve">    EXPERT    71%    0% / 4% / 24%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       52% / 0%</t>
+          <t xml:space="preserve">    STRONG     0%    8% / 67% / 24%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE HEARTLESS       62% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    87% / 12% / 0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE KING'S BATON    55% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE UNSIGNED        54% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
+          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNHEARING       46% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  45% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE METRONOME       50% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7860,18 +7890,22 @@
     <row r="12" ht="15" customHeight="1" s="33">
       <c r="A12" s="48" t="inlineStr">
         <is>
-          <t>Elite drops a musician</t>
+          <t>Normal fight motif (turn battle)</t>
         </is>
       </c>
       <c r="B12" s="60" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C12" s="50" t="inlineStr">
         <is>
-          <t>EliteRecruitChance</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="n"/>
+          <t>MotifChanceNormal</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>ไฟต์ธรรมดาได้แค่เงิน (29 ต.ค.) ELITE กับ BOSS ยังให้เลือก</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1" s="33">
       <c r="A14" s="40" t="inlineStr">
@@ -7988,34 +8022,44 @@
     <row r="22" ht="15" customHeight="1" s="33">
       <c r="A22" s="45" t="inlineStr">
         <is>
-          <t>Extra seat : first price</t>
-        </is>
-      </c>
-      <c r="B22" s="46" t="n">
-        <v>55</v>
+          <t>Shop weapon tier I / II / III</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>50 / 70 / 95</t>
+        </is>
       </c>
       <c r="C22" s="47" t="inlineStr">
         <is>
-          <t>SeatPriceBase</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="n"/>
+          <t>ShopWeaponPrice</t>
+        </is>
+      </c>
+      <c r="D22" s="47" t="inlineStr">
+        <is>
+          <t>อาวุธคนหนึ่งขึ้น 1 ขั้น (29 ต.ค.)</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="33">
       <c r="A23" s="48" t="inlineStr">
         <is>
-          <t>Extra seat : each next adds</t>
+          <t>Shop SECTIONAL (every weapon +1 tier)</t>
         </is>
       </c>
       <c r="B23" s="49" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>SeatPriceStep</t>
-        </is>
-      </c>
-      <c r="D23" s="50" t="n"/>
+          <t>ShopSectionalPrice</t>
+        </is>
+      </c>
+      <c r="D23" s="50" t="inlineStr">
+        <is>
+          <t>สุ่มแทน TUNING 25% (ShopSectionalChance)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="33">
       <c r="A24" s="45" t="inlineStr">
@@ -8054,20 +8098,22 @@
     <row r="26" ht="15" customHeight="1" s="33">
       <c r="A26" s="45" t="inlineStr">
         <is>
-          <t>Seats buyable per floor</t>
-        </is>
-      </c>
-      <c r="B26" s="46" t="n">
-        <v>2</v>
+          <t>Shop REROLL : first / each next adds</t>
+        </is>
+      </c>
+      <c r="B26" s="46" t="inlineStr">
+        <is>
+          <t>10 / 5</t>
+        </is>
       </c>
       <c r="C26" s="47" t="inlineStr">
         <is>
-          <t>SeatsPerFloor</t>
+          <t>ShopRerollBase / ShopRerollStep</t>
         </is>
       </c>
       <c r="D26" s="47" t="inlineStr">
         <is>
-          <t>สูงสุด 9 ที่บนเวที</t>
+          <t>แพงขึ้นทุกครั้งในการเข้าร้านครั้งเดียว</t>
         </is>
       </c>
     </row>
@@ -8103,27 +8149,29 @@
       </c>
       <c r="D28" s="47" t="inlineStr">
         <is>
-          <t>คืนลม 40% ของสูงสุด</t>
+          <t>คืนเลือด 40% ของสูงสุด</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="33">
       <c r="A29" s="48" t="inlineStr">
         <is>
-          <t>Hire a musician</t>
-        </is>
-      </c>
-      <c r="B29" s="49" t="n">
-        <v>80</v>
+          <t>Luthier / treasure</t>
+        </is>
+      </c>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>HirePrice</t>
+          <t>RunFlow</t>
         </is>
       </c>
       <c r="D29" s="50" t="inlineStr">
         <is>
-          <t>คนจากยุคนี้</t>
+          <t>LUTHIER อาวุธขึ้น 1 ขั้น TREASURE ได้ MOTIF 1 ใบ (29 ต.ค.)</t>
         </is>
       </c>
     </row>
@@ -8202,7 +8250,7 @@
     <row r="35" ht="15" customHeight="1" s="33">
       <c r="A35" s="45" t="inlineStr">
         <is>
-          <t>REHEARSE : +1 power, times per musician</t>
+          <t>REHEARSE : +1 weapon tier, top tier</t>
         </is>
       </c>
       <c r="B35" s="46" t="n">
@@ -8213,7 +8261,11 @@
           <t>RehearseMax</t>
         </is>
       </c>
-      <c r="D35" s="47" t="n"/>
+      <c r="D35" s="47" t="inlineStr">
+        <is>
+          <t>I II III</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="21" customHeight="1" s="33">
       <c r="A37" s="40" t="inlineStr">
@@ -8675,7 +8727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -8770,7 +8822,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{ 30, 26, 36 }</t>
+          <t>{ 45, 39, 54 }</t>
         </is>
       </c>
     </row>
@@ -8938,17 +8990,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TurnAttackScale</t>
+          <t>BandSize</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
+          <t>the musicians a run picks at its start, every one of them plays every fight</t>
         </is>
       </c>
     </row>
@@ -8960,17 +9012,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TurnAttackOffBeat</t>
+          <t>TurnAttackScale</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATTACK : the OFF-BEAT it adds</t>
+          <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
         </is>
       </c>
     </row>
@@ -8982,17 +9034,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TurnStartBand</t>
+          <t>TurnAttackOffBeat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>seats on stage a run starts with (FULL STAGE in the ARCHIVE adds 1, EXTRA SEAT in the shop 1 each).</t>
+          <t>ATTACK : the OFF-BEAT it adds</t>
         </is>
       </c>
     </row>
@@ -9004,17 +9056,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TurnFieldMost</t>
+          <t>TurnCutInSpeed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>musicians on the field at most, the called ones too</t>
+          <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
         </is>
       </c>
     </row>
@@ -9026,105 +9078,105 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TurnCallCost</t>
+          <t>TurnCutInAfter</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CALL : BREATH to bring one in from the BENCH, one per bar (NORMAL)</t>
+          <t>right after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ONE BAR</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MaestroTurnCallCost</t>
+          <t>TurnPackEarly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>{ 1, 2, 3 }</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>an ENCOUNTER in the first half of the floor</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ONE BAR</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TurnCallCostStep</t>
+          <t>TurnPackLate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>the second call of a fight and every one after costs this much more</t>
+          <t>in the second half</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ONE BAR</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TurnCutInSpeed</t>
+          <t>TurnEliteEscort</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>{ 0, 1, 2 }</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
+          <t>ordinary enemies that come with an ELITE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ONE BAR</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TurnCutInAfter</t>
+          <t>TurnBossEscort</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>{ 0, 1, 2 }</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>right after this many of the band's moves</t>
+          <t>and with the BOSS</t>
         </is>
       </c>
     </row>
@@ -9136,17 +9188,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TurnPackEarly</t>
+          <t>MaestroTurnDamage</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>an ENCOUNTER in the first half of the floor</t>
+          <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
         </is>
       </c>
     </row>
@@ -9158,144 +9210,144 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TurnPackLate</t>
+          <t>TurnShardsPerEscort</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>in the second half</t>
+          <t>shards for each enemy beyond the first</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>Floor Scale</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TurnEliteEscort</t>
+          <t>TurnFloorLife</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{ 0, 1, 2 }</t>
+          <t>{ 1.6, 2.1, 2.7 }</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ordinary enemies that come with an ELITE</t>
+          <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>Floor Scale</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TurnBossEscort</t>
+          <t>TurnFloorDamage</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{ 0, 1, 2 }</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>and with the BOSS</t>
+          <t>{ 1, 1.2, 1.4 }</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MaestroTurnDamage</t>
+          <t>TurnFillsGapsScale</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
+          <t>DEAD AIR : a missed note</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TurnShardsPerEscort</t>
+          <t>TurnLullHeal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>shards for each enemy beyond the first</t>
+          <t>THE LULL : life back on its humming turn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Floor Scale</t>
+          <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TurnFloorLife</t>
+          <t>TurnLullEvery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{ 1.6, 2.1, 2.7 }</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
+          <t>every this many turns</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Floor Scale</t>
+          <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TurnFloorDamage</t>
+          <t>TurnFastGap</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{ 1, 1.2, 1.4 }</t>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>REQUIEM : the gap between notes below half life</t>
         </is>
       </c>
     </row>
@@ -9307,193 +9359,193 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TurnFillsGapsScale</t>
+          <t>TurnBargainSteal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEAD AIR : a missed note</t>
+          <t>THE DEVIL'S STRING : breath taken by each attack</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enemy Traits in the turn battle</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TurnLullHeal</t>
+          <t>TurnRoomToneKeep</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>THE LULL : life back on its humming turn</t>
+          <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Enemy Traits in the turn battle</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TurnLullEvery</t>
+          <t>TurnFeltHandBreath</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>every this many turns</t>
+          <t>THE DAMPER (FELT HAND, 29 Oct) : an ATTACK gives this much less BREATH while it stands (until CALL went</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enemy Traits in the turn battle</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TurnFastGap</t>
+          <t>TurnTwiceFirst</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>REQUIEM : the gap between notes below half life</t>
+          <t>STUTTER : cuts in after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Enemy Traits in the turn battle</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TurnBargainSteal</t>
+          <t>TurnTwiceSecond</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>THE DEVIL'S STRING : breath taken by each attack</t>
+          <t>and again after this many</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ONE BAR enemies</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TurnRoomToneKeep</t>
+          <t>TurnByTouchMost</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
+          <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ONE BAR enemies</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TurnFeltHandCall</t>
+          <t>TurnCourtKeep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>THE DAMPER : a CALL costs this much more while it stands (2 left the sim's STRONG player at 23 percent against it)</t>
+          <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ONE BAR enemies</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TurnTwiceFirst</t>
+          <t>TurnStaffEvery</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>STUTTER : cuts in after this many of the band's moves</t>
+          <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ONE BAR enemies</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TurnTwiceSecond</t>
+          <t>TurnStaffPower</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>and again after this many</t>
+          <t>that one note hits everyone this much harder</t>
         </is>
       </c>
     </row>
@@ -9505,166 +9557,156 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TurnByTouchMost</t>
+          <t>TurnThorns</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
+          <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bosses of step 14</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TurnCourtKeep</t>
+          <t>TurnPracticeHp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
+          <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bosses of step 14</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TurnStaffEvery</t>
+          <t>TurnPracticeSpeed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bosses of step 14</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TurnStaffPower</t>
+          <t>TurnPracticePower</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>that one note hits everyone this much harder</t>
+          <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bosses of step 14</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TurnThorns</t>
+          <t>TurnNotesMin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>{ 1, 2, 3 }</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
+          <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TurnPracticeHp</t>
+          <t>TurnNotesMax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TurnPracticeSpeed</t>
+          <t>TurnSmallNotesMin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>{ 1, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ordinary enemies</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TurnPracticePower</t>
+          <t>TurnSmallNotesMax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>each note hits this x TurnNoteDamage (4 life)</t>
+          <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
@@ -9676,268 +9718,273 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TurnNotesMin</t>
+          <t>TurnNoteDamage</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ELITE and BOSS</t>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PARRY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TurnNotesMax</t>
+          <t>TurnParryGoodKeep</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMin</t>
+          <t>TurnBreathMax</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{ 1, 1, 2 }</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ordinary enemies</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMax</t>
+          <t>TurnBreathStart</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{ 2, 2, 2 }</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TurnNoteDamage</t>
+          <t>TurnBreathPerAttack</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
+          <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PARRY</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TurnParryGoodKeep</t>
+          <t>TurnBreathPerParry</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>KNOCKED OUT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TurnBreathMax</t>
+          <t>TurnReviveHp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TurnBreathStart</t>
+          <t>TurnOffBeatMax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TurnBreathPerAttack</t>
+          <t>TurnParryOffBeat</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
+          <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TurnBreathPerParry</t>
+          <t>TurnOffBeatScale</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>for each note parried PERFECT</t>
+          <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KNOCKED OUT</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TurnReviveHp</t>
+          <t>TurnDissonanceMost</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TurnOffBeatMax</t>
+          <t>TurnCrescendoStep</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TurnParryOffBeat</t>
+          <t>TurnCrescendoMost</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>each note parried PERFECT</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TurnOffBeatScale</t>
+          <t>TurnMuteTurns</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>damage against an enemy off the beat</t>
+          <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
@@ -9949,173 +9996,158 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TurnDissonanceMost</t>
+          <t>TurnGuardKeep</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DISSONANCE stacks no higher</t>
+          <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TurnCrescendoStep</t>
+          <t>TurnCounterScale</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>CRESCENDO : each stack hits this much harder</t>
+          <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TurnCrescendoMost</t>
+          <t>TurnCadenzaCounter</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TurnMuteTurns</t>
+          <t>TurnCadenzaEvery</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>MUTE : turns without skills</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TurnGuardKeep</t>
+          <t>TurnCadenzaPower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>GUARD : the share of a hit that gets through</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TurnCounterScale</t>
+          <t>TurnHoldBase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>x the target's attack damage</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TurnCadenzaCounter</t>
+          <t>TurnHoldGain</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TurnCadenzaEvery</t>
+          <t>TurnRollPerfect</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TurnCadenzaPower</t>
+          <t>TurnRollGood</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10127,12 +10159,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TurnHoldBase</t>
+          <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -10144,185 +10176,200 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TurnHoldGain</t>
+          <t>MaestroTurnRollGood</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TurnRollPerfect</t>
+          <t>TurnSignatureNeed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TurnRollGood</t>
+          <t>PlaytestSignatureNeed</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MaestroTurnRollPerfect</t>
+          <t>TurnBeethovenMost</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MaestroTurnRollGood</t>
+          <t>TurnBoltDamage</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TurnSignatureNeed</t>
+          <t>TurnMozartRun</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TurnBeethovenMost</t>
+          <t>TurnFeatherPerStroke</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
+          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TurnBoltDamage</t>
+          <t>TurnFugueScale</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
+          <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TurnMozartRun</t>
+          <t>TurnPaganiniLife</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TurnFeatherPerStroke</t>
+          <t>TurnCapricePrice</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
+          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
         </is>
       </c>
     </row>
@@ -10334,17 +10381,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TurnFugueScale</t>
+          <t>TurnCapricePerStroke</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
+          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
         </is>
       </c>
     </row>
@@ -10356,17 +10403,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TurnPaganiniLife</t>
+          <t>TurnLullyWindow</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now)</t>
+          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
         </is>
       </c>
     </row>
@@ -10378,17 +10425,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TurnCapricePrice</t>
+          <t>TurnSunHeal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
+          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent. Step 15 : 8 -&gt; 6)</t>
         </is>
       </c>
     </row>
@@ -10400,17 +10447,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TurnCapricePerStroke</t>
+          <t>TurnFannyScale</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
+          <t>FANNY MENDELSSOHN AND ???'s PASSIVE : FANNY's voice hits this much harder</t>
         </is>
       </c>
     </row>
@@ -10422,17 +10469,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TurnLullyWindow</t>
+          <t>TurnFelixHeal</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
+          <t>FELIX's voice heals this much more</t>
         </is>
       </c>
     </row>
@@ -10444,17 +10491,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TurnSunHeal</t>
+          <t>TurnFelixCrescendo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent. Step 15 : 8 -&gt; 6)</t>
+          <t>and gives this much more CRESCENDO</t>
         </is>
       </c>
     </row>
@@ -10466,17 +10513,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TurnFannyScale</t>
+          <t>TurnDuetDamage</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>THE UNSIGNED's PASSIVE : FANNY's voice hits this much harder</t>
+          <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, FANNY 46 percent)</t>
         </is>
       </c>
     </row>
@@ -10488,83 +10535,83 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TurnFelixHeal</t>
+          <t>TurnDuetHeal</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FELIX's voice heals this much more</t>
+          <t>and life back for every musician</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TurnFelixCrescendo</t>
+          <t>TurnCountsWindow</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>and gives this much more CRESCENDO</t>
+          <t>COUNTS ALOUD (PAGANINI) : seconds added to their PERFECT window</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TurnDuetDamage</t>
+          <t>TurnQuietScale</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, THE UNSIGNED 46 percent)</t>
+          <t>THE QUIET PART (QUANTZ) : against an enemy showing a p note</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The other four of the lore</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TurnDuetHeal</t>
+          <t>TurnMomentumMost</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>and life back for every musician</t>
+          <t>MOMENTUM (PFUNDT) : power gained by hits in a row, at most</t>
         </is>
       </c>
     </row>
@@ -10576,17 +10623,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TurnCountsWindow</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>COUNTS ALOUD (ANNA) : seconds added to her PERFECT window</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -10598,17 +10645,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TurnQuietScale</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>THE QUIET PART (KLARA) : against an enemy showing a p note</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
@@ -10620,17 +10667,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TurnMomentumMost</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MOMENTUM (OTTO) : power gained by hits in a row, at most</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
         </is>
       </c>
     </row>
@@ -10642,17 +10689,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnFourBarsEvery</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>FOUR BARS STRAIGHT (DUPORT) : every this many ATTACKs</t>
         </is>
       </c>
     </row>
@@ -10664,17 +10711,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnFourBarsScale</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>hits this much harder</t>
         </is>
       </c>
     </row>
@@ -10686,17 +10733,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnLateBonus</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
+          <t>FASHIONABLY LATE (PUNTO) : seconds after the GOOD window a late stroke still counts</t>
         </is>
       </c>
     </row>
@@ -10708,83 +10755,83 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TurnFourBarsEvery</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FOUR BARS STRAIGHT (LUKA) : every this many ATTACKs</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TurnFourBarsScale</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>hits this much harder</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TurnLateBonus</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FASHIONABLY LATE (IRIS) : seconds after the GOOD window a late stroke still counts</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -10796,17 +10843,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
@@ -10818,17 +10865,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
@@ -10840,17 +10887,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
@@ -10862,17 +10909,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
@@ -10884,17 +10931,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10953,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>ArchiveFirstChairTier</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10916,63 +10963,63 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ArchiveStagePerLevel</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10982,7 +11029,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FULL STAGE : musicians more on the field at the start (step 12)</t>
+          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
         </is>
       </c>
     </row>
@@ -10994,17 +11041,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -11016,17 +11063,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -11038,17 +11085,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -11060,17 +11107,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -11082,17 +11129,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>SFORZANDO : a PERFECT f note</t>
         </is>
       </c>
     </row>
@@ -11104,17 +11151,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -11126,17 +11173,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -11148,17 +11195,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SFORZANDO : a PERFECT f note</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11217,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -11180,7 +11227,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11239,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -11202,7 +11249,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
@@ -11214,17 +11261,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
@@ -11236,17 +11283,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
@@ -11258,83 +11305,83 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
@@ -11346,83 +11393,83 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Feel</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ENTRANCE : a called musician's moves in their first bar</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Feel</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GREEN ROOM : life back for each musician on the BENCH at the end of a bar</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Feel</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -11434,17 +11481,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -11456,17 +11503,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -11478,17 +11525,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -11500,17 +11547,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -11522,17 +11569,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -11544,17 +11591,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnNumberTime</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back</t>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
@@ -11566,17 +11613,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnBigHit</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
@@ -11588,17 +11635,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnNumberCell</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
@@ -11610,17 +11657,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnNumberBigCell</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>the same for a big hit (was 8)</t>
         </is>
       </c>
     </row>
@@ -11632,17 +11679,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnDissolveTime</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
         </is>
       </c>
     </row>
@@ -11654,17 +11701,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnCutInTime</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
         </is>
       </c>
     </row>
@@ -11676,17 +11723,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnKillStop</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding</t>
+          <t>the freeze when an enemy falls silent</t>
         </is>
       </c>
     </row>
@@ -11698,17 +11745,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TurnHoldStill</t>
+          <t>TurnEndTime</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>pixels per second the baton may drift and still count as still</t>
+          <t>the win or lose banner stays this long</t>
         </is>
       </c>
     </row>
@@ -11720,15 +11767,81 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>TurnHoldStill</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>pixels per second the baton may drift and still count as still</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -12267,7 +12380,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>It always strikes the musician who was CALLED in last.</t>
+          <t>It always strikes the musician who played the last skill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -12312,7 +12425,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>While it stands, a CALL costs 1 more BREATH.</t>
+          <t>While it stands, an ATTACK gives 1 less BREATH.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1516,105 +1516,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.8b   0%   BOSS  100%  7.0b   0%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.5b   0%   BOSS  100%  6.8b   0%   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.6b   0%   LATE  100%  4.2b   0%   ELITE 100%  5.3b   0%   BOSS  100%  9.6b   0%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.5b   0%   LATE  100%  4.2b   0%   ELITE 100%  5.3b   0%   BOSS  100%  9.5b   0%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.5b   0%   LATE  100%  6.6b   0%   ELITE 100%  7.8b   0%   BOSS  100% 13.0b   0%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.6b   0%   LATE  100%  6.6b   0%   ELITE 100%  7.8b   0%   BOSS  100% 12.9b   0%   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.2b   1%   LATE  100%  3.2b   4%   ELITE 100%  4.1b   4%   BOSS  100%  7.6b  11%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.2b   1%   LATE  100%  3.2b   4%   ELITE 100%  3.9b   4%   BOSS  100%  7.4b   9%   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.8b   6%   LATE  100%  5.2b  10%   ELITE 100%  5.9b  13%   BOSS  100% 10.5b  22%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.8b   5%   LATE  100%  5.0b   9%   ELITE 100%  5.8b  11%   BOSS  100% 10.3b  21%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.2b  13%   LATE  100%  7.3b  16%   ELITE 100%  8.8b  21%   BOSS   99% 14.7b  33%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.1b  12%   LATE  100%  7.2b  16%   ELITE 100%  8.5b  20%   BOSS   98% 14.2b  30%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.4b   4%   LATE  100%  3.7b  10%   ELITE 100%  4.5b  11%   BOSS  100%  8.6b  22%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.4b   4%   LATE  100%  3.7b   9%   ELITE 100%  4.4b   9%   BOSS  100%  8.5b  24%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.5b  15%   LATE  100%  6.3b  23%   ELITE 100%  7.3b  29%   BOSS   85% 12.5b  55%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.4b  14%   LATE  100%  6.0b  22%   ELITE  99%  7.0b  27%   BOSS   90% 12.4b  50%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.5b  26%   LATE  100%  9.3b  31%   ELITE  84% 11.6b  58%   BOSS   39% 14.3b  82%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.4b  28%   LATE   99%  9.1b  34%   ELITE  85% 11.2b  57%   BOSS   34% 13.8b  84%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.0b  10%   LATE  100%  5.1b  25%   ELITE 100%  6.2b  27%   BOSS   69% 11.9b  67%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.9b   9%   LATE  100%  4.9b  23%   ELITE 100%  5.6b  26%   BOSS   69% 11.0b  67%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.4b  38%   LATE   79%  8.9b  62%   ELITE  38%  9.8b  87%   BOSS    4%  9.0b  98%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.0b  32%   LATE   91%  8.3b  53%   ELITE  57%  9.8b  81%   BOSS   11%  9.6b  96%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  51%  9.3b  80%   LATE   12%  7.6b  96%   ELITE   0%  6.0b 100%   BOSS    0%  5.2b 100%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  50%  9.5b  80%   LATE   12%  7.2b  95%   ELITE   0%  6.4b  99%   BOSS    0%  5.9b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  3.7b  17%   LATE   98%  6.8b  44%   ELITE  90%  8.8b  59%   BOSS   17% 10.8b  92%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  3.5b  16%   LATE   99%  6.3b  42%   ELITE  92%  8.0b  52%   BOSS   17% 10.2b  92%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  67%  8.8b  75%   LATE    4%  6.2b  99%   ELITE   0%  6.0b  99%   BOSS    0%  5.1b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  83%  8.1b  63%   LATE   18%  7.5b  95%   ELITE   1%  6.5b  99%   BOSS    0%  5.9b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.0b  99%   LATE    0%  3.5b 100%   ELITE   0%  3.5b 100%   BOSS    0%  3.3b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   2%  5.0b  99%   LATE    0%  3.5b 100%   ELITE   0%  3.6b 100%   BOSS    0%  3.3b 100%   </t>
         </is>
       </c>
     </row>
@@ -1643,28 +1643,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    43 /  50 /   6 /   0   x1.70</t>
+          <t xml:space="preserve">  EXPERT    51 /  44 /   3 /   0   x1.75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG     6 /  36 /  49 /   7   x1.37</t>
+          <t xml:space="preserve">  STRONG     9 /  40 /  43 /   6   x1.40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE    0 /   6 /  43 /  49   x1.15</t>
+          <t xml:space="preserve">  AVERAGE    2 /   9 /  48 /  40   x1.19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   1 /  18 /  80   x1.05</t>
+          <t xml:space="preserve">  NEWCOMER   0 /   3 /  27 /  68   x1.09</t>
         </is>
       </c>
     </row>
@@ -1679,119 +1679,119 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   78%  8.5b    100%  6.1b    </t>
+          <t xml:space="preserve">  HUSH                   85%  8.4b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               76%  8.7b    100%  6.2b    </t>
+          <t xml:space="preserve">  DEAD AIR               93%  8.4b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               87%  10.0b    100%  6.5b    </t>
+          <t xml:space="preserve">  THE LULL               95%  9.3b    100%  6.3b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 84%  8.7b    100%  6.1b    </t>
+          <t xml:space="preserve">  STATIC                 90%  8.1b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         52%  10.0b    100%  7.1b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         71%  9.7b    100%  6.9b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            33%  8.7b    100%  7.2b    </t>
+          <t xml:space="preserve">  WHITE NOISE            40%  8.6b    100%  7.1b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  4.9b     20%  13.7b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  5.1b     28%  14.1b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     0%  7.8b     85%  16.3b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.2b     89%  15.8b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.5b      5%  11.4b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.6b      6%  11.6b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              83%  9.1b    100%  6.2b    </t>
+          <t xml:space="preserve">  ROOM TONE              94%  8.4b    100%  6.1b    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                86%  9.2b    100%  6.3b    </t>
+          <t xml:space="preserve">  THE CUE                93%  8.7b    100%  6.2b    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             75%  8.7b    100%  6.1b    </t>
+          <t xml:space="preserve">  THE DAMPER             94%  8.4b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                87%  8.3b    100%  5.8b    </t>
+          <t xml:space="preserve">  STUTTER                94%  8.1b    100%  5.7b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              30%  10.6b    100%  7.5b    </t>
+          <t xml:space="preserve">  THE ROUND              51%  10.6b    100%  7.1b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.1b     15%  15.5b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.6b     20%  15.5b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  5.4b     42%  15.3b    </t>
+          <t xml:space="preserve">  THE STAFF               0%  5.3b     38%  14.7b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.4b     34%  13.5b    </t>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.7b     42%  14.1b    </t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RUNS (3 floors, life carried over, no motifs) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
+          <t>RUNS (3 floors, life carried over, no motifs, Beethoven) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
@@ -1827,21 +1827,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    46%    0% / 8% / 45%</t>
+          <t xml:space="preserve">    STRONG    47%    0% / 5% / 47%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    35% / 64% / 1%</t>
+          <t xml:space="preserve">    AVERAGE    0%    35% / 62% / 2%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
+          <t xml:space="preserve">    NEWCOMER   0%    89% / 10% / 0%</t>
         </is>
       </c>
     </row>
@@ -1862,21 +1862,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    71%    0% / 4% / 24%</t>
+          <t xml:space="preserve">    EXPERT    74%    0% / 3% / 22%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    8% / 67% / 24%</t>
+          <t xml:space="preserve">    STRONG     0%    12% / 54% / 33%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    87% / 12% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    76% / 23% / 0%</t>
         </is>
       </c>
     </row>
@@ -1898,21 +1898,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       46% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       51% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  45% / 0%</t>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  58% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       50% / 0%</t>
+          <t xml:space="preserve">  THE METRONOME       45% / 0%</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -8897,7 +8897,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>ONE RULE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8912,14 +8912,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>right way, right size, on time</t>
+          <t>right way, on time</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>ONE RULE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8934,51 +8934,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>right way, right size, a little off time</t>
+          <t>right way, a little off time</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>ONE RULE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TurnWrongSize</t>
+          <t>TurnMiss</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>on time but the wrong size</t>
+          <t>the wrong way, too early, too late or no swipe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>ONE BAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TurnMiss</t>
+          <t>BandSize</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>the wrong way, too early, too late or no swipe</t>
+          <t>the musicians a run picks at its start, every one of them plays every fight</t>
         </is>
       </c>
     </row>
@@ -8990,17 +8990,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BandSize</t>
+          <t>TurnAttackScale</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>the musicians a run picks at its start, every one of them plays every fight</t>
+          <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
         </is>
       </c>
     </row>
@@ -9012,17 +9012,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TurnAttackScale</t>
+          <t>TurnAttackOffBeat</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
+          <t>ATTACK : the OFF-BEAT it adds</t>
         </is>
       </c>
     </row>
@@ -9034,17 +9034,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TurnAttackOffBeat</t>
+          <t>TurnCutInSpeed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ATTACK : the OFF-BEAT it adds</t>
+          <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
         </is>
       </c>
     </row>
@@ -9056,39 +9056,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TurnCutInSpeed</t>
+          <t>TurnCutInAfter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
+          <t>right after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ONE BAR</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TurnCutInAfter</t>
+          <t>TurnPackEarly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>{ 1, 2, 3 }</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>right after this many of the band's moves</t>
+          <t>an ENCOUNTER in the first half of the floor</t>
         </is>
       </c>
     </row>
@@ -9100,17 +9100,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TurnPackEarly</t>
+          <t>TurnPackLate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>an ENCOUNTER in the first half of the floor</t>
+          <t>in the second half</t>
         </is>
       </c>
     </row>
@@ -9122,17 +9122,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TurnPackLate</t>
+          <t>TurnEliteEscort</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>{ 0, 1, 2 }</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>in the second half</t>
+          <t>ordinary enemies that come with an ELITE</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TurnEliteEscort</t>
+          <t>TurnBossEscort</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ordinary enemies that come with an ELITE</t>
+          <t>and with the BOSS</t>
         </is>
       </c>
     </row>
@@ -9166,17 +9166,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TurnBossEscort</t>
+          <t>MaestroTurnDamage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{ 0, 1, 2 }</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>and with the BOSS</t>
+          <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
         </is>
       </c>
     </row>
@@ -9188,39 +9188,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MaestroTurnDamage</t>
+          <t>TurnShardsPerEscort</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
+          <t>shards for each enemy beyond the first</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>Floor Scale</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TurnShardsPerEscort</t>
+          <t>TurnFloorLife</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>{ 1.6, 2.1, 2.7 }</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>shards for each enemy beyond the first</t>
+          <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
         </is>
       </c>
     </row>
@@ -9232,34 +9232,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TurnFloorLife</t>
+          <t>TurnFloorDamage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{ 1.6, 2.1, 2.7 }</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
+          <t>{ 1, 1.2, 1.4 }</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Floor Scale</t>
+          <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TurnFloorDamage</t>
+          <t>TurnFillsGapsScale</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{ 1, 1.2, 1.4 }</t>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DEAD AIR : a missed note</t>
         </is>
       </c>
     </row>
@@ -9271,17 +9271,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TurnFillsGapsScale</t>
+          <t>TurnLullHeal</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEAD AIR : a missed note</t>
+          <t>THE LULL : life back on its humming turn</t>
         </is>
       </c>
     </row>
@@ -9293,17 +9293,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TurnLullHeal</t>
+          <t>TurnLullEvery</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>THE LULL : life back on its humming turn</t>
+          <t>every this many turns</t>
         </is>
       </c>
     </row>
@@ -9315,17 +9315,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TurnLullEvery</t>
+          <t>TurnFastGap</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>every this many turns</t>
+          <t>REQUIEM : the gap between notes below half life</t>
         </is>
       </c>
     </row>
@@ -9337,39 +9337,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TurnFastGap</t>
+          <t>TurnBargainSteal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>REQUIEM : the gap between notes below half life</t>
+          <t>THE DEVIL'S STRING : breath taken by each attack</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enemy Traits in the turn battle</t>
+          <t>ONE BAR enemies</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TurnBargainSteal</t>
+          <t>TurnRoomToneKeep</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>THE DEVIL'S STRING : breath taken by each attack</t>
+          <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
         </is>
       </c>
     </row>
@@ -9381,17 +9381,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TurnRoomToneKeep</t>
+          <t>TurnFeltHandBreath</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
+          <t>THE DAMPER (FELT HAND, 29 Oct) : an ATTACK gives this much less BREATH while it stands (until CALL went</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TurnFeltHandBreath</t>
+          <t>TurnTwiceFirst</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>THE DAMPER (FELT HAND, 29 Oct) : an ATTACK gives this much less BREATH while it stands (until CALL went</t>
+          <t>STUTTER : cuts in after this many of the band's moves</t>
         </is>
       </c>
     </row>
@@ -9425,39 +9425,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TurnTwiceFirst</t>
+          <t>TurnTwiceSecond</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>STUTTER : cuts in after this many of the band's moves</t>
+          <t>and again after this many</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ONE BAR enemies</t>
+          <t>Bosses of step 14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TurnTwiceSecond</t>
+          <t>TurnByTouchMost</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>and again after this many</t>
+          <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
         </is>
       </c>
     </row>
@@ -9469,17 +9469,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TurnByTouchMost</t>
+          <t>TurnCourtKeep</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
+          <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
         </is>
       </c>
     </row>
@@ -9491,17 +9491,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TurnCourtKeep</t>
+          <t>TurnStaffEvery</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
+          <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
         </is>
       </c>
     </row>
@@ -9513,17 +9513,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TurnStaffEvery</t>
+          <t>TurnStaffPower</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
+          <t>that one note hits everyone this much harder</t>
         </is>
       </c>
     </row>
@@ -9535,39 +9535,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TurnStaffPower</t>
+          <t>TurnThorns</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>that one note hits everyone this much harder</t>
+          <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bosses of step 14</t>
+          <t>PRACTICE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TurnThorns</t>
+          <t>TurnPracticeHp</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
+          <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
         </is>
       </c>
     </row>
@@ -9579,17 +9579,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TurnPracticeHp</t>
+          <t>TurnPracticeSpeed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -9601,34 +9596,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TurnPracticeSpeed</t>
+          <t>TurnPracticePower</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PRACTICE</t>
+          <t>Enemy Attack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TurnPracticePower</t>
+          <t>TurnNotesMin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>{ 1, 2, 3 }</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>each note hits this x TurnNoteDamage (4 life)</t>
+          <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
@@ -9640,17 +9640,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TurnNotesMin</t>
+          <t>TurnNotesMax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{ 1, 2, 3 }</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ELITE and BOSS</t>
+          <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
@@ -9662,12 +9657,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TurnNotesMax</t>
+          <t>TurnSmallNotesMin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{ 2, 3, 4 }</t>
+          <t>{ 1, 1, 2 }</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ordinary enemies</t>
         </is>
       </c>
     </row>
@@ -9679,17 +9679,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMin</t>
+          <t>TurnSmallNotesMax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{ 1, 1, 2 }</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>ordinary enemies</t>
+          <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
@@ -9701,51 +9696,51 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TurnSmallNotesMax</t>
+          <t>TurnNoteDamage</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{ 2, 2, 2 }</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Enemy Attack</t>
+          <t>PARRY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TurnNoteDamage</t>
+          <t>TurnParryGoodKeep</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PARRY</t>
+          <t>BREATH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TurnParryGoodKeep</t>
+          <t>TurnBreathMax</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -9757,12 +9752,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TurnBreathMax</t>
+          <t>TurnBreathStart</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -9774,12 +9769,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TurnBreathStart</t>
+          <t>TurnBreathPerAttack</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
         </is>
       </c>
     </row>
@@ -9791,56 +9791,51 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TurnBreathPerAttack</t>
+          <t>TurnBreathPerParry</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
+          <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BREATH</t>
+          <t>KNOCKED OUT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TurnBreathPerParry</t>
+          <t>TurnReviveHp</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KNOCKED OUT</t>
+          <t>OFF-BEAT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TurnReviveHp</t>
+          <t>TurnOffBeatMax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -9852,12 +9847,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TurnOffBeatMax</t>
+          <t>TurnParryOffBeat</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
@@ -9869,39 +9869,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TurnParryOffBeat</t>
+          <t>TurnOffBeatScale</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>each note parried PERFECT</t>
+          <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OFF-BEAT</t>
+          <t>Statuses</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TurnOffBeatScale</t>
+          <t>TurnDissonanceMost</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>damage against an enemy off the beat</t>
+          <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
@@ -9913,17 +9913,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TurnDissonanceMost</t>
+          <t>TurnCrescendoStep</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DISSONANCE stacks no higher</t>
+          <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
@@ -9935,17 +9935,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TurnCrescendoStep</t>
+          <t>TurnCrescendoMost</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>CRESCENDO : each stack hits this much harder</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -9957,12 +9952,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TurnCrescendoMost</t>
+          <t>TurnMuteTurns</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
@@ -9974,39 +9974,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TurnMuteTurns</t>
+          <t>TurnGuardKeep</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MUTE : turns without skills</t>
+          <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Statuses</t>
+          <t>COUNTER and CADENZA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TurnGuardKeep</t>
+          <t>TurnCounterScale</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GUARD : the share of a hit that gets through</t>
+          <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
@@ -10018,17 +10018,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TurnCounterScale</t>
+          <t>TurnCadenzaCounter</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>x the target's attack damage</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -10040,12 +10035,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TurnCadenzaCounter</t>
+          <t>TurnCadenzaEvery</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10057,29 +10052,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TurnCadenzaEvery</t>
+          <t>TurnCadenzaPower</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COUNTER and CADENZA</t>
+          <t>Skill Notes</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TurnCadenzaPower</t>
+          <t>TurnHoldBase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.6</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10086,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TurnHoldBase</t>
+          <t>TurnHoldGain</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -10108,12 +10103,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TurnHoldGain</t>
+          <t>TurnRollPerfect</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -10125,12 +10120,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TurnRollPerfect</t>
+          <t>TurnRollGood</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10142,12 +10137,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TurnRollGood</t>
+          <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -10159,46 +10154,46 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MaestroTurnRollPerfect</t>
+          <t>MaestroTurnRollGood</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Skill Notes</t>
+          <t>Conductors</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MaestroTurnRollGood</t>
+          <t>TurnSignatureNeed</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Conductors</t>
+          <t>PLAYTEST</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TurnSignatureNeed</t>
+          <t>PlaytestSignatureNeed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10210,12 +10205,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PlaytestSignatureNeed</t>
+          <t>TurnBeethovenMost</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
@@ -10227,17 +10227,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TurnBeethovenMost</t>
+          <t>TurnBoltDamage</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
+          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
@@ -10249,17 +10249,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TurnBoltDamage</t>
+          <t>TurnMozartRun</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
+          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
@@ -10271,39 +10271,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TurnMozartRun</t>
+          <t>TurnFeatherPerStroke</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
+          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PLAYTEST</t>
+          <t>The other four of the lore</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TurnFeatherPerStroke</t>
+          <t>TurnLockedTempoWindow</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
+          <t>LOCKED TEMPO : seconds added to the PERFECT window of skills and the SIGNATURE, never</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>THE QUIET PART (QUANTZ) : against an enemy showing a p note</t>
+          <t>THE QUIET PART (QUANTZ) : against an enemy whose next attack is aimed at someone else</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy showing an f note</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
         </is>
       </c>
     </row>
@@ -10689,17 +10689,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TurnFourBarsEvery</t>
+          <t>TurnLongNotes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FOUR BARS STRAIGHT (DUPORT) : every this many ATTACKs</t>
+          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
         </is>
       </c>
     </row>
@@ -10711,17 +10711,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TurnFourBarsScale</t>
+          <t>TurnFourBarsEvery</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>hits this much harder</t>
+          <t>FOUR BARS STRAIGHT (DUPORT) : every this many ATTACKs</t>
         </is>
       </c>
     </row>
@@ -10733,17 +10733,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TurnLateBonus</t>
+          <t>TurnFourBarsScale</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>FASHIONABLY LATE (PUNTO) : seconds after the GOOD window a late stroke still counts</t>
+          <t>hits this much harder</t>
         </is>
       </c>
     </row>
@@ -10755,39 +10755,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnLateBonus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>FASHIONABLY LATE (PUNTO) : seconds after the GOOD window a late stroke still counts</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
@@ -10799,17 +10799,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
@@ -10821,17 +10821,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
@@ -10843,17 +10843,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -10865,17 +10865,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
@@ -10887,17 +10887,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
@@ -10909,17 +10909,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
@@ -10931,17 +10931,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
@@ -10953,39 +10953,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ArchiveFirstChairTier</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>ArchiveFirstChairTier</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -11019,17 +11019,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for a p note parried PERFECT</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -11041,17 +11041,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
         </is>
       </c>
     </row>
@@ -11063,17 +11063,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -11107,17 +11107,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -11129,17 +11129,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SFORZANDO : a PERFECT f note</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -11151,17 +11151,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -11205,7 +11205,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
@@ -11261,17 +11261,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
@@ -11283,17 +11283,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
@@ -11305,29 +11305,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
@@ -11349,17 +11349,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
@@ -11371,17 +11371,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
@@ -11393,39 +11393,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -11437,17 +11437,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -11459,17 +11459,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnLateReveal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -11503,17 +11503,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -11525,17 +11525,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -11547,17 +11547,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -11569,17 +11569,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -11591,17 +11591,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnNumberTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -11613,17 +11613,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TurnBigHit</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>from this much damage it is drawn bigger</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -11635,17 +11635,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnNumberCell</t>
+          <t>TurnNumberTime</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
@@ -11657,17 +11657,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TurnNumberBigCell</t>
+          <t>TurnBigHit</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>the same for a big hit (was 8)</t>
+          <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
@@ -11679,17 +11679,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TurnDissolveTime</t>
+          <t>TurnNumberCell</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TurnCutInTime</t>
+          <t>TurnNumberBigCell</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+          <t>the same for a big hit (was 8)</t>
         </is>
       </c>
     </row>
@@ -11723,17 +11723,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnDissolveTime</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
         </is>
       </c>
     </row>
@@ -11745,17 +11745,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnCutInTime</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
         </is>
       </c>
     </row>
@@ -11767,17 +11767,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnKillStop</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>the freeze when an enemy falls silent</t>
         </is>
       </c>
     </row>
@@ -11789,17 +11789,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnEndTime</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding</t>
+          <t>the win or lose banner stays this long</t>
         </is>
       </c>
     </row>
@@ -11811,17 +11811,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TurnHoldStill</t>
+          <t>TurnSparkGap</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>pixels per second the baton may drift and still count as still</t>
+          <t>a spark comes this soon after the note before it</t>
         </is>
       </c>
     </row>
@@ -11833,15 +11833,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -11944,7 +11966,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dp Up, Lp Rp Dp</t>
+          <t>D U, L R D</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -11985,7 +12007,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lmf Rmf, Dmf Dmf Umf</t>
+          <t>L R, D D U</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -12026,7 +12048,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dp Dp, Up Dp Up</t>
+          <t>D D, U D U</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -12067,7 +12089,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lf Rp, Umf Df Lp</t>
+          <t>L R, U D L</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -12077,7 +12099,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>One note of each attack shows the wrong size.</t>
+          <t>One note of each attack hides its arrow behind a ? until late.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12112,7 +12134,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Df Df Uf, Lmf Rmf Lmf Rmf</t>
+          <t>D D U, L R L R</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -12153,7 +12175,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lp Rp Lp Rp, Up Dp Up Dp</t>
+          <t>L R L R, U D U D</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -12198,7 +12220,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Df Lmf Rmf Uf, Lf Rf Lf Rf</t>
+          <t>D L R U, L R L R</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12243,7 +12265,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dmf Umf Lmf, Rf Lf Dp Up</t>
+          <t>D U L, R L D U</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -12284,7 +12306,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rf Rf Lf, Uf Df Uf Df</t>
+          <t>R R L, U D U D</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -12329,7 +12351,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dp, Up Dp</t>
+          <t>D, U D</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -12370,7 +12392,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rmf Lmf, Uf</t>
+          <t>R L, U</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -12415,7 +12437,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dmf Dp, Lmf Rmf</t>
+          <t>D D, L R</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -12456,7 +12478,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lp, Rp, Up</t>
+          <t>L, R, U</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -12501,7 +12523,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Df Dmf Df, Lmf Rmf Lf Rf</t>
+          <t>D D D, L R L R</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -12542,7 +12564,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Uf Uf Uf Df, Lf Rf Df</t>
+          <t>U U U D, L R D</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -12587,7 +12609,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Df Dmf Df, Dmf Lmf Dmf Rmf</t>
+          <t>D D D, D L D R</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -12628,7 +12650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Df Umf Df Umf, Lmf Rmf Lp Rp</t>
+          <t>D U D U, L R L R</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -16,8 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Battle" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Enemies" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Conductors" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Sim" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Skills" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Conductors" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Turn Sim" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1196,6 +1197,824 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="67" t="inlineStr">
+        <is>
+          <t>Musician</t>
+        </is>
+      </c>
+      <c r="B1" s="67" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C1" s="67" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D1" s="67" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
+      <c r="E1" s="67" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F1" s="67" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G1" s="67" t="inlineStr">
+        <is>
+          <t>Damage per note</t>
+        </is>
+      </c>
+      <c r="H1" s="67" t="inlineStr">
+        <is>
+          <t>DISSONANCE</t>
+        </is>
+      </c>
+      <c r="I1" s="67" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="J1" s="67" t="inlineStr">
+        <is>
+          <t>CRESCENDO</t>
+        </is>
+      </c>
+      <c r="K1" s="67" t="inlineStr">
+        <is>
+          <t>BREATH back</t>
+        </is>
+      </c>
+      <c r="L1" s="67" t="inlineStr">
+        <is>
+          <t>OFF-BEAT</t>
+        </is>
+      </c>
+      <c r="M1" s="67" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="N1" s="67" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="O1" s="67" t="inlineStr">
+        <is>
+          <t>Trait (turn battle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>PAGANINI (String, power 5)</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>CAPRICE</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F2" s="32" t="inlineStr">
+        <is>
+          <t>L R L R</t>
+        </is>
+      </c>
+      <c r="G2" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H2" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="32" t="inlineStr">
+        <is>
+          <t>4 quick cuts. Each adds 1 DISSONANCE.</t>
+        </is>
+      </c>
+      <c r="O2" s="32" t="inlineStr">
+        <is>
+          <t>THE DEVIL'S BARGAIN : Short of BREATH, their skills take 6 life for each BREATH missing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="32" t="inlineStr">
+        <is>
+          <t>IL CANNONE</t>
+        </is>
+      </c>
+      <c r="C3" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>HOLD L</t>
+        </is>
+      </c>
+      <c r="G3" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N3" s="32" t="inlineStr">
+        <is>
+          <t>One big held shot. Hold it = harder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>QUANTZ (Wind, power 4)</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>SOFT AIR</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>AllAllies</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>D U</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="32" t="inlineStr">
+        <is>
+          <t>Heals the whole band 3 per note.</t>
+        </is>
+      </c>
+      <c r="O4" s="32" t="inlineStr">
+        <is>
+          <t>BREATH CONTROL : Their ATTACK gives 1 BREATH more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>THE LESSON</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Ally</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>U D</t>
+        </is>
+      </c>
+      <c r="M5" s="32" t="inlineStr">
+        <is>
+          <t>LESSON</t>
+        </is>
+      </c>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>A friend's next skill : wider PERFECT, harder hits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>PFUNDT (Percussion, power 6)</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>TIMPANI ROLL</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>ROLL</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
+        <is>
+          <t>Shake fast. Big OFF-BEAT.</t>
+        </is>
+      </c>
+      <c r="O6" s="32" t="inlineStr">
+        <is>
+          <t>TURN OF THE HAND : An enemy their skill hits plays 1 note fewer next time (2 at least).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>THUNDER CALL</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Defend</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M7" s="32" t="inlineStr">
+        <is>
+          <t>GUARD TAUNT</t>
+        </is>
+      </c>
+      <c r="N7" s="32" t="inlineStr">
+        <is>
+          <t>Enemies aim at PFUNDT, who takes half damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>DUPORT (String, power 6)</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>SHIELD</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Defend</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>Ally</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>HOLD R</t>
+        </is>
+      </c>
+      <c r="M8" s="32" t="inlineStr">
+        <is>
+          <t>SHIELD</t>
+        </is>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>Guard a friend : their hits land on DUPORT, halved.</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="inlineStr">
+        <is>
+          <t>THE SCAR : Every attack that hurts them gives 1 CRESCENDO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>LANCE</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>R R</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M9" s="32" t="inlineStr">
+        <is>
+          <t>x2 WHEN HIT</t>
+        </is>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>2 thrusts. Twice as hard if DUPORT was just hit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>PUNTO (Wind, power 5)</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>FANFARE</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Boost</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>AllAllies</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>L L</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>The band hits harder : 1 CRESCENDO per note.</t>
+        </is>
+      </c>
+      <c r="O10" s="32" t="inlineStr">
+        <is>
+          <t>THE HUNTING CALL : The musician who plays right after them in the bar hits harder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>CHAKRAM</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>L R L</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>BOUNCE 3</t>
+        </is>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>3 throws, a new enemy each. Hit again = half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>MALI (String, power 5) hidden</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>BY EAR</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>D SPARK</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
+        <is>
+          <t>A hit and a spark. Each adds 1 DISSONANCE.</t>
+        </is>
+      </c>
+      <c r="O12" s="32" t="inlineStr">
+        <is>
+          <t>BY EAR : Hits 50 percent harder against an enemy that is OFF-BEAT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>SLIDE</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>U D U D</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="32" t="inlineStr">
+        <is>
+          <t>4 notes up and down. Each adds 1 DISSONANCE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>CHAI (Wind, power 4) hidden</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>HELD NOTE</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Ally</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>HOLD R</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>Heals one musician. Hold it = more.</t>
+        </is>
+      </c>
+      <c r="O14" s="32" t="inlineStr">
+        <is>
+          <t>HELD NOTE : His ATTACK rings on : a second hit for 40 percent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>CIRCULAR</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>AllAllies</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>ROLL</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" s="32" t="inlineStr">
+        <is>
+          <t>Shake fast. Heals everyone 3, 3 BREATH back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>NUAN (Percussion, power 6) hidden</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>RUN</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>L R L</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>3 big hits. OFF-BEAT each.</t>
+        </is>
+      </c>
+      <c r="O16" s="32" t="inlineStr">
+        <is>
+          <t>ONE STEP BETTER : Hits 30 percent harder against an enemy whose next attack has 3 notes or more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>ONE STEP</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>L SPARK</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L17" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="N17" s="32" t="inlineStr">
+        <is>
+          <t>A big hit and a spark. OFF-BEAT each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>BORIS (Percussion, power 7) hidden</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>THE FLOOR</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>AllEnemies</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>HOLD D</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="N18" s="32" t="inlineStr">
+        <is>
+          <t>Hits every enemy. Hold it = harder.</t>
+        </is>
+      </c>
+      <c r="O18" s="32" t="inlineStr">
+        <is>
+          <t>THE WHOLE FLOOR : The PERFECT last note of his skills takes 2 off each note of the enemy's next attack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>THUNDER</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>D D ROLL</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="N19" s="32" t="inlineStr">
+        <is>
+          <t>2 big hits and a roll. Big OFF-BEAT.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1472,451 +2291,487 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>turnsim.txt (--shots turnsim, Core/DebugShots.TurnSim.cs)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>TACET TURN BATTLE BALANCE, ONE BAR  (200 fights per cell, 300 runs per player)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Players : timing spread FLAWLESS 0 / EXPERT 0.08 / STRONG 0.12 / AVERAGE 0.2 / NEWCOMER 0.3 seconds</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>FIGHTS at full life (the band of three) : WIN PERCENT  /  BARS  /  LIFE LOST PERCENT</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.5b   0%   BOSS  100%  6.8b   0%   </t>
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.1b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.5b   0%   BOSS  100%  7.3b   0%   </t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.5b   0%   LATE  100%  4.2b   0%   ELITE 100%  5.3b   0%   BOSS  100%  9.5b   0%   </t>
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.6b   0%   LATE  100%  4.6b   1%   ELITE 100%  5.9b   0%   BOSS  100% 10.5b   1%   </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  5.6b   0%   LATE  100%  6.6b   0%   ELITE 100%  7.8b   0%   BOSS  100% 12.9b   0%   </t>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  6.2b   3%   LATE  100%  7.2b   2%   ELITE 100%  8.4b   1%   BOSS  100% 14.4b   3%   </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.2b   1%   LATE  100%  3.2b   4%   ELITE 100%  3.9b   4%   BOSS  100%  7.4b   9%   </t>
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.3b   1%   LATE  100%  3.2b   4%   ELITE 100%  4.0b   3%   BOSS  100%  8.1b  11%   </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.8b   5%   LATE  100%  5.0b   9%   ELITE 100%  5.8b  11%   BOSS  100% 10.3b  21%   </t>
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.0b   6%   LATE  100%  5.6b  11%   ELITE 100%  6.5b  13%   BOSS  100% 11.5b  24%   </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  6.1b  12%   LATE  100%  7.2b  16%   ELITE 100%  8.5b  20%   BOSS   98% 14.2b  30%   </t>
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  7.0b  15%   LATE  100%  8.1b  18%   ELITE 100%  9.6b  21%   BOSS   96% 16.3b  36%   </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.4b   4%   LATE  100%  3.7b   9%   ELITE 100%  4.4b   9%   BOSS  100%  8.5b  24%   </t>
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.5b   4%   LATE  100%  3.8b  10%   ELITE 100%  4.7b  11%   BOSS   99%  9.3b  28%   </t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.4b  14%   LATE  100%  6.0b  22%   ELITE  99%  7.0b  27%   BOSS   90% 12.4b  50%   </t>
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.9b  15%   LATE  100%  6.5b  24%   ELITE 100%  8.0b  29%   BOSS   84% 13.9b  56%   </t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  7.4b  28%   LATE   99%  9.1b  34%   ELITE  85% 11.2b  57%   BOSS   34% 13.8b  84%   </t>
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  8.1b  29%   LATE   99% 10.1b  34%   ELITE  86% 12.8b  53%   BOSS   26% 14.3b  87%   </t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.9b   9%   LATE  100%  4.9b  23%   ELITE 100%  5.6b  26%   BOSS   69% 11.0b  67%   </t>
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.2b  11%   LATE  100%  5.2b  24%   ELITE  99%  6.7b  30%   BOSS   64% 12.1b  71%   </t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.0b  32%   LATE   91%  8.3b  53%   ELITE  57%  9.8b  81%   BOSS   11%  9.6b  96%   </t>
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.8b  37%   LATE   82%  9.2b  61%   ELITE  50% 11.0b  82%   BOSS    5%  9.7b  97%   </t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  50%  9.5b  80%   LATE   12%  7.2b  95%   ELITE   0%  6.4b  99%   BOSS    0%  5.9b 100%   </t>
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  35%  9.3b  85%   LATE   11%  7.5b  95%   ELITE   0%  6.5b  99%   BOSS    0%  5.3b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  3.5b  16%   LATE   99%  6.3b  42%   ELITE  92%  8.0b  52%   BOSS   17% 10.2b  92%   </t>
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.0b  19%   LATE   98%  6.9b  42%   ELITE  83%  9.6b  62%   BOSS   16% 11.0b  94%   </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  83%  8.1b  63%   LATE   18%  7.5b  95%   ELITE   1%  6.5b  99%   BOSS    0%  5.9b 100%   </t>
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  63%  9.0b  76%   LATE   11%  6.8b  96%   ELITE   0%  6.6b  99%   BOSS    0%  5.6b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   2%  5.0b  99%   LATE    0%  3.5b 100%   ELITE   0%  3.6b 100%   BOSS    0%  3.3b 100%   </t>
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.0b  99%   LATE    0%  3.7b 100%   ELITE   0%  3.7b 100%   BOSS    0%  3.4b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 31%  SKILLS 68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 24%  SKILLS 75%</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>RANKS of the won fights above : S / A / B / C PERCENT  /  SHARDS SCALE</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  FLAWLESS 100 /   0 /   0 /   0   x2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    51 /  44 /   3 /   0   x1.75</t>
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    40 /  53 /   5 /   0   x1.69</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG     9 /  40 /  43 /   6   x1.40</t>
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG     5 /  37 /  50 /   7   x1.36</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE    2 /   9 /  48 /  40   x1.19</t>
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE    0 /   6 /  48 /  43   x1.16</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   3 /  27 /  68   x1.09</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER   0 /   1 /  23 /  75   x1.07</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HUSH                   85%  8.4b    100%  6.0b    </t>
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HUSH                   81%  9.2b    100%  6.4b    </t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DEAD AIR               93%  8.4b    100%  6.0b    </t>
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DEAD AIR               73%  9.1b    100%  6.5b    </t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE LULL               95%  9.3b    100%  6.3b    </t>
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE LULL               89%  10.4b    100%  7.1b    </t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STATIC                 90%  8.1b    100%  5.9b    </t>
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STATIC                 77%  9.0b    100%  6.4b    </t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         71%  9.7b    100%  6.9b    </t>
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE MUTE CHOIR         66%  11.0b    100%  7.8b    </t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHITE NOISE            40%  8.6b    100%  7.1b    </t>
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHITE NOISE            23%  9.2b    100%  7.6b    </t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REQUIEM                 0%  5.1b     28%  14.1b    </t>
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REQUIEM                 0%  4.9b     21%  14.4b    </t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.2b     89%  15.8b    </t>
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.3b     89%  18.3b    </t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.6b      6%  11.6b    </t>
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.9b      6%  12.5b    </t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ROOM TONE              94%  8.4b    100%  6.1b    </t>
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROOM TONE              83%  9.5b    100%  6.5b    </t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE CUE                93%  8.7b    100%  6.2b    </t>
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE CUE                86%  9.9b    100%  6.6b    </t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DAMPER             94%  8.4b    100%  5.9b    </t>
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DAMPER             77%  9.0b    100%  6.5b    </t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STUTTER                94%  8.1b    100%  5.7b    </t>
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STUTTER                87%  8.7b    100%  6.1b    </t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE ROUND              51%  10.6b    100%  7.1b    </t>
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE ROUND              36%  12.4b    100%  8.3b    </t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.6b     20%  15.5b    </t>
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.4b      8%  15.2b    </t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE STAFF               0%  5.3b     38%  14.7b    </t>
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE STAFF               0%  5.4b     28%  16.1b    </t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.7b     42%  14.1b    </t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.9b     26%  13.9b    </t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>RUNS (3 floors, life carried over, no motifs, Beethoven) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    STRONG    47%    0% / 5% / 47%</t>
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG    52%    0% / 6% / 42%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    AVERAGE    0%    35% / 62% / 2%</t>
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    41% / 56% / 2%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NEWCOMER   0%    89% / 10% / 0%</t>
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    EXPERT    74%    0% / 3% / 22%</t>
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EXPERT    76%    0% / 1% / 22%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    STRONG     0%    12% / 54% / 33%</t>
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG     0%    16% / 57% / 26%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    AVERAGE    0%    76% / 23% / 0%</t>
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    89% / 11% / 0%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62"/>
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    99% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="32" t="inlineStr">
         <is>
           <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE UNHEARING       51% / 0%</t>
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNHEARING       56% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  58% / 0%</t>
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  49% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE METRONOME       45% / 0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE METRONOME       53% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>MUSICIANS (the NORMAL STRONG runs above) : WIN PERCENT  WITH them in the band / WITHOUT them</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAGANINI    52% / 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  QUANTZ      48% / 58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PFUNDT      51% / 53%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DUPORT      55% / 47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PUNTO       53% / 50%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8613,7 +9468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="32" min="1" max="1"/>
@@ -8708,6 +9563,18 @@
       <c r="B8" s="32" t="inlineStr">
         <is>
           <t>แท็บ Turn Battle / Turn Enemies / Turn Conductors / Turn Sim = การต่อสู้แบบผลัดตา (branch Alpha7, 19 ต.ค.) สร้างจากโค้ดด้วยสคริปต์ ค่าในแท็บอื่นเป็นของดวลเดิม (Alpha6) ที่ยังอยู่ในโค้ดตอนปิด TurnBattleOn</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Beta1</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>แท็บ Turn Skills (29 ต.ค.) คือสกิลกับความสามารถติดตัวของนักดนตรีแต่ละคน ชุดใหม่ของ 5 คนอยู่บนสุด สร้างจากโค้ดด้วยสคริปต์ docs/turn_balance_tabs.py เหมือนแท็บ Turn อื่น</t>
         </is>
       </c>
     </row>
@@ -8727,7 +9594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -8759,3111 +9626,3199 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>Turn Battle On</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>TurnBattleOn</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>LifeWord</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "LIFE" : "BREATH"</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>LifeWordLower</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "life" : "breath"</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>TurnHp</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>{ 45, 39, 54 }</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>TurnSpeed</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>{ 5, 7, 3 }</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>TurnEnemyHp</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>{ 50, 120, 250 }</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>TurnEnemySpeed</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>{ 4, 4, 4 }</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>TurnAttackPerPower</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>TurnPerfect</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>right way, on time</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>TurnGood</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>right way, a little off time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>TurnMiss</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>the wrong way, too early, too late or no swipe</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>BandSize</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>the musicians a run picks at its start, every one of them plays every fight</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>TurnAttackScale</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>TurnAttackOffBeat</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>ATTACK : the OFF-BEAT it adds</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>TurnCutInSpeed</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>TurnCutInAfter</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>right after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>TurnPackEarly</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>{ 1, 2, 3 }</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>an ENCOUNTER in the first half of the floor</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>TurnPackLate</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="32" t="inlineStr">
         <is>
           <t>{ 2, 3, 4 }</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="32" t="inlineStr">
         <is>
           <t>in the second half</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>TurnEliteEscort</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>{ 0, 1, 2 }</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="32" t="inlineStr">
         <is>
           <t>ordinary enemies that come with an ELITE</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>TurnBossEscort</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="32" t="inlineStr">
         <is>
           <t>{ 0, 1, 2 }</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="32" t="inlineStr">
         <is>
           <t>and with the BOSS</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="32" t="inlineStr">
         <is>
           <t>MaestroTurnDamage</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="32" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>TurnShardsPerEscort</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="32" t="inlineStr">
         <is>
           <t>shards for each enemy beyond the first</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="32" t="inlineStr">
         <is>
           <t>TurnFloorLife</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>{ 1.6, 2.1, 2.7 }</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="32" t="inlineStr">
         <is>
           <t>TurnFloorDamage</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="32" t="inlineStr">
         <is>
           <t>{ 1, 1.2, 1.4 }</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="32" t="inlineStr">
         <is>
           <t>TurnFillsGapsScale</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="32" t="inlineStr">
         <is>
           <t>DEAD AIR : a missed note</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>TurnLullHeal</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>THE LULL : life back on its humming turn</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>TurnLullEvery</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="32" t="inlineStr">
         <is>
           <t>every this many turns</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
         <is>
           <t>TurnFastGap</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="32" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="32" t="inlineStr">
         <is>
           <t>REQUIEM : the gap between notes below half life</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="32" t="inlineStr">
         <is>
           <t>TurnBargainSteal</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="32" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING : breath taken by each attack</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="32" t="inlineStr">
         <is>
           <t>TurnRoomToneKeep</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="32" t="inlineStr">
         <is>
           <t>TurnFeltHandBreath</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>THE DAMPER (FELT HAND, 29 Oct) : an ATTACK gives this much less BREATH while it stands (until CALL went</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="32" t="inlineStr">
         <is>
           <t>TurnTwiceFirst</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="32" t="inlineStr">
         <is>
           <t>STUTTER : cuts in after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="32" t="inlineStr">
         <is>
           <t>TurnTwiceSecond</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>and again after this many</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="32" t="inlineStr">
         <is>
           <t>TurnByTouchMost</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>TurnCourtKeep</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="32" t="inlineStr">
         <is>
           <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
         <is>
           <t>TurnStaffEvery</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="32" t="inlineStr">
         <is>
           <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="32" t="inlineStr">
         <is>
           <t>TurnStaffPower</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="32" t="inlineStr">
         <is>
           <t>that one note hits everyone this much harder</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="32" t="inlineStr">
         <is>
           <t>TurnThorns</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="32" t="inlineStr">
         <is>
           <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="32" t="inlineStr">
         <is>
           <t>TurnPracticeHp</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="32" t="inlineStr">
         <is>
           <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="32" t="inlineStr">
         <is>
           <t>TurnPracticeSpeed</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="32" t="inlineStr">
         <is>
           <t>TurnPracticePower</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="32" t="inlineStr">
         <is>
           <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>TurnNotesMin</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="32" t="inlineStr">
         <is>
           <t>{ 1, 2, 3 }</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="32" t="inlineStr">
         <is>
           <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="32" t="inlineStr">
         <is>
           <t>TurnNotesMax</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="32" t="inlineStr">
         <is>
           <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="32" t="inlineStr">
         <is>
           <t>TurnSmallNotesMin</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="32" t="inlineStr">
         <is>
           <t>{ 1, 1, 2 }</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="32" t="inlineStr">
         <is>
           <t>ordinary enemies</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="32" t="inlineStr">
         <is>
           <t>TurnSmallNotesMax</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="32" t="inlineStr">
         <is>
           <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="32" t="inlineStr">
         <is>
           <t>TurnNoteDamage</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>PARRY</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="32" t="inlineStr">
         <is>
           <t>TurnParryGoodKeep</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="32" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="32" t="inlineStr">
         <is>
           <t>TurnBreathMax</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="32" t="inlineStr">
         <is>
           <t>TurnBreathStart</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="32" t="inlineStr">
         <is>
           <t>TurnBreathPerAttack</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="32" t="inlineStr">
         <is>
           <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="32" t="inlineStr">
         <is>
           <t>TurnBreathPerParry</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="32" t="inlineStr">
         <is>
           <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t>KNOCKED OUT</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="32" t="inlineStr">
         <is>
           <t>TurnReviveHp</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="32" t="inlineStr">
         <is>
           <t>TurnOffBeatMax</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="32" t="inlineStr">
         <is>
           <t>TurnParryOffBeat</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="32" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="32" t="inlineStr">
         <is>
           <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="32" t="inlineStr">
         <is>
           <t>TurnOffBeatScale</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="32" t="inlineStr">
         <is>
           <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="32" t="inlineStr">
         <is>
           <t>TurnDissonanceMost</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="32" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="32" t="inlineStr">
         <is>
           <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="32" t="inlineStr">
         <is>
           <t>TurnCrescendoStep</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="32" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="32" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="32" t="inlineStr">
         <is>
           <t>TurnCrescendoMost</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="32" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="32" t="inlineStr">
         <is>
           <t>TurnMuteTurns</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="32" t="inlineStr">
         <is>
           <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>TurnGuardKeep</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="32" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="32" t="inlineStr">
         <is>
           <t>TurnCounterScale</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="32" t="inlineStr">
         <is>
           <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="32" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="32" t="inlineStr">
         <is>
           <t>TurnCadenzaCounter</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="32" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="32" t="inlineStr">
         <is>
           <t>TurnCadenzaEvery</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="32" t="inlineStr">
         <is>
           <t>TurnCadenzaPower</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="32" t="inlineStr">
         <is>
           <t>TurnHoldBase</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="32" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="32" t="inlineStr">
         <is>
           <t>TurnHoldGain</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="32" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="32" t="inlineStr">
         <is>
           <t>TurnRollPerfect</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="32" t="inlineStr">
         <is>
           <t>TurnRollGood</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="32" t="inlineStr">
         <is>
           <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="32" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="32" t="inlineStr">
         <is>
           <t>MaestroTurnRollGood</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="32" t="inlineStr">
         <is>
           <t>Conductors</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="32" t="inlineStr">
         <is>
           <t>TurnSignatureNeed</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="32" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="32" t="inlineStr">
         <is>
           <t>PlaytestSignatureNeed</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="32" t="inlineStr">
         <is>
           <t>TurnBeethovenMost</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="32" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="32" t="inlineStr">
         <is>
           <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="32" t="inlineStr">
         <is>
           <t>TurnBoltDamage</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="32" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="32" t="inlineStr">
         <is>
           <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="32" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="32" t="inlineStr">
         <is>
           <t>TurnMozartRun</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="32" t="inlineStr">
         <is>
           <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="32" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="32" t="inlineStr">
         <is>
           <t>TurnFeatherPerStroke</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="32" t="inlineStr">
         <is>
           <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="32" t="inlineStr">
         <is>
           <t>TurnLockedTempoWindow</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="32" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="32" t="inlineStr">
         <is>
           <t>LOCKED TEMPO : seconds added to the PERFECT window of skills and the SIGNATURE, never</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>TurnFugueScale</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="32" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="32" t="inlineStr">
         <is>
           <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="32" t="inlineStr">
         <is>
           <t>TurnPaganiniLife</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now)</t>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>TurnCapricePrice</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="32" t="inlineStr">
         <is>
           <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="32" t="inlineStr">
         <is>
           <t>TurnCapricePerStroke</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="32" t="inlineStr">
         <is>
           <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="32" t="inlineStr">
         <is>
           <t>TurnLullyWindow</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="32" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="32" t="inlineStr">
         <is>
           <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="32" t="inlineStr">
         <is>
           <t>TurnSunHeal</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent. Step 15 : 8 -&gt; 6)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>TurnFannyScale</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="32" t="inlineStr">
         <is>
           <t>FANNY MENDELSSOHN AND ???'s PASSIVE : FANNY's voice hits this much harder</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="32" t="inlineStr">
         <is>
           <t>TurnFelixHeal</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="32" t="inlineStr">
         <is>
           <t>FELIX's voice heals this much more</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>TurnFelixCrescendo</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="32" t="inlineStr">
         <is>
           <t>and gives this much more CRESCENDO</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="32" t="inlineStr">
         <is>
           <t>TurnDuetDamage</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="32" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="32" t="inlineStr">
         <is>
           <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, FANNY 46 percent)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="32" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="32" t="inlineStr">
         <is>
           <t>TurnDuetHeal</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="32" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="32" t="inlineStr">
         <is>
           <t>and life back for every musician</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="32" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>TurnCountsWindow</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>TurnBreathControl</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="inlineStr">
+        <is>
+          <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B91" s="32" t="inlineStr">
+        <is>
+          <t>TurnHandCut</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" s="32" t="inlineStr">
+        <is>
+          <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>TurnHandLeast</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
+        <is>
+          <t>never fewer notes left than this (its point is a long phrase,</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B93" s="32" t="inlineStr">
+        <is>
+          <t>TurnScarCrescendo</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" s="32" t="inlineStr">
+        <is>
+          <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B94" s="32" t="inlineStr">
+        <is>
+          <t>TurnHuntingCallScale</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="inlineStr">
+        <is>
+          <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="inlineStr">
+        <is>
+          <t>TurnLessonWindow</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>COUNTS ALOUD (PAGANINI) : seconds added to their PERFECT window</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="D95" s="32" t="inlineStr">
+        <is>
+          <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="32" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>TurnQuietScale</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>TurnLessonShakes</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="inlineStr">
+        <is>
+          <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B97" s="32" t="inlineStr">
+        <is>
+          <t>TurnLessonScale</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D97" s="32" t="inlineStr">
+        <is>
+          <t>and the skill plays this much harder</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B98" s="32" t="inlineStr">
+        <is>
+          <t>TurnShieldKeep</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D98" s="32" t="inlineStr">
+        <is>
+          <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>Musician Traits in the turn battle</t>
+        </is>
+      </c>
+      <c r="B99" s="32" t="inlineStr">
+        <is>
+          <t>TurnChakramRepeat</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D99" s="32" t="inlineStr">
+        <is>
+          <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>The hidden musicians</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>TurnByEarScale</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>THE QUIET PART (QUANTZ) : against an enemy whose next attack is aimed at someone else</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>TurnMomentumMost</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="D100" s="32" t="inlineStr">
+        <is>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>The hidden musicians</t>
+        </is>
+      </c>
+      <c r="B101" s="32" t="inlineStr">
+        <is>
+          <t>TurnHeldNoteShare</t>
+        </is>
+      </c>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D101" s="32" t="inlineStr">
+        <is>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>The hidden musicians</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>TurnStepBetterScale</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="inlineStr">
+        <is>
+          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>The hidden musicians</t>
+        </is>
+      </c>
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>TurnLongNotes</t>
+        </is>
+      </c>
+      <c r="C103" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>MOMENTUM (PFUNDT) : power gained by hits in a row, at most</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>TurnByEarScale</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
+      <c r="D103" s="32" t="inlineStr">
+        <is>
+          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>The hidden musicians</t>
+        </is>
+      </c>
+      <c r="B104" s="32" t="inlineStr">
+        <is>
+          <t>TurnThunderSoften</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D104" s="32" t="inlineStr">
+        <is>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B105" s="32" t="inlineStr">
+        <is>
+          <t>EchoesPerWin</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D105" s="32" t="inlineStr">
+        <is>
+          <t>each fight won</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>EchoesPerFloor</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>each floor cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>EchoesRunWon</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D107" s="32" t="inlineStr">
+        <is>
+          <t>the whole run won</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>EchoesMaestro</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>TurnHeldNoteShare</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TurnStepBetterScale</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="D108" s="32" t="inlineStr">
+        <is>
+          <t>MAESTRO pays more</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>ArchiveLifePerLevel</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D109" s="32" t="inlineStr">
+        <is>
+          <t>STRONGER BAND</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>ArchiveBreathPerLevel</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="inlineStr">
+        <is>
+          <t>DEEP BREATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>ArchiveSignaturePerLevel</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D111" s="32" t="inlineStr">
+        <is>
+          <t>WARM UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B112" s="32" t="inlineStr">
+        <is>
+          <t>ArchiveShardsPerLevel</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D112" s="32" t="inlineStr">
+        <is>
+          <t>SAVINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="32" t="inlineStr">
+        <is>
+          <t>ARCHIVE</t>
+        </is>
+      </c>
+      <c r="B113" s="32" t="inlineStr">
+        <is>
+          <t>ArchiveFirstChairTier</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="inlineStr">
+        <is>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B114" s="32" t="inlineStr">
+        <is>
+          <t>TurnReedCaseHeal</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D114" s="32" t="inlineStr">
+        <is>
+          <t>REED CASE : wind players' healing</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B115" s="32" t="inlineStr">
+        <is>
+          <t>TurnSpareSticksOffBeat</t>
+        </is>
+      </c>
+      <c r="C115" s="32" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D115" s="32" t="inlineStr">
+        <is>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B116" s="32" t="inlineStr">
+        <is>
+          <t>TurnPianissimoBreath</t>
+        </is>
+      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" s="32" t="inlineStr">
+        <is>
+          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B117" s="32" t="inlineStr">
+        <is>
+          <t>TurnBreathMarkStart</t>
+        </is>
+      </c>
+      <c r="C117" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D117" s="32" t="inlineStr">
+        <is>
+          <t>BREATH MARK : more breath at the start of a fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B118" s="32" t="inlineStr">
+        <is>
+          <t>TurnTuttiScale</t>
+        </is>
+      </c>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="D118" s="32" t="inlineStr">
+        <is>
+          <t>TUTTI : skills that reach everyone</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B119" s="32" t="inlineStr">
+        <is>
+          <t>TurnRubatoMiss</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="inlineStr">
+        <is>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B120" s="32" t="inlineStr">
+        <is>
+          <t>TurnCrescendoStart</t>
+        </is>
+      </c>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D120" s="32" t="inlineStr">
+        <is>
+          <t>CRESCENDO : stacks on every musician at the start</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B121" s="32" t="inlineStr">
+        <is>
+          <t>TurnSforzandoScale</t>
+        </is>
+      </c>
+      <c r="C121" s="32" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>TurnLongNotes</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
+      <c r="D121" s="32" t="inlineStr">
+        <is>
+          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B122" s="32" t="inlineStr">
+        <is>
+          <t>TurnOvertureScale</t>
+        </is>
+      </c>
+      <c r="C122" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D122" s="32" t="inlineStr">
+        <is>
+          <t>OVERTURE : the band's first hit of a fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B123" s="32" t="inlineStr">
+        <is>
+          <t>TurnCounterpointScale</t>
+        </is>
+      </c>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D123" s="32" t="inlineStr">
+        <is>
+          <t>COUNTERPOINT : the COUNTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B124" s="32" t="inlineStr">
+        <is>
+          <t>TurnAccelerandoShakes</t>
+        </is>
+      </c>
+      <c r="C124" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D124" s="32" t="inlineStr">
+        <is>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B125" s="32" t="inlineStr">
+        <is>
+          <t>TurnGraceTimes</t>
+        </is>
+      </c>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D125" s="32" t="inlineStr">
+        <is>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B126" s="32" t="inlineStr">
+        <is>
+          <t>TurnMarcatoOffBeat</t>
+        </is>
+      </c>
+      <c r="C126" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D126" s="32" t="inlineStr">
+        <is>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B127" s="32" t="inlineStr">
+        <is>
+          <t>TurnConBrioNeed</t>
+        </is>
+      </c>
+      <c r="C127" s="32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D127" s="32" t="inlineStr">
+        <is>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B128" s="32" t="inlineStr">
+        <is>
+          <t>TurnCodaBelow</t>
+        </is>
+      </c>
+      <c r="C128" s="32" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D128" s="32" t="inlineStr">
+        <is>
+          <t>CODA : an enemy under this share of its life</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="32" t="inlineStr">
+        <is>
+          <t>Turn Motifs</t>
+        </is>
+      </c>
+      <c r="B129" s="32" t="inlineStr">
+        <is>
+          <t>TurnCodaScale</t>
+        </is>
+      </c>
+      <c r="C129" s="32" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D129" s="32" t="inlineStr">
+        <is>
+          <t>takes this much more</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="32" t="inlineStr">
+        <is>
+          <t>ONE BAR motifs</t>
+        </is>
+      </c>
+      <c r="B130" s="32" t="inlineStr">
+        <is>
+          <t>TurnDownbeatScale</t>
+        </is>
+      </c>
+      <c r="C130" s="32" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D130" s="32" t="inlineStr">
+        <is>
+          <t>DOWNBEAT : the first move of a bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="32" t="inlineStr">
+        <is>
+          <t>ONE BAR motifs</t>
+        </is>
+      </c>
+      <c r="B131" s="32" t="inlineStr">
+        <is>
+          <t>TurnEntranceScale</t>
+        </is>
+      </c>
+      <c r="C131" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D131" s="32" t="inlineStr">
+        <is>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="32" t="inlineStr">
+        <is>
+          <t>ONE BAR motifs</t>
+        </is>
+      </c>
+      <c r="B132" s="32" t="inlineStr">
+        <is>
+          <t>TurnGreenRoomHeal</t>
+        </is>
+      </c>
+      <c r="C132" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TurnFourBarsEvery</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>FOUR BARS STRAIGHT (DUPORT) : every this many ATTACKs</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TurnFourBarsScale</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
+      <c r="D132" s="32" t="inlineStr">
+        <is>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="32" t="inlineStr">
+        <is>
+          <t>ONE BAR motifs</t>
+        </is>
+      </c>
+      <c r="B133" s="32" t="inlineStr">
+        <is>
+          <t>TurnUnisonScale</t>
+        </is>
+      </c>
+      <c r="C133" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>hits this much harder</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>TurnLateBonus</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>FASHIONABLY LATE (PUNTO) : seconds after the GOOD window a late stroke still counts</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Musician Traits in the turn battle</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>TurnThunderSoften</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>EchoesPerWin</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>each fight won</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>EchoesPerFloor</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>each floor cleared</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>EchoesRunWon</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>the whole run won</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>EchoesMaestro</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>MAESTRO pays more</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>ArchiveLifePerLevel</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>STRONGER BAND</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>ArchiveBreathPerLevel</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>DEEP BREATH</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>ArchiveSignaturePerLevel</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>WARM UP</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>ArchiveShardsPerLevel</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>SAVINGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>ARCHIVE</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>ArchiveFirstChairTier</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>TurnReedCaseHeal</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>REED CASE : wind players' healing</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>TurnSpareSticksOffBeat</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>TurnPianissimoBreath</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>TurnBreathMarkStart</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>TurnTuttiScale</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>TUTTI : skills that reach everyone</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>TurnRubatoMiss</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>TurnCrescendoStart</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TurnSforzandoScale</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="D133" s="32" t="inlineStr">
+        <is>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B134" s="32" t="inlineStr">
+        <is>
+          <t>TurnRingTime</t>
+        </is>
+      </c>
+      <c r="C134" s="32" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D134" s="32" t="inlineStr">
+        <is>
+          <t>from a note showing to the moment to swipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B135" s="32" t="inlineStr">
+        <is>
+          <t>TurnLateReveal</t>
+        </is>
+      </c>
+      <c r="C135" s="32" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D135" s="32" t="inlineStr">
+        <is>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B136" s="32" t="inlineStr">
+        <is>
+          <t>MaestroTurnRingTime</t>
+        </is>
+      </c>
+      <c r="C136" s="32" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D136" s="32" t="inlineStr">
+        <is>
+          <t>MAESTRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B137" s="32" t="inlineStr">
+        <is>
+          <t>TurnNoteGap</t>
+        </is>
+      </c>
+      <c r="C137" s="32" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D137" s="32" t="inlineStr">
+        <is>
+          <t>between the notes of one enemy attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B138" s="32" t="inlineStr">
+        <is>
+          <t>TurnPause</t>
+        </is>
+      </c>
+      <c r="C138" s="32" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D138" s="32" t="inlineStr">
+        <is>
+          <t>after a turn, before the next one starts</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B139" s="32" t="inlineStr">
+        <is>
+          <t>TurnHitStop</t>
+        </is>
+      </c>
+      <c r="C139" s="32" t="inlineStr">
+        <is>
+          <t>0.075</t>
+        </is>
+      </c>
+      <c r="D139" s="32" t="inlineStr">
+        <is>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B140" s="32" t="inlineStr">
+        <is>
+          <t>TurnStrikeTime</t>
+        </is>
+      </c>
+      <c r="C140" s="32" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="D140" s="32" t="inlineStr">
+        <is>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B141" s="32" t="inlineStr">
+        <is>
+          <t>TurnStrikeImpact</t>
+        </is>
+      </c>
+      <c r="C141" s="32" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="D141" s="32" t="inlineStr">
+        <is>
+          <t>when in it the hit lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B142" s="32" t="inlineStr">
+        <is>
+          <t>TurnStrikeStop</t>
+        </is>
+      </c>
+      <c r="C142" s="32" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="D142" s="32" t="inlineStr">
+        <is>
+          <t>the freeze when it lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B143" s="32" t="inlineStr">
+        <is>
+          <t>TurnNumberTime</t>
+        </is>
+      </c>
+      <c r="C143" s="32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D143" s="32" t="inlineStr">
+        <is>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B144" s="32" t="inlineStr">
+        <is>
+          <t>TurnBigHit</t>
+        </is>
+      </c>
+      <c r="C144" s="32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D144" s="32" t="inlineStr">
+        <is>
+          <t>from this much damage it is drawn bigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B145" s="32" t="inlineStr">
+        <is>
+          <t>TurnNumberCell</t>
+        </is>
+      </c>
+      <c r="C145" s="32" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D145" s="32" t="inlineStr">
+        <is>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B146" s="32" t="inlineStr">
+        <is>
+          <t>TurnNumberBigCell</t>
+        </is>
+      </c>
+      <c r="C146" s="32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D146" s="32" t="inlineStr">
+        <is>
+          <t>the same for a big hit (was 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B147" s="32" t="inlineStr">
+        <is>
+          <t>TurnDissolveTime</t>
+        </is>
+      </c>
+      <c r="C147" s="32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D147" s="32" t="inlineStr">
+        <is>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B148" s="32" t="inlineStr">
+        <is>
+          <t>TurnCutInTime</t>
+        </is>
+      </c>
+      <c r="C148" s="32" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TurnOvertureScale</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>TurnCounterpointScale</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>COUNTERPOINT : the COUNTER</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TurnAccelerandoShakes</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TurnGraceTimes</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>TurnMarcatoOffBeat</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TurnConBrioNeed</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>TurnCodaBelow</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>CODA : an enemy under this share of its life</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Turn Motifs</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TurnCodaScale</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>takes this much more</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ONE BAR motifs</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>TurnDownbeatScale</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>DOWNBEAT : the first move of a bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>ONE BAR motifs</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>TurnEntranceScale</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>ONE BAR motifs</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>TurnGreenRoomHeal</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>ONE BAR motifs</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TurnUnisonScale</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="D148" s="32" t="inlineStr">
+        <is>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="32" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>TurnRingTime</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>from a note showing to the moment to swipe</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="B149" s="32" t="inlineStr">
+        <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C149" s="32" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D149" s="32" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="32" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>TurnLateReveal</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="B150" s="32" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C150" s="32" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D150" s="32" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="32" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>MaestroTurnRingTime</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
+      <c r="B151" s="32" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C151" s="32" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D151" s="32" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B152" s="32" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C152" s="32" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>MAESTRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="D152" s="32" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="32" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>TurnNoteGap</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>between the notes of one enemy attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>TurnPause</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>after a turn, before the next one starts</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>TurnHitStop</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.075</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>TurnStrikeTime</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>TurnStrikeImpact</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>when in it the hit lands</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>TurnStrikeStop</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>the freeze when it lands</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>TurnNumberTime</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>TurnBigHit</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>from this much damage it is drawn bigger</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>TurnNumberCell</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>TurnNumberBigCell</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>the same for a big hit (was 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>TurnDissolveTime</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>TurnCutInTime</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>TurnKillStop</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>the freeze when an enemy falls silent</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>TurnEndTime</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>the win or lose banner stays this long</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>TurnSparkGap</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>a spark comes this soon after the note before it</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>TurnHoldTime</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Turn Feel</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
+      <c r="B153" s="32" t="inlineStr">
         <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C153" s="32" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D153" s="32" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -11941,729 +12896,729 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>HUSH</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>D U, L R D</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>ECHO FADES (2)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>Each note that gets through adds 1 DISSONANCE.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" s="32" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>DEAD AIR</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>L R, D D U</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>FILLS THE GAPS (2)</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>A note you miss hits 50 percent harder.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" s="32" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>THE LULL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="32" t="inlineStr">
         <is>
           <t>D D, U D U</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t>LULLABY (2)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="32" t="inlineStr">
         <is>
           <t>Every third turn it hums instead of attacking and gets back 12 life.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" s="32" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>L R, U D L</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="32" t="inlineStr">
         <is>
           <t>FALSE NOTES (2)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="32" t="inlineStr">
         <is>
           <t>One note of each attack hides its arrow behind a ? until late.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>THE MUTE CHOIR</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>D D U, L R L R</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>SILENT MOUTHS (1)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>A note you miss takes the target's skills away for a turn.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>WHITE NOISE</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>L R L R, U D U D</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>NO REST (1)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>One note more in every attack, and parrying it gives no BREATH.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>REQUIEM</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>D L R U, L R L R</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>UNFINISHED (1)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>Below half life it swaps left and right and plays faster.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>THE NAMELESS MASTER</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
         <is>
           <t>D U L, R L D U</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>ANSWER BETTER (1)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>It answers with the notes of the last skill your band played.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>R R L, U D U D</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>THE BARGAIN (1)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>Each of its attacks steals 1 BREATH.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>ROOM TONE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="32" t="inlineStr">
         <is>
           <t>D, U D</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t>HOLDS THE ROOM (2)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>While it stands, the other enemies take 30 percent less.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>THE CUE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>R L, U</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t>ON CUE (2)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>It always strikes the musician who played the last skill.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>THE DAMPER</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>D D, L R</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>FELT HAND (2)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>While it stands, an ATTACK gives 1 less BREATH.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>STUTTER</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>L, R, U</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>TWICE A BAR (2)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>It cuts in twice a bar, after the 1st and the 3rd move, one note each time.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>THE ROUND</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>D D D, L R L R</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>FIRST IN LINE (1)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>It always strikes the musician who plays first in the bar.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>THE DEAF CROWN</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="32" t="inlineStr">
         <is>
           <t>U U U D, L R D</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>DECREE (1)</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>Each bar it forbids SKILLS or ATTACKS, and breaking it hurts. It never takes a COUNTER.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>THE STAFF</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="32" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>D D D, D L D R</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>THE COURT (1)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>While its court stands it takes half. Every third attack it strikes the floor and hits everyone.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>THE BLIND CANTOR</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="32" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>D U D U, L R L R</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t>BY TOUCH (1)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>It strikes the seats in turn, front to back. A note you miss comes back in its next attack.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1278,727 +1278,727 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>PAGANINI (String, power 5)</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>CAPRICE</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D2" s="32" t="n">
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="32" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>L R L R</t>
         </is>
       </c>
-      <c r="G2" s="32" t="n">
+      <c r="G2" t="n">
         <v>0.4</v>
       </c>
-      <c r="H2" s="32" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="32" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4 quick cuts. Each adds 1 DISSONANCE.</t>
         </is>
       </c>
-      <c r="O2" s="32" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>THE DEVIL'S BARGAIN : Short of BREATH, their skills take 6 life for each BREATH missing.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>IL CANNONE</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D3" s="32" t="n">
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>HOLD L</t>
         </is>
       </c>
-      <c r="G3" s="32" t="n">
+      <c r="G3" t="n">
         <v>1.5</v>
       </c>
-      <c r="N3" s="32" t="inlineStr">
-        <is>
-          <t>One big held shot. Hold it = harder.</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>One big held shot. Hold it = harder. Goes through GUARD.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>QUANTZ (Wind, power 4)</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SOFT AIR</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="32" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>AllAllies</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>D U</t>
         </is>
       </c>
-      <c r="I4" s="32" t="n">
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="32" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Heals the whole band 3 per note.</t>
         </is>
       </c>
-      <c r="O4" s="32" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>BREATH CONTROL : Their ATTACK gives 1 BREATH more.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>THE LESSON</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Boost</t>
         </is>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>U D</t>
         </is>
       </c>
-      <c r="M5" s="32" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>LESSON</t>
         </is>
       </c>
-      <c r="N5" s="32" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>A friend's next skill : wider PERFECT, harder hits.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>PFUNDT (Percussion, power 6)</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TIMPANI ROLL</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ROLL</t>
         </is>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="32" t="n">
+      <c r="L6" t="n">
         <v>30</v>
       </c>
-      <c r="N6" s="32" t="inlineStr">
-        <is>
-          <t>Shake fast. Big OFF-BEAT.</t>
-        </is>
-      </c>
-      <c r="O6" s="32" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Shake fast. Big OFF-BEAT. Breaks a CHARGE.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>TURN OF THE HAND : An enemy their skill hits plays 1 note fewer next time (2 at least).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>THUNDER CALL</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Defend</t>
         </is>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="M7" s="32" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>GUARD TAUNT</t>
         </is>
       </c>
-      <c r="N7" s="32" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Enemies aim at PFUNDT, who takes half damage.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>DUPORT (String, power 6)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>SHIELD</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Defend</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>HOLD R</t>
         </is>
       </c>
-      <c r="M8" s="32" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>SHIELD</t>
         </is>
       </c>
-      <c r="N8" s="32" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Guard a friend : their hits land on DUPORT, halved.</t>
         </is>
       </c>
-      <c r="O8" s="32" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>THE SCAR : Every attack that hurts them gives 1 CRESCENDO.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>LANCE</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>R R</t>
         </is>
       </c>
-      <c r="G9" s="32" t="n">
+      <c r="G9" t="n">
         <v>0.7</v>
       </c>
-      <c r="M9" s="32" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>x2 WHEN HIT</t>
         </is>
       </c>
-      <c r="N9" s="32" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2 thrusts. Twice as hard if DUPORT was just hit.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>PUNTO (Wind, power 5)</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>FANFARE</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Boost</t>
         </is>
       </c>
-      <c r="D10" s="32" t="n">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>AllAllies</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>L L</t>
         </is>
       </c>
-      <c r="J10" s="32" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" s="32" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>The band hits harder : 1 CRESCENDO per note.</t>
         </is>
       </c>
-      <c r="O10" s="32" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>THE HUNTING CALL : The musician who plays right after them in the bar hits harder.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>CHAKRAM</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>L R L</t>
         </is>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="32" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>BOUNCE 3</t>
         </is>
       </c>
-      <c r="N11" s="32" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>3 throws, a new enemy each. Hit again = half.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MALI (String, power 5) hidden</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>BY EAR</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>D SPARK</t>
         </is>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" t="n">
         <v>0.8</v>
       </c>
-      <c r="H12" s="32" t="n">
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="32" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>A hit and a spark. Each adds 1 DISSONANCE.</t>
         </is>
       </c>
-      <c r="O12" s="32" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>BY EAR : Hits 50 percent harder against an enemy that is OFF-BEAT.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>SLIDE</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>U D U D</t>
         </is>
       </c>
-      <c r="G13" s="32" t="n">
+      <c r="G13" t="n">
         <v>0.4</v>
       </c>
-      <c r="H13" s="32" t="n">
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="N13" s="32" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>4 notes up and down. Each adds 1 DISSONANCE.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>CHAI (Wind, power 4) hidden</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>HELD NOTE</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Ally</t>
         </is>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>HOLD R</t>
         </is>
       </c>
-      <c r="I14" s="32" t="n">
+      <c r="I14" t="n">
         <v>9</v>
       </c>
-      <c r="N14" s="32" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Heals one musician. Hold it = more.</t>
         </is>
       </c>
-      <c r="O14" s="32" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>HELD NOTE : His ATTACK rings on : a second hit for 40 percent.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>CIRCULAR</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Heal</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="32" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>AllAllies</t>
         </is>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>ROLL</t>
         </is>
       </c>
-      <c r="I15" s="32" t="n">
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="32" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
-      <c r="N15" s="32" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Shake fast. Heals everyone 3, 3 BREATH back.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>NUAN (Percussion, power 6) hidden</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>RUN</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>L R L</t>
         </is>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" t="n">
         <v>0.5</v>
       </c>
-      <c r="L16" s="32" t="n">
+      <c r="L16" t="n">
         <v>12</v>
       </c>
-      <c r="N16" s="32" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>3 big hits. OFF-BEAT each.</t>
         </is>
       </c>
-      <c r="O16" s="32" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>ONE STEP BETTER : Hits 30 percent harder against an enemy whose next attack has 3 notes or more.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ONE STEP</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="32" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>L SPARK</t>
         </is>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" t="n">
         <v>0.7</v>
       </c>
-      <c r="L17" s="32" t="n">
+      <c r="L17" t="n">
         <v>12</v>
       </c>
-      <c r="N17" s="32" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>A big hit and a spark. OFF-BEAT each.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>BORIS (Percussion, power 7) hidden</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>THE FLOOR</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>AllEnemies</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>HOLD D</t>
         </is>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" s="32" t="n">
+      <c r="L18" t="n">
         <v>20</v>
       </c>
-      <c r="N18" s="32" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Hits every enemy. Hold it = harder.</t>
         </is>
       </c>
-      <c r="O18" s="32" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>THE WHOLE FLOOR : The PERFECT last note of his skills takes 2 off each note of the enemy's next attack.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>THUNDER</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D19" s="32" t="n">
+      <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="32" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Enemy</t>
         </is>
       </c>
-      <c r="F19" s="32" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>D D ROLL</t>
         </is>
       </c>
-      <c r="G19" s="32" t="n">
+      <c r="G19" t="n">
         <v>0.8</v>
       </c>
-      <c r="L19" s="32" t="n">
+      <c r="L19" t="n">
         <v>15</v>
       </c>
-      <c r="N19" s="32" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2 big hits and a roll. Big OFF-BEAT.</t>
         </is>
@@ -2297,481 +2297,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A73"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="33" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>turnsim.txt (--shots turnsim, Core/DebugShots.TurnSim.cs)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TACET TURN BATTLE BALANCE, ONE BAR  (200 fights per cell, 300 runs per player)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Players : timing spread FLAWLESS 0 / EXPERT 0.08 / STRONG 0.12 / AVERAGE 0.2 / NEWCOMER 0.3 seconds</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>FIGHTS at full life (the band of three) : WIN PERCENT  /  BARS  /  LIFE LOST PERCENT</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.1b   0%   LATE  100%  3.0b   0%   ELITE 100%  3.5b   0%   BOSS  100%  7.3b   0%   </t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.1b   0%   LATE  100%  3.1b   0%   ELITE 100%  3.8b   0%   BOSS  100%  7.3b   0%   </t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.6b   0%   LATE  100%  4.6b   1%   ELITE 100%  5.9b   0%   BOSS  100% 10.5b   1%   </t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.8b   0%   LATE  100%  4.8b   1%   ELITE 100%  6.0b   0%   BOSS  100% 10.5b   1%   </t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  6.2b   3%   LATE  100%  7.2b   2%   ELITE 100%  8.4b   1%   BOSS  100% 14.4b   3%   </t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  6.3b   3%   LATE  100%  7.4b   2%   ELITE 100%  9.0b   1%   BOSS  100% 14.4b   3%   </t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.3b   1%   LATE  100%  3.2b   4%   ELITE 100%  4.0b   3%   BOSS  100%  8.1b  11%   </t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.3b   1%   LATE  100%  3.3b   4%   ELITE 100%  4.2b   4%   BOSS  100%  8.0b  12%   </t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.0b   6%   LATE  100%  5.6b  11%   ELITE 100%  6.5b  13%   BOSS  100% 11.5b  24%   </t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.4b   7%   LATE  100%  5.6b   9%   ELITE 100%  6.8b  11%   BOSS   99% 11.7b  25%   </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  7.0b  15%   LATE  100%  8.1b  18%   ELITE 100%  9.6b  21%   BOSS   96% 16.3b  36%   </t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  7.1b  13%   LATE  100%  8.4b  18%   ELITE 100% 10.1b  20%   BOSS   98% 16.2b  37%   </t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.5b   4%   LATE  100%  3.8b  10%   ELITE 100%  4.7b  11%   BOSS   99%  9.3b  28%   </t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.5b   3%   LATE  100%  4.0b  10%   ELITE 100%  4.9b  10%   BOSS  100%  9.5b  28%   </t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  4.9b  15%   LATE  100%  6.5b  24%   ELITE 100%  8.0b  29%   BOSS   84% 13.9b  56%   </t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  5.1b  14%   LATE  100%  6.7b  23%   ELITE 100%  8.3b  25%   BOSS   82% 13.9b  58%   </t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  8.1b  29%   LATE   99% 10.1b  34%   ELITE  86% 12.8b  53%   BOSS   26% 14.3b  87%   </t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  8.4b  27%   LATE   99% 10.4b  34%   ELITE  91% 13.3b  49%   BOSS   30% 14.7b  87%   </t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.2b  11%   LATE  100%  5.2b  24%   ELITE  99%  6.7b  30%   BOSS   64% 12.1b  71%   </t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.3b   9%   LATE  100%  5.5b  23%   ELITE 100%  6.9b  26%   BOSS   63% 12.2b  71%   </t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  6.8b  37%   LATE   82%  9.2b  61%   ELITE  50% 11.0b  82%   BOSS    5%  9.7b  97%   </t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  7.1b  34%   LATE   83%  9.8b  58%   ELITE  60% 12.4b  74%   BOSS    7% 10.0b  97%   </t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  35%  9.3b  85%   LATE   11%  7.5b  95%   ELITE   0%  6.5b  99%   BOSS    0%  5.3b 100%   </t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  47% 10.2b  80%   LATE   15%  7.9b  93%   ELITE   1%  8.3b  99%   BOSS    0%  5.8b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.0b  19%   LATE   98%  6.9b  42%   ELITE  83%  9.6b  62%   BOSS   16% 11.0b  94%   </t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.1b  18%   LATE   99%  7.4b  42%   ELITE  91%  9.7b  51%   BOSS   15% 10.8b  94%   </t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  63%  9.0b  76%   LATE   11%  6.8b  96%   ELITE   0%  6.6b  99%   BOSS    0%  5.6b 100%   </t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  66%  9.6b  72%   LATE   12%  7.7b  96%   ELITE   2%  8.6b  99%   BOSS    0%  5.8b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.0b  99%   LATE    0%  3.7b 100%   ELITE   0%  3.7b 100%   BOSS    0%  3.4b 100%   </t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   0%  5.7b  99%   LATE    0%  3.9b 100%   ELITE   0%  4.5b 100%   BOSS    0%  3.5b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 24%  SKILLS 75%</t>
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>RANKS of the won fights above : S / A / B / C PERCENT  /  SHARDS SCALE</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">  FLAWLESS 100 /   0 /   0 /   0   x2.00</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EXPERT    40 /  53 /   5 /   0   x1.69</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EXPERT    41 /  52 /   5 /   0   x1.69</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STRONG     5 /  37 /  50 /   7   x1.36</t>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STRONG     5 /  36 /  50 /   7   x1.37</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AVERAGE    0 /   6 /  48 /  43   x1.16</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  AVERAGE    0 /   7 /  48 /  43   x1.16</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   1 /  23 /  75   x1.07</t>
-        </is>
-      </c>
-    </row>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEWCOMER   0 /   2 /  27 /  69   x1.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>EACH ENEMY leading its pack (normal floor 2 late, elite floor 2, boss floor 3) : WIN PERCENT / BARS  AVERAGE, then STRONG</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HUSH                   81%  9.2b    100%  6.4b    </t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HUSH                   80%  9.5b    100%  6.7b    </t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DEAD AIR               73%  9.1b    100%  6.5b    </t>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DEAD AIR               82%  9.9b    100%  6.7b    </t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE LULL               89%  10.4b    100%  7.1b    </t>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE LULL               86%  10.4b    100%  7.0b    </t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STATIC                 77%  9.0b    100%  6.4b    </t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STATIC                 79%  9.4b    100%  6.5b    </t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         66%  11.0b    100%  7.8b    </t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE MUTE CHOIR         82%  12.9b    100%  8.7b    </t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHITE NOISE            23%  9.2b    100%  7.6b    </t>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHITE NOISE            28%  9.2b    100%  7.8b    </t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REQUIEM                 0%  4.9b     21%  14.4b    </t>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  REQUIEM                 0%  5.2b     19%  14.6b    </t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.3b     89%  18.3b    </t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.2b     80%  17.9b    </t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.9b      6%  12.5b    </t>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.7b      4%  13.1b    </t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ROOM TONE              83%  9.5b    100%  6.5b    </t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROOM TONE              89%  9.7b    100%  6.8b    </t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE CUE                86%  9.9b    100%  6.6b    </t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE CUE                87%  10.1b    100%  6.8b    </t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DAMPER             77%  9.0b    100%  6.5b    </t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DAMPER             80%  10.1b    100%  6.9b    </t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STUTTER                87%  8.7b    100%  6.1b    </t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STUTTER                91%  9.3b    100%  6.3b    </t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE ROUND              36%  12.4b    100%  8.3b    </t>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE ROUND              67%  14.9b    100%  8.4b    </t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.4b      8%  15.2b    </t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.3b     12%  14.9b    </t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE STAFF               0%  5.4b     28%  16.1b    </t>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE STAFF               0%  5.9b     29%  15.9b    </t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.9b     26%  13.9b    </t>
-        </is>
-      </c>
-    </row>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.9b     26%  14.1b    </t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>RUNS (3 floors, life carried over, no motifs, Beethoven) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">  NORMAL</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    STRONG    52%    0% / 6% / 42%</t>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG    56%    0% / 8% / 34%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    AVERAGE    0%    41% / 56% / 2%</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    43% / 53% / 3%</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">  MAESTRO</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    EXPERT    76%    0% / 1% / 22%</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EXPERT    77%    0% / 4% / 18%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    STRONG     0%    16% / 57% / 26%</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    STRONG     0%    12% / 51% / 35%</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    AVERAGE    0%    89% / 11% / 0%</t>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AVERAGE    0%    83% / 16% / 0%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NEWCOMER   0%    99% / 0% / 0%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" s="32" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>CONDUCTORS (runs as above, NORMAL) : WIN PERCENT  STRONG / AVERAGE</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE UNHEARING       56% / 0%</t>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE UNHEARING       55% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  49% / 0%</t>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  54% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE METRONOME       53% / 0%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE METRONOME       49% / 0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
     <row r="68">
-      <c r="A68" s="32" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>MUSICIANS (the NORMAL STRONG runs above) : WIN PERCENT  WITH them in the band / WITHOUT them</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PAGANINI    52% / 51%</t>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PAGANINI    50% / 63%</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  QUANTZ      48% / 58%</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  QUANTZ      55% / 57%</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PFUNDT      51% / 53%</t>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PFUNDT      56% / 55%</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DUPORT      55% / 47%</t>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DUPORT      56% / 54%</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  PUNTO       53% / 50%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PUNTO       60% / 47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9594,7 +9601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -9626,3199 +9633,3243 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Turn Battle On</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TurnBattleOn</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>LifeWord</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "LIFE" : "BREATH"</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Life Word</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>LifeWordLower</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>TurnBattleOn ? "life" : "breath"</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>TurnHp</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>{ 45, 39, 54 }</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Life and Speed of the band</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>TurnSpeed</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>{ 5, 7, 3 }</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>TurnEnemyHp</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>{ 50, 120, 250 }</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Life and Speed of TACET</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>TurnEnemySpeed</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>{ 4, 4, 4 }</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>TurnAttackPerPower</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>TurnPerfect</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>right way, on time</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>TurnGood</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>right way, a little off time</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>ONE RULE</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>TurnMiss</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>the wrong way, too early, too late or no swipe</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>BandSize</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>the musicians a run picks at its start, every one of them plays every fight</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>TurnAttackScale</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ATTACK : no swipe, it always hits at this (step 15 : was 1, the user found ATTACK far too strong and fights too short.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>TurnAttackOffBeat</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ATTACK : the OFF-BEAT it adds</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>TurnCutInSpeed</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>CUT IN : an enemy this fast plays in the middle of the bar</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>ONE BAR</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>TurnCutInAfter</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>right after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>TurnPackEarly</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>{ 1, 2, 3 }</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>an ENCOUNTER in the first half of the floor</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>TurnPackLate</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>{ 2, 3, 4 }</t>
         </is>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>in the second half</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>TurnEliteEscort</t>
         </is>
       </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>{ 0, 1, 2 }</t>
         </is>
       </c>
-      <c r="D20" s="32" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ordinary enemies that come with an ELITE</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>TurnBossEscort</t>
         </is>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>{ 0, 1, 2 }</t>
         </is>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>and with the BOSS</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>MaestroTurnDamage</t>
         </is>
       </c>
-      <c r="C22" s="32" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D22" s="32" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>MAESTRO : each of TACET's notes hits this much harder (1 = as NORMAL :</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>PACKS</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>TurnShardsPerEscort</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>shards for each enemy beyond the first</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>TurnFloorLife</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>{ 1.6, 2.1, 2.7 }</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>step 15 : was 1 / 1.3 / 1.6, fights about 1.5 times longer (the user asked for longer fights)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Floor Scale</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>TurnFloorDamage</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>{ 1, 1.2, 1.4 }</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>TurnFillsGapsScale</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D26" s="32" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>DEAD AIR : a missed note</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>TurnLullHeal</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>THE LULL : life back on its humming turn</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>TurnLullEvery</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="32" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>every this many turns</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>TurnFastGap</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>REQUIEM : the gap between notes below half life</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Enemy Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>TurnBargainSteal</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING : breath taken by each attack</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>TurnRoomToneKeep</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>ROOM TONE : the share of the band's damage the OTHER enemies take while it stands</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>TurnFeltHandBreath</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>THE DAMPER (FELT HAND, 29 Oct) : an ATTACK gives this much less BREATH while it stands (until CALL went</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>TurnTwiceFirst</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>STUTTER : cuts in after this many of the band's moves</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>ONE BAR enemies</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>TurnTwiceSecond</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>and again after this many</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>TurnByTouchMost</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="32" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>THE BLIND CANTOR : missed notes that come back in its next attack, at most</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>TurnCourtKeep</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>THE STAFF : the share of the band's damage it takes while another enemy stands</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>TurnStaffEvery</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D37" s="32" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>every this many attacks it strikes the floor (instead of a CADENZA)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>TurnStaffPower</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>that one note hits everyone this much harder</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Bosses of step 14</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>TurnThorns</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D39" s="32" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>THE DEAF CROWN : life lost by a musician who breaks the DECREE (x the floor's note scale)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ENEMY MOVES</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TurnChargePower</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CHARGE : the charged blow is one note this many times as hard as one of its notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ENEMY MOVES</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TurnChargeCounter</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>the COUNTER after parrying it PERFECT hits this much harder (like a CADENZA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>TurnPracticeHp</t>
         </is>
       </c>
-      <c r="C40" s="32" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>x TurnFloorLife on floor 1 (1.6) = 96, step 15 (was 160 with the floor at 1)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>TurnPracticeSpeed</t>
         </is>
       </c>
-      <c r="C41" s="32" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="32" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="B42" s="32" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>TurnPracticePower</t>
         </is>
       </c>
-      <c r="C42" s="32" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>each note hits this x TurnNoteDamage (4 life)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B43" s="32" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>TurnNotesMin</t>
         </is>
       </c>
-      <c r="C43" s="32" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>{ 1, 2, 3 }</t>
         </is>
       </c>
-      <c r="D43" s="32" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>ELITE and BOSS</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B44" s="32" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>TurnNotesMax</t>
         </is>
       </c>
-      <c r="C44" s="32" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>{ 2, 3, 4 }</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B45" s="32" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>TurnSmallNotesMin</t>
         </is>
       </c>
-      <c r="C45" s="32" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>{ 1, 1, 2 }</t>
         </is>
       </c>
-      <c r="D45" s="32" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>ordinary enemies</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>TurnSmallNotesMax</t>
         </is>
       </c>
-      <c r="C46" s="32" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>{ 2, 2, 2 }</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="32" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Enemy Attack</t>
         </is>
       </c>
-      <c r="B47" s="32" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>TurnNoteDamage</t>
         </is>
       </c>
-      <c r="C47" s="32" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>step 12 : was 1.5, the user found NORMAL far too easy (turnsim STRONG 81 -&gt; 57 percent).</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>PARRY</t>
         </is>
       </c>
-      <c r="B48" s="32" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>TurnParryGoodKeep</t>
         </is>
       </c>
-      <c r="C48" s="32" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B49" s="32" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>TurnBreathMax</t>
         </is>
       </c>
-      <c r="C49" s="32" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>TurnBreathStart</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="32" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B51" s="32" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>TurnBreathPerAttack</t>
         </is>
       </c>
-      <c r="C51" s="32" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D51" s="32" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>step 15 : was 1. A weaker ATTACK pays for the skills instead</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>BREATH</t>
         </is>
       </c>
-      <c r="B52" s="32" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>TurnBreathPerParry</t>
         </is>
       </c>
-      <c r="C52" s="32" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D52" s="32" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>for each note parried PERFECT</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="32" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>KNOCKED OUT</t>
         </is>
       </c>
-      <c r="B53" s="32" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>TurnReviveHp</t>
         </is>
       </c>
-      <c r="C53" s="32" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="32" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B54" s="32" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>TurnOffBeatMax</t>
         </is>
       </c>
-      <c r="C54" s="32" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="32" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B55" s="32" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>TurnParryOffBeat</t>
         </is>
       </c>
-      <c r="C55" s="32" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>each note parried PERFECT</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>OFF-BEAT</t>
         </is>
       </c>
-      <c r="B56" s="32" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>TurnOffBeatScale</t>
         </is>
       </c>
-      <c r="C56" s="32" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>damage against an enemy off the beat</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B57" s="32" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>TurnDissonanceMost</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>DISSONANCE stacks no higher</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="32" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B58" s="32" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>TurnCrescendoStep</t>
         </is>
       </c>
-      <c r="C58" s="32" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D58" s="32" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>CRESCENDO : each stack hits this much harder</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="32" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B59" s="32" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>TurnCrescendoMost</t>
         </is>
       </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="32" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B60" s="32" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>TurnMuteTurns</t>
         </is>
       </c>
-      <c r="C60" s="32" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>MUTE : turns without skills</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="32" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Statuses</t>
         </is>
       </c>
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>TurnGuardKeep</t>
         </is>
       </c>
-      <c r="C61" s="32" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D61" s="32" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>GUARD : the share of a hit that gets through</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="32" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B62" s="32" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>TurnCounterScale</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D62" s="32" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>x the target's attack damage</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="32" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B63" s="32" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>TurnCadenzaCounter</t>
         </is>
       </c>
-      <c r="C63" s="32" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="32" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B64" s="32" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>TurnCadenzaEvery</t>
         </is>
       </c>
-      <c r="C64" s="32" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="32" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>COUNTER and CADENZA</t>
         </is>
       </c>
-      <c r="B65" s="32" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>TurnCadenzaPower</t>
         </is>
       </c>
-      <c r="C65" s="32" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="32" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B66" s="32" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>TurnHoldBase</t>
         </is>
       </c>
-      <c r="C66" s="32" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="32" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B67" s="32" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>TurnHoldGain</t>
         </is>
       </c>
-      <c r="C67" s="32" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="32" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B68" s="32" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>TurnRollPerfect</t>
         </is>
       </c>
-      <c r="C68" s="32" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="32" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B69" s="32" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>TurnRollGood</t>
         </is>
       </c>
-      <c r="C69" s="32" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="32" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B70" s="32" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>MaestroTurnRollPerfect</t>
         </is>
       </c>
-      <c r="C70" s="32" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="32" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Skill Notes</t>
         </is>
       </c>
-      <c r="B71" s="32" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>MaestroTurnRollGood</t>
         </is>
       </c>
-      <c r="C71" s="32" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="32" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Conductors</t>
         </is>
       </c>
-      <c r="B72" s="32" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>TurnSignatureNeed</t>
         </is>
       </c>
-      <c r="C72" s="32" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="32" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B73" s="32" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>PlaytestSignatureNeed</t>
         </is>
       </c>
-      <c r="C73" s="32" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="32" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B74" s="32" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>TurnBeethovenMost</t>
         </is>
       </c>
-      <c r="C74" s="32" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D74" s="32" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>THE UNHEARING's PASSIVE : up to this much harder as the band's life runs out</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="32" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B75" s="32" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>TurnBoltDamage</t>
         </is>
       </c>
-      <c r="C75" s="32" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D75" s="32" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>LIGHTNING : damage to every enemy at full strength (x1)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="32" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B76" s="32" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>TurnMozartRun</t>
         </is>
       </c>
-      <c r="C76" s="32" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D76" s="32" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>THE SHADOWLESS's PASSIVE : this many PERFECTs in a row give 1 breath</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="32" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>PLAYTEST</t>
         </is>
       </c>
-      <c r="B77" s="32" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>TurnFeatherPerStroke</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D77" s="32" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>FEATHER : free ATTACKs per stroke that lands (step 12, was 1 extra turn : 25 percent of STRONG runs won)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="32" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>TurnLockedTempoWindow</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>LOCKED TEMPO : seconds added to the PERFECT window of skills and the SIGNATURE, never</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="32" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>TurnFugueScale</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>FUGUE : the echo plays at the SIGNATURE's strength x this (step 13 : was 1, THE METRONOME was the weakest at 44 percent)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="32" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B80" s="32" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>TurnPaganiniLife</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D80" s="32" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>THE HEARTLESS's PASSIVE : life paid for each BREATH a skill is short of (step 15 : was 3, skills carry the fight now).</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="32" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B81" s="32" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>TurnCapricePrice</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D81" s="32" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>CAPRICE : when it ends, every musician pays this share of their life (never below 1, step 13 : was 0.1)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="32" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B82" s="32" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>TurnCapricePerStroke</t>
         </is>
       </c>
-      <c r="C82" s="32" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>CAPRICE : turns per stroke that lands (step 12, a bar has more turns now)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="32" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B83" s="32" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>TurnLullyWindow</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>THE KING'S BATON's PASSIVE : seconds added to both parry windows (0.05 won 99 percent of STRONG runs, the others 83 to 90;</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="32" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B84" s="32" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>TurnSunHeal</t>
         </is>
       </c>
-      <c r="C84" s="32" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>THE SUN : life back for every musician at full strength (step 13 : was 12, THE KING'S BATON was the strongest at 71 percent. Step 15 : 8 -&gt; 6)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="32" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B85" s="32" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>TurnFannyScale</t>
         </is>
       </c>
-      <c r="C85" s="32" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D85" s="32" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>FANNY MENDELSSOHN AND ???'s PASSIVE : FANNY's voice hits this much harder</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="32" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B86" s="32" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>TurnFelixHeal</t>
         </is>
       </c>
-      <c r="C86" s="32" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D86" s="32" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>FELIX's voice heals this much more</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="32" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B87" s="32" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>TurnFelixCrescendo</t>
         </is>
       </c>
-      <c r="C87" s="32" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D87" s="32" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>and gives this much more CRESCENDO</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="32" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B88" s="32" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>TurnDuetDamage</t>
         </is>
       </c>
-      <c r="C88" s="32" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D88" s="32" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>TWO VOICES : damage to every enemy at full strength (step 13 : was 9 and 6, FANNY 46 percent)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="32" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>The other four of the lore</t>
         </is>
       </c>
-      <c r="B89" s="32" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>TurnDuetHeal</t>
         </is>
       </c>
-      <c r="C89" s="32" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D89" s="32" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>and life back for every musician</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="32" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B90" s="32" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>TurnBreathControl</t>
         </is>
       </c>
-      <c r="C90" s="32" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D90" s="32" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="32" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B91" s="32" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>TurnHandCut</t>
         </is>
       </c>
-      <c r="C91" s="32" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D91" s="32" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="32" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B92" s="32" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>TurnHandLeast</t>
         </is>
       </c>
-      <c r="C92" s="32" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D92" s="32" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>never fewer notes left than this (its point is a long phrase,</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="32" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B93" s="32" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>TurnScarCrescendo</t>
         </is>
       </c>
-      <c r="C93" s="32" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D93" s="32" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="32" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B94" s="32" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>TurnHuntingCallScale</t>
         </is>
       </c>
-      <c r="C94" s="32" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D94" s="32" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="32" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B95" s="32" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>TurnLessonWindow</t>
         </is>
       </c>
-      <c r="C95" s="32" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D95" s="32" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="32" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B96" s="32" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>TurnLessonShakes</t>
         </is>
       </c>
-      <c r="C96" s="32" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D96" s="32" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="32" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B97" s="32" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>TurnLessonScale</t>
         </is>
       </c>
-      <c r="C97" s="32" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D97" s="32" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>and the skill plays this much harder</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="32" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B98" s="32" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>TurnShieldKeep</t>
         </is>
       </c>
-      <c r="C98" s="32" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D98" s="32" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="32" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Musician Traits in the turn battle</t>
         </is>
       </c>
-      <c r="B99" s="32" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>TurnChakramRepeat</t>
         </is>
       </c>
-      <c r="C99" s="32" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D99" s="32" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="32" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>The hidden musicians</t>
         </is>
       </c>
-      <c r="B100" s="32" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>TurnByEarScale</t>
         </is>
       </c>
-      <c r="C100" s="32" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D100" s="32" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="32" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>The hidden musicians</t>
         </is>
       </c>
-      <c r="B101" s="32" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>TurnHeldNoteShare</t>
         </is>
       </c>
-      <c r="C101" s="32" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D101" s="32" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="32" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>The hidden musicians</t>
         </is>
       </c>
-      <c r="B102" s="32" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>TurnStepBetterScale</t>
         </is>
       </c>
-      <c r="C102" s="32" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D102" s="32" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="32" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>The hidden musicians</t>
         </is>
       </c>
-      <c r="B103" s="32" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>TurnLongNotes</t>
         </is>
       </c>
-      <c r="C103" s="32" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D103" s="32" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="32" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>The hidden musicians</t>
         </is>
       </c>
-      <c r="B104" s="32" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>TurnThunderSoften</t>
         </is>
       </c>
-      <c r="C104" s="32" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D104" s="32" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="32" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B105" s="32" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>EchoesPerWin</t>
         </is>
       </c>
-      <c r="C105" s="32" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D105" s="32" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>each fight won</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="32" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B106" s="32" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>EchoesPerFloor</t>
         </is>
       </c>
-      <c r="C106" s="32" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D106" s="32" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>each floor cleared</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="32" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B107" s="32" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>EchoesRunWon</t>
         </is>
       </c>
-      <c r="C107" s="32" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D107" s="32" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>the whole run won</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="32" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B108" s="32" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>EchoesMaestro</t>
         </is>
       </c>
-      <c r="C108" s="32" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D108" s="32" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="32" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B109" s="32" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>ArchiveLifePerLevel</t>
         </is>
       </c>
-      <c r="C109" s="32" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D109" s="32" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="32" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B110" s="32" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
-      <c r="C110" s="32" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D110" s="32" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="32" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B111" s="32" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
-      <c r="C111" s="32" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D111" s="32" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>WARM UP</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="32" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B112" s="32" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
-      <c r="C112" s="32" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D112" s="32" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>SAVINGS</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="32" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>ARCHIVE</t>
         </is>
       </c>
-      <c r="B113" s="32" t="inlineStr">
+      <c r="B115" t="inlineStr">
         <is>
           <t>ArchiveFirstChairTier</t>
         </is>
       </c>
-      <c r="C113" s="32" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D113" s="32" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="32" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B114" s="32" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>TurnReedCaseHeal</t>
         </is>
       </c>
-      <c r="C114" s="32" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D114" s="32" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="32" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B115" s="32" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
-      <c r="C115" s="32" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D115" s="32" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="32" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B116" s="32" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>TurnPianissimoBreath</t>
         </is>
       </c>
-      <c r="C116" s="32" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D116" s="32" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="32" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B117" s="32" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>TurnBreathMarkStart</t>
         </is>
       </c>
-      <c r="C117" s="32" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D117" s="32" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="32" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B118" s="32" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>TurnTuttiScale</t>
         </is>
       </c>
-      <c r="C118" s="32" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="D118" s="32" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="32" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B119" s="32" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>TurnRubatoMiss</t>
         </is>
       </c>
-      <c r="C119" s="32" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="D119" s="32" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="32" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B120" s="32" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>TurnCrescendoStart</t>
         </is>
       </c>
-      <c r="C120" s="32" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D120" s="32" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="32" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B121" s="32" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>TurnSforzandoScale</t>
         </is>
       </c>
-      <c r="C121" s="32" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D121" s="32" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="32" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B122" s="32" t="inlineStr">
+      <c r="B124" t="inlineStr">
         <is>
           <t>TurnOvertureScale</t>
         </is>
       </c>
-      <c r="C122" s="32" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D122" s="32" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="32" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B123" s="32" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>TurnCounterpointScale</t>
         </is>
       </c>
-      <c r="C123" s="32" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D123" s="32" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="32" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B124" s="32" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>TurnAccelerandoShakes</t>
         </is>
       </c>
-      <c r="C124" s="32" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D124" s="32" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="32" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B125" s="32" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>TurnGraceTimes</t>
         </is>
       </c>
-      <c r="C125" s="32" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D125" s="32" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="32" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B126" s="32" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
-      <c r="C126" s="32" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D126" s="32" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="32" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B127" s="32" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>TurnConBrioNeed</t>
         </is>
       </c>
-      <c r="C127" s="32" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D127" s="32" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="32" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B128" s="32" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>TurnCodaBelow</t>
         </is>
       </c>
-      <c r="C128" s="32" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D128" s="32" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="32" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>Turn Motifs</t>
         </is>
       </c>
-      <c r="B129" s="32" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>TurnCodaScale</t>
         </is>
       </c>
-      <c r="C129" s="32" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D129" s="32" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>takes this much more</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="32" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>ONE BAR motifs</t>
         </is>
       </c>
-      <c r="B130" s="32" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>TurnDownbeatScale</t>
         </is>
       </c>
-      <c r="C130" s="32" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D130" s="32" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="32" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>ONE BAR motifs</t>
         </is>
       </c>
-      <c r="B131" s="32" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>TurnEntranceScale</t>
         </is>
       </c>
-      <c r="C131" s="32" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D131" s="32" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="32" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>ONE BAR motifs</t>
         </is>
       </c>
-      <c r="B132" s="32" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>TurnGreenRoomHeal</t>
         </is>
       </c>
-      <c r="C132" s="32" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D132" s="32" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="32" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>ONE BAR motifs</t>
         </is>
       </c>
-      <c r="B133" s="32" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>TurnUnisonScale</t>
         </is>
       </c>
-      <c r="C133" s="32" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D133" s="32" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="32" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B134" s="32" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>TurnRingTime</t>
         </is>
       </c>
-      <c r="C134" s="32" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="D134" s="32" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="32" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B135" s="32" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>TurnLateReveal</t>
         </is>
       </c>
-      <c r="C135" s="32" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D135" s="32" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="32" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B136" s="32" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>MaestroTurnRingTime</t>
         </is>
       </c>
-      <c r="C136" s="32" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D136" s="32" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>MAESTRO</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="32" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B137" s="32" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>TurnNoteGap</t>
         </is>
       </c>
-      <c r="C137" s="32" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="D137" s="32" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="32" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B138" s="32" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>TurnPause</t>
         </is>
       </c>
-      <c r="C138" s="32" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D138" s="32" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="32" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B139" s="32" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>TurnHitStop</t>
         </is>
       </c>
-      <c r="C139" s="32" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>0.075</t>
         </is>
       </c>
-      <c r="D139" s="32" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="32" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B140" s="32" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>TurnStrikeTime</t>
         </is>
       </c>
-      <c r="C140" s="32" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="D140" s="32" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="32" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B141" s="32" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>TurnStrikeImpact</t>
         </is>
       </c>
-      <c r="C141" s="32" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>0.24</t>
         </is>
       </c>
-      <c r="D141" s="32" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="32" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B142" s="32" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>TurnStrikeStop</t>
         </is>
       </c>
-      <c r="C142" s="32" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>0.08</t>
         </is>
       </c>
-      <c r="D142" s="32" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="32" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B143" s="32" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>TurnNumberTime</t>
         </is>
       </c>
-      <c r="C143" s="32" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D143" s="32" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="32" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B144" s="32" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>TurnBigHit</t>
         </is>
       </c>
-      <c r="C144" s="32" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D144" s="32" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="32" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B145" s="32" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>TurnNumberCell</t>
         </is>
       </c>
-      <c r="C145" s="32" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="D145" s="32" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="32" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B146" s="32" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>TurnNumberBigCell</t>
         </is>
       </c>
-      <c r="C146" s="32" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D146" s="32" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>the same for a big hit (was 8)</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="32" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B147" s="32" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>TurnDissolveTime</t>
         </is>
       </c>
-      <c r="C147" s="32" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D147" s="32" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="32" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B148" s="32" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>TurnCutInTime</t>
         </is>
       </c>
-      <c r="C148" s="32" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="D148" s="32" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="32" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B149" s="32" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>TurnKillStop</t>
         </is>
       </c>
-      <c r="C149" s="32" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>0.18</t>
         </is>
       </c>
-      <c r="D149" s="32" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>the freeze when an enemy falls silent</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="32" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B150" s="32" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>TurnEndTime</t>
         </is>
       </c>
-      <c r="C150" s="32" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="D150" s="32" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>the win or lose banner stays this long</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="32" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B151" s="32" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>TurnSparkGap</t>
         </is>
       </c>
-      <c r="C151" s="32" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D151" s="32" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>a spark comes this soon after the note before it</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="32" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B152" s="32" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>TurnHoldTime</t>
         </is>
       </c>
-      <c r="C152" s="32" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="D152" s="32" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="32" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>Turn Feel</t>
         </is>
       </c>
-      <c r="B153" s="32" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C153" s="32" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D153" s="32" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>
@@ -12835,7 +12886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="33" min="1" max="1"/>
@@ -12894,731 +12945,821 @@
           <t>CUT IN (speed 5 or more)</t>
         </is>
       </c>
+      <c r="J1" s="67" t="inlineStr">
+        <is>
+          <t>MOVES in turn (GUARD block on floor 1 before x1.6)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>HUSH</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D2" s="32" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E2" s="32" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>D U, L R D</t>
         </is>
       </c>
-      <c r="G2" s="32" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ECHO FADES (2)</t>
         </is>
       </c>
-      <c r="H2" s="32" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Each note that gets through adds 1 DISSONANCE.</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>DEAD AIR</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="32" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>L R, D D U</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>FILLS THE GAPS (2)</t>
         </is>
       </c>
-      <c r="H3" s="32" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>A note you miss hits 50 percent harder.</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ATTACK, CHARGE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>THE LULL</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>D D, U D U</t>
         </is>
       </c>
-      <c r="G4" s="32" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>LULLABY (2)</t>
         </is>
       </c>
-      <c r="H4" s="32" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Every third turn it hums instead of attacking and gets back 12 life.</t>
         </is>
       </c>
-      <c r="I4" s="32" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>L R, U D L</t>
         </is>
       </c>
-      <c r="G5" s="32" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>FALSE NOTES (2)</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>One note of each attack hides its arrow behind a ? until late.</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>THE MUTE CHOIR</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>D D U, L R L R</t>
         </is>
       </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>SILENT MOUTHS (1)</t>
         </is>
       </c>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>A note you miss takes the target's skills away for a turn.</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ATTACK, GUARD, ATTACK (GUARD 22)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>WHITE NOISE</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="32" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>L R L R, U D U D</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>NO REST (1)</t>
         </is>
       </c>
-      <c r="H7" s="32" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>One note more in every attack, and parrying it gives no BREATH.</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>REQUIEM</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>D L R U, L R L R</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>UNFINISHED (1)</t>
         </is>
       </c>
-      <c r="H8" s="32" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Below half life it swaps left and right and plays faster.</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>THE NAMELESS MASTER</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>D U L, R L D U</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>ANSWER BETTER (1)</t>
         </is>
       </c>
-      <c r="H9" s="32" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>It answers with the notes of the last skill your band played.</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>THE DEVIL'S STRING</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>R R L, U D U D</t>
         </is>
       </c>
-      <c r="G10" s="32" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>THE BARGAIN (1)</t>
         </is>
       </c>
-      <c r="H10" s="32" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Each of its attacks steals 1 BREATH.</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>ROOM TONE</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>D, U D</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>HOLDS THE ROOM (2)</t>
         </is>
       </c>
-      <c r="H11" s="32" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>While it stands, the other enemies take 30 percent less.</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>THE CUE</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C12" s="32" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="32" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>R L, U</t>
         </is>
       </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>ON CUE (2)</t>
         </is>
       </c>
-      <c r="H12" s="32" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>It always strikes the musician who played the last skill.</t>
         </is>
       </c>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>THE DAMPER</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>D D, L R</t>
         </is>
       </c>
-      <c r="G13" s="32" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>FELT HAND (2)</t>
         </is>
       </c>
-      <c r="H13" s="32" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>While it stands, an ATTACK gives 1 less BREATH.</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ATTACK, GUARD (GUARD 14)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>STUTTER</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="32" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>L, R, U</t>
         </is>
       </c>
-      <c r="G14" s="32" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>TWICE A BAR (2)</t>
         </is>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>It cuts in twice a bar, after the 1st and the 3rd move, one note each time.</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>THE ROUND</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="32" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>D D D, L R L R</t>
         </is>
       </c>
-      <c r="G15" s="32" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>FIRST IN LINE (1)</t>
         </is>
       </c>
-      <c r="H15" s="32" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>It always strikes the musician who plays first in the bar.</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ATTACK, ATTACK, CHARGE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>THE DEAF CROWN</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>U U U D, L R D</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>DECREE (1)</t>
         </is>
       </c>
-      <c r="H16" s="32" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Each bar it forbids SKILLS or ATTACKS, and breaking it hurts. It never takes a COUNTER.</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>THE STAFF</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="32" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>D D D, D L D R</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>THE COURT (1)</t>
         </is>
       </c>
-      <c r="H17" s="32" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>While its court stands it takes half. Every third attack it strikes the floor and hits everyone.</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>THE BLIND CANTOR</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="C18" s="32" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E18" s="32" t="n">
+      <c r="E18" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>D U D U, L R L R</t>
         </is>
       </c>
-      <c r="G18" s="32" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>BY TOUCH (1)</t>
         </is>
       </c>
-      <c r="H18" s="32" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>It strikes the seats in turn, front to back. A note you miss comes back in its next attack.</t>
         </is>
       </c>
-      <c r="I18" s="32" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ATTACK</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -2335,112 +2335,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.1b   0%   LATE  100%  3.1b   0%   ELITE 100%  3.8b   0%   BOSS  100%  7.3b   0%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  2.2b   6%   ELITE 100%  3.0b   8%   BOSS  100%  5.4b  13%   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.8b   0%   LATE  100%  4.8b   1%   ELITE 100%  6.0b   0%   BOSS  100% 10.5b   1%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.2b   9%   LATE  100%  4.9b  13%   ELITE 100%  5.7b  15%   BOSS  100% 10.6b  17%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  6.3b   3%   LATE  100%  7.4b   2%   ELITE 100%  9.0b   1%   BOSS  100% 14.4b   3%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.9b  13%   LATE  100%  6.1b  16%   ELITE 100%  6.7b  18%   BOSS  100% 12.2b  17%   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.3b   1%   LATE  100%  3.3b   4%   ELITE 100%  4.2b   4%   BOSS  100%  8.0b  12%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  1.1b   3%   LATE  100%  2.0b   7%   ELITE 100%  2.0b   7%   BOSS  100%  3.7b  11%   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  4.4b   7%   LATE  100%  5.6b   9%   ELITE 100%  6.8b  11%   BOSS   99% 11.7b  25%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.3b  12%   LATE  100%  4.4b  17%   ELITE 100%  4.8b  17%   BOSS  100%  8.1b  23%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  7.1b  13%   LATE  100%  8.4b  18%   ELITE 100% 10.1b  20%   BOSS   98% 16.2b  37%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  5.3b  19%   LATE  100%  6.9b  21%   ELITE 100%  7.9b  22%   BOSS   99% 14.5b  25%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.5b   3%   LATE  100%  4.0b  10%   ELITE 100%  4.9b  10%   BOSS  100%  9.5b  28%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   5%   LATE  100%  2.1b  10%   ELITE 100%  2.5b  10%   BOSS  100%  4.2b  16%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  5.1b  14%   LATE  100%  6.7b  23%   ELITE 100%  8.3b  25%   BOSS   82% 13.9b  58%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.7b  18%   LATE  100%  4.8b  22%   ELITE 100%  5.9b  25%   BOSS   95% 10.8b  35%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  8.4b  27%   LATE   99% 10.4b  34%   ELITE  91% 13.3b  49%   BOSS   30% 14.7b  87%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  6.7b  25%   LATE  100%  9.0b  27%   ELITE  93% 11.9b  36%   BOSS   61% 18.4b  66%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  3.3b   9%   LATE  100%  5.5b  23%   ELITE 100%  6.9b  26%   BOSS   63% 12.2b  71%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.7b   9%   LATE  100%  2.9b  19%   ELITE 100%  3.1b  20%   BOSS   99%  5.6b  35%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  7.1b  34%   LATE   83%  9.8b  58%   ELITE  60% 12.4b  74%   BOSS    7% 10.0b  97%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY 100%  5.1b  29%   LATE   96%  8.1b  41%   ELITE  76% 10.6b  59%   BOSS   21% 11.7b  90%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  47% 10.2b  80%   LATE   15%  7.9b  93%   ELITE   1%  8.3b  99%   BOSS    0%  5.8b 100%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  63% 11.3b  65%   LATE   31% 10.9b  84%   ELITE  10% 10.9b  95%   BOSS    0%  7.8b  99%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  4.1b  18%   LATE   99%  7.4b  42%   ELITE  91%  9.7b  51%   BOSS   15% 10.8b  94%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  30%   ELITE 100%  4.1b  29%   BOSS   69%  8.0b  71%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  66%  9.6b  72%   LATE   12%  7.7b  96%   ELITE   2%  8.6b  99%   BOSS    0%  5.8b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  83%  7.9b  59%   LATE   28%  8.7b  89%   ELITE   7%  9.4b  98%   BOSS    0%  6.3b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   0%  5.7b  99%   LATE    0%  3.9b 100%   ELITE   0%  4.5b 100%   BOSS    0%  3.5b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.8b  99%   LATE    0%  4.2b 100%   ELITE   0%  4.2b 100%   BOSS    0%  3.7b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 24%  SKILLS 75%</t>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 13%  SKILLS 86%</t>
         </is>
       </c>
     </row>
@@ -2462,28 +2462,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    41 /  52 /   5 /   0   x1.69</t>
+          <t xml:space="preserve">  EXPERT    31 /  66 /   2 /   0   x1.65</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG     5 /  36 /  50 /   7   x1.37</t>
+          <t xml:space="preserve">  STRONG     3 /  51 /  43 /   2   x1.40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE    0 /   7 /  48 /  43   x1.16</t>
+          <t xml:space="preserve">  AVERAGE    0 /   4 /  64 /  30   x1.19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   2 /  27 /  69   x1.08</t>
+          <t xml:space="preserve">  NEWCOMER   0 /   0 /  35 /  63   x1.09</t>
         </is>
       </c>
     </row>
@@ -2498,119 +2498,119 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   80%  9.5b    100%  6.7b    </t>
+          <t xml:space="preserve">  HUSH                   94%  8.1b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               82%  9.9b    100%  6.7b    </t>
+          <t xml:space="preserve">  DEAD AIR               94%  7.7b    100%  5.1b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               86%  10.4b    100%  7.0b    </t>
+          <t xml:space="preserve">  THE LULL               96%  8.4b    100%  5.1b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 79%  9.4b    100%  6.5b    </t>
+          <t xml:space="preserve">  STATIC                 92%  7.9b    100%  5.1b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         82%  12.9b    100%  8.7b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         89%  11.0b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            28%  9.2b    100%  7.8b    </t>
+          <t xml:space="preserve">  WHITE NOISE            62%  8.8b    100%  5.6b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  5.2b     19%  14.6b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  7.2b     52%  17.7b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     0%  8.2b     80%  17.9b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     2%  11.3b     91%  17.3b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  4.7b      4%  13.1b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  6.4b     35%  16.8b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              89%  9.7b    100%  6.8b    </t>
+          <t xml:space="preserve">  ROOM TONE              94%  7.9b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                87%  10.1b    100%  6.8b    </t>
+          <t xml:space="preserve">  THE CUE                97%  8.2b    100%  5.3b    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             80%  10.1b    100%  6.9b    </t>
+          <t xml:space="preserve">  THE DAMPER             96%  8.1b    100%  5.1b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                91%  9.3b    100%  6.3b    </t>
+          <t xml:space="preserve">  STUTTER                98%  7.4b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              67%  14.9b    100%  8.4b    </t>
+          <t xml:space="preserve">  THE ROUND              82%  12.9b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.3b     12%  14.9b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.7b     48%  21.1b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  5.9b     29%  15.9b    </t>
+          <t xml:space="preserve">  THE STAFF               0%  7.9b     66%  18.7b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.9b     26%  14.1b    </t>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.5b     62%  17.6b    </t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RUNS (3 floors, life carried over, no motifs, Beethoven) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3</t>
+          <t>RUNS (3 floors, life carried over, no motifs, Beethoven) : WIN PERCENT  /  LOST ON FLOOR 1, 2, 3  /  BARS A FIGHT WON ON FLOOR 1, 2, 3</t>
         </is>
       </c>
     </row>
@@ -2632,35 +2632,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.4 / 5.1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%    3.1 / 4.7 / 5.5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    56%    0% / 8% / 34%</t>
+          <t xml:space="preserve">    STRONG    60%    0% / 9% / 31%    3.5 / 5.6 / 6.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    43% / 53% / 3%</t>
+          <t xml:space="preserve">    AVERAGE    0%    10% / 85% / 4%    4.5 / 7.0 / 7.8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    92% / 7% / 0%</t>
+          <t xml:space="preserve">    NEWCOMER   0%    69% / 30% / 0%    5.2 / 8.0 / -</t>
         </is>
       </c>
     </row>
@@ -2674,35 +2674,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.6 / 5.4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    77%    0% / 4% / 18%</t>
+          <t xml:space="preserve">    EXPERT    82%    0% / 3% / 14%    3.2 / 5.0 / 5.9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    12% / 51% / 35%</t>
+          <t xml:space="preserve">    STRONG     0%    1% / 68% / 30%    3.8 / 6.1 / 6.8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    83% / 16% / 0%</t>
+          <t xml:space="preserve">    AVERAGE    0%    58% / 41% / 0%    4.7 / 6.9 / -</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    100% / 0% / 0%</t>
+          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%    5.1 / - / -</t>
         </is>
       </c>
     </row>
@@ -2717,21 +2717,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       55% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       60% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  54% / 0%</t>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  63% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       49% / 0%</t>
+          <t xml:space="preserve">  THE METRONOME       55% / 0%</t>
         </is>
       </c>
     </row>
@@ -2746,35 +2746,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAGANINI    50% / 63%</t>
+          <t xml:space="preserve">  PAGANINI    57% / 64%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUANTZ      55% / 57%</t>
+          <t xml:space="preserve">  QUANTZ      59% / 61%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PFUNDT      56% / 55%</t>
+          <t xml:space="preserve">  PFUNDT      63% / 54%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DUPORT      56% / 54%</t>
+          <t xml:space="preserve">  DUPORT      59% / 60%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PUNTO       60% / 47%</t>
+          <t xml:space="preserve">  PUNTO       60% / 59%</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{ 1.6, 2.1, 2.7 }</t>
+          <t>{ 1.6, 3.6, 5.4 }</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10111,7 +10111,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{ 1, 1.2, 1.4 }</t>
+          <t>{ 1, 1.35, 1.65 }</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PATH (Beta1 30 Oct) : was 1.6 / 2.1 / 2.7 and 1 / 1.2 / 1.4. The band grows a step a</t>
         </is>
       </c>
     </row>
@@ -11690,496 +11695,486 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnBloodScale</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnPactLife</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>and costs this much life (never the last of it)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnLastCutScale</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
+          <t>CAPRICE No. 24 (PAGANINI) : the last cut of CAPRICE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TurnLongNotes</t>
+          <t>TurnLessonStrong</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
+          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnLessonEcho</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnShieldThird</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>TurnCallStrong</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>TurnHandOneLeast</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>TurnHandPaukenCut</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>TurnInspiredNeed</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>STRONGER BAND</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>TurnInspiredBreath</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>DEEP BREATH</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ArchiveFirstChairTier</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>TurnLongNotes</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12189,51 +12184,51 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>ArchiveFirstChairTier</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
@@ -12245,17 +12240,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -12267,17 +12262,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -12289,17 +12284,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
         </is>
       </c>
     </row>
@@ -12311,17 +12306,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -12333,95 +12328,95 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
+          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -12431,249 +12426,249 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnLateReveal</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TurnNumberTime</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TurnBigHit</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>from this much damage it is drawn bigger</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -12685,17 +12680,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TurnNumberCell</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -12707,17 +12702,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TurnNumberBigCell</t>
+          <t>TurnLateReveal</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>the same for a big hit (was 8)</t>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
@@ -12729,17 +12724,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TurnDissolveTime</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -12751,17 +12746,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TurnCutInTime</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -12773,17 +12768,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -12795,17 +12790,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -12817,17 +12812,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -12839,17 +12834,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -12861,15 +12856,257 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>TurnStrikeStop</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>the freeze when it lands</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TurnNumberTime</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>TurnBigHit</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>from this much damage it is drawn bigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>TurnNumberCell</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>TurnNumberBigCell</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>the same for a big hit (was 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>TurnDissolveTime</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>TurnCutInTime</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G2" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : every musician's next move plays twice. Better strokes, louder echo.</t>
+          <t>The 4/4 shape : every musician's next move plays twice. Better strokes, louder echo. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G3" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : strikes every enemy and throws it OFF-BEAT. Better strokes, bigger strike.</t>
+          <t>The 4/4 shape : strikes every enemy and throws it OFF-BEAT. Better strokes, bigger strike. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G7" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : FANNY strikes every enemy while ??? heals every musician.</t>
+          <t>The 4/4 shape : FANNY strikes every enemy while ??? heals every musician. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -2342,14 +2342,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.2b   9%   LATE  100%  4.9b  13%   ELITE 100%  5.7b  15%   BOSS  100% 10.6b  17%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   8%   LATE  100%  4.5b  11%   ELITE 100%  5.5b  15%   BOSS  100%  9.9b  17%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.9b  13%   LATE  100%  6.1b  16%   ELITE 100%  6.7b  18%   BOSS  100% 12.2b  17%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.1b  11%   LATE  100%  5.0b  14%   ELITE 100%  6.0b  16%   BOSS  100% 10.7b  16%   </t>
         </is>
       </c>
     </row>
@@ -2363,77 +2363,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.3b  12%   LATE  100%  4.4b  17%   ELITE 100%  4.8b  17%   BOSS  100%  8.1b  23%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b  12%   LATE  100%  4.1b  16%   ELITE 100%  4.6b  17%   BOSS  100%  8.0b  22%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  5.3b  19%   LATE  100%  6.9b  21%   ELITE 100%  7.9b  22%   BOSS   99% 14.5b  25%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.7b  18%   LATE  100%  5.6b  22%   ELITE 100%  7.0b  23%   BOSS   99% 12.7b  25%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   5%   LATE  100%  2.1b  10%   ELITE 100%  2.5b  10%   BOSS  100%  4.2b  16%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   5%   LATE  100%  2.2b  10%   ELITE 100%  2.4b  11%   BOSS  100%  4.1b  17%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.7b  18%   LATE  100%  4.8b  22%   ELITE 100%  5.9b  25%   BOSS   95% 10.8b  35%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.5b  18%   LATE  100%  4.6b  22%   ELITE  99%  5.7b  23%   BOSS   96% 10.8b  38%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  6.7b  25%   LATE  100%  9.0b  27%   ELITE  93% 11.9b  36%   BOSS   61% 18.4b  66%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  5.9b  26%   LATE  100%  7.4b  27%   ELITE  95% 10.0b  37%   BOSS   73% 15.4b  54%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.7b   9%   LATE  100%  2.9b  19%   ELITE 100%  3.1b  20%   BOSS   99%  5.6b  35%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.8b   9%   LATE  100%  2.9b  18%   ELITE 100%  3.1b  20%   BOSS   98%  5.4b  34%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY 100%  5.1b  29%   LATE   96%  8.1b  41%   ELITE  76% 10.6b  59%   BOSS   21% 11.7b  90%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  5.3b  31%   LATE   96%  7.9b  41%   ELITE  77% 10.6b  58%   BOSS   22% 11.3b  89%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  63% 11.3b  65%   LATE   31% 10.9b  84%   ELITE  10% 10.9b  95%   BOSS    0%  7.8b  99%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  67%  9.5b  64%   LATE   38%  8.6b  84%   ELITE  13%  9.9b  94%   BOSS    0%  6.5b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  30%   ELITE 100%  4.1b  29%   BOSS   69%  8.0b  71%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  29%   ELITE 100%  4.1b  30%   BOSS   65%  8.1b  72%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  83%  7.9b  59%   LATE   28%  8.7b  89%   ELITE   7%  9.4b  98%   BOSS    0%  6.3b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  81%  8.5b  61%   LATE   29%  8.3b  89%   ELITE   5%  9.1b  98%   BOSS    0%  6.3b  99%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.8b  99%   LATE    0%  4.2b 100%   ELITE   0%  4.2b 100%   BOSS    0%  3.7b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.5b  99%   LATE    0%  3.7b 100%   ELITE   0%  4.5b 100%   BOSS    0%  3.4b 100%   </t>
         </is>
       </c>
     </row>
@@ -2462,21 +2462,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    31 /  66 /   2 /   0   x1.65</t>
+          <t xml:space="preserve">  EXPERT    31 /  66 /   1 /   0   x1.65</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG     3 /  51 /  43 /   2   x1.40</t>
+          <t xml:space="preserve">  STRONG     3 /  49 /  44 /   2   x1.39</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE    0 /   4 /  64 /  30   x1.19</t>
+          <t xml:space="preserve">  AVERAGE    0 /   4 /  63 /  31   x1.18</t>
         </is>
       </c>
     </row>
@@ -2498,119 +2498,119 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   94%  8.1b    100%  5.0b    </t>
+          <t xml:space="preserve">  HUSH                   98%  7.1b    100%  4.8b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               94%  7.7b    100%  5.1b    </t>
+          <t xml:space="preserve">  DEAD AIR               96%  7.2b    100%  4.7b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               96%  8.4b    100%  5.1b    </t>
+          <t xml:space="preserve">  THE LULL               97%  7.8b    100%  4.9b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 92%  7.9b    100%  5.1b    </t>
+          <t xml:space="preserve">  STATIC                 92%  7.3b    100%  4.6b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         89%  11.0b    100%  5.9b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         93%  10.1b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            62%  8.8b    100%  5.6b    </t>
+          <t xml:space="preserve">  WHITE NOISE            66%  8.5b    100%  5.4b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  7.2b     52%  17.7b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  7.1b     67%  16.1b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     2%  11.3b     91%  17.3b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     3%  10.6b     94%  14.6b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  6.4b     35%  16.8b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  5.6b     43%  15.2b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              94%  7.9b    100%  5.0b    </t>
+          <t xml:space="preserve">  ROOM TONE              97%  7.5b    100%  4.9b    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                97%  8.2b    100%  5.3b    </t>
+          <t xml:space="preserve">  THE CUE                96%  7.8b    100%  4.9b    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             96%  8.1b    100%  5.1b    </t>
+          <t xml:space="preserve">  THE DAMPER             94%  7.7b    100%  4.8b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                98%  7.4b    100%  5.0b    </t>
+          <t xml:space="preserve">  STUTTER                99%  7.0b    100%  4.4b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              82%  12.9b    100%  5.9b    </t>
+          <t xml:space="preserve">  THE ROUND              76%  12.4b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.7b     48%  21.1b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.8b     61%  19.6b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  7.9b     66%  18.7b    </t>
+          <t xml:space="preserve">  THE STAFF               0%  7.0b     73%  17.3b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.5b     62%  17.6b    </t>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.7b     77%  15.4b    </t>
         </is>
       </c>
     </row>
@@ -2632,35 +2632,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.4 / 5.1</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.2 / 4.8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%    3.1 / 4.7 / 5.5</t>
+          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%    3.0 / 4.5 / 4.9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    60%    0% / 9% / 31%    3.5 / 5.6 / 6.7</t>
+          <t xml:space="preserve">    STRONG    63%    0% / 8% / 28%    3.5 / 5.4 / 6.2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    10% / 85% / 4%    4.5 / 7.0 / 7.8</t>
+          <t xml:space="preserve">    AVERAGE    0%    8% / 89% / 2%    4.4 / 6.8 / 7.1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    69% / 30% / 0%    5.2 / 8.0 / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    70% / 29% / 0%    5.3 / 6.9 / -</t>
         </is>
       </c>
     </row>
@@ -2674,35 +2674,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.6 / 5.4</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.2 / 4.8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    82%    0% / 3% / 14%    3.2 / 5.0 / 5.9</t>
+          <t xml:space="preserve">    EXPERT    84%    0% / 3% / 12%    3.3 / 5.0 / 5.6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    1% / 68% / 30%    3.8 / 6.1 / 6.8</t>
+          <t xml:space="preserve">    STRONG     0%    2% / 65% / 32%    3.7 / 5.8 / 6.7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    58% / 41% / 0%    4.7 / 6.9 / -</t>
+          <t xml:space="preserve">    AVERAGE    0%    53% / 46% / 0%    4.7 / 6.2 / -</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%    5.1 / - / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    98% / 2% / 0%    5.0 / - / -</t>
         </is>
       </c>
     </row>
@@ -2724,14 +2724,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  63% / 0%</t>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  68% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       55% / 0%</t>
+          <t xml:space="preserve">  THE METRONOME       63% / 0%</t>
         </is>
       </c>
     </row>
@@ -2746,35 +2746,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAGANINI    57% / 64%</t>
+          <t xml:space="preserve">  PAGANINI    61% / 65%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUANTZ      59% / 61%</t>
+          <t xml:space="preserve">  QUANTZ      66% / 58%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PFUNDT      63% / 54%</t>
+          <t xml:space="preserve">  PFUNDT      66% / 58%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DUPORT      59% / 60%</t>
+          <t xml:space="preserve">  DUPORT      59% / 70%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PUNTO       60% / 59%</t>
+          <t xml:space="preserve">  PUNTO       62% / 64%</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{ 1.6, 3.6, 5.4 }</t>
+          <t>{ 1.6, 3.8, 5.9 }</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{ 1, 1.35, 1.65 }</t>
+          <t>{ 1, 1.38, 1.7 }</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PATH (Beta1 30 Oct) : was 1.6 / 2.1 / 2.7 and 1 / 1.2 / 1.4. The band grows a step a</t>
+          <t>PATH and SIGNATURE GROWS (Beta1 30 Oct) : was 1.6 / 2.1 / 2.7 and 1 / 1.2 / 1.4. The band</t>
         </is>
       </c>
     </row>
@@ -11475,44 +11475,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>SIGNATURE GROWS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TurnBreathControl</t>
+          <t>TurnJahrCrescendo</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>SIGNATURE GROWS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TurnHandCut</t>
+          <t>TurnJahrScale</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
@@ -11524,17 +11514,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TurnHandLeast</t>
+          <t>TurnBreathControl</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>never fewer notes left than this (its point is a long phrase,</t>
+          <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11536,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TurnScarCrescendo</t>
+          <t>TurnHandCut</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11556,7 +11546,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
+          <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
         </is>
       </c>
     </row>
@@ -11568,17 +11558,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TurnHuntingCallScale</t>
+          <t>TurnHandLeast</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
+          <t>never fewer notes left than this (its point is a long phrase,</t>
         </is>
       </c>
     </row>
@@ -11590,17 +11580,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TurnLessonWindow</t>
+          <t>TurnScarCrescendo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
+          <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
         </is>
       </c>
     </row>
@@ -11612,17 +11602,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TurnLessonShakes</t>
+          <t>TurnHuntingCallScale</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
+          <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
         </is>
       </c>
     </row>
@@ -11634,17 +11624,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TurnLessonScale</t>
+          <t>TurnLessonWindow</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>and the skill plays this much harder</t>
+          <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
         </is>
       </c>
     </row>
@@ -11656,17 +11646,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TurnShieldKeep</t>
+          <t>TurnLessonShakes</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
+          <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
         </is>
       </c>
     </row>
@@ -11678,61 +11668,61 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TurnChakramRepeat</t>
+          <t>TurnLessonScale</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
+          <t>and the skill plays this much harder</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TurnBloodScale</t>
+          <t>TurnShieldKeep</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
+          <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TurnPactLife</t>
+          <t>TurnChakramRepeat</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>and costs this much life (never the last of it)</t>
+          <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
         </is>
       </c>
     </row>
@@ -11744,17 +11734,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TurnLastCutScale</t>
+          <t>TurnBloodScale</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CAPRICE No. 24 (PAGANINI) : the last cut of CAPRICE</t>
+          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
         </is>
       </c>
     </row>
@@ -11766,17 +11756,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TurnLessonStrong</t>
+          <t>TurnPactLife</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
+          <t>and costs this much life (never the last of it)</t>
         </is>
       </c>
     </row>
@@ -11788,17 +11778,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TurnLessonEcho</t>
+          <t>TurnLastCutScale</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
+          <t>CAPRICE No. 24 (PAGANINI) : the last cut of CAPRICE</t>
         </is>
       </c>
     </row>
@@ -11810,17 +11800,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TurnShieldThird</t>
+          <t>TurnLessonStrong</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
+          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
         </is>
       </c>
     </row>
@@ -11832,17 +11822,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TurnCallStrong</t>
+          <t>TurnLessonEcho</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
+          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
         </is>
       </c>
     </row>
@@ -11854,17 +11844,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TurnHandOneLeast</t>
+          <t>TurnShieldThird</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
+          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
         </is>
       </c>
     </row>
@@ -11876,95 +11866,95 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TurnHandPaukenCut</t>
+          <t>TurnCallStrong</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
+          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TurnInspiredNeed</t>
+          <t>TurnHandOneLeast</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnInspiredBreath</t>
+          <t>TurnHandPaukenCut</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnInspiredNeed</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnInspiredBreath</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11976,17 +11966,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -11998,17 +11988,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnLongNotes</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
@@ -12020,29 +12010,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnLongNotes</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12052,29 +12042,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
@@ -12086,17 +12076,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
@@ -12108,17 +12098,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
@@ -12130,17 +12120,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -12152,17 +12142,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
@@ -12174,7 +12164,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -12184,7 +12174,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
@@ -12196,17 +12186,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
@@ -12218,61 +12208,61 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ArchiveFirstChairTier</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>ArchiveFirstChairTier</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
@@ -12284,17 +12274,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -12306,17 +12296,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -12328,17 +12318,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
         </is>
       </c>
     </row>
@@ -12350,17 +12340,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -12372,17 +12362,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -12394,17 +12384,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -12416,17 +12406,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -12438,17 +12428,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12450,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -12470,7 +12460,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12472,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -12492,7 +12482,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12494,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12514,7 +12504,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
@@ -12526,17 +12516,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
@@ -12548,17 +12538,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
@@ -12570,61 +12560,61 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
@@ -12636,17 +12626,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12648,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -12668,51 +12658,51 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TurnLateReveal</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12714,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12736,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnLateReveal</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12758,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12778,7 +12768,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -12790,17 +12780,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -12812,17 +12802,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -12834,17 +12824,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -12856,17 +12846,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -12878,17 +12868,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TurnNumberTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -12900,17 +12890,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TurnBigHit</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>from this much damage it is drawn bigger</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -12922,17 +12912,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TurnNumberCell</t>
+          <t>TurnNumberTime</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12934,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TurnNumberBigCell</t>
+          <t>TurnBigHit</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>the same for a big hit (was 8)</t>
+          <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
@@ -12966,17 +12956,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TurnDissolveTime</t>
+          <t>TurnNumberCell</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
@@ -12988,17 +12978,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TurnCutInTime</t>
+          <t>TurnNumberBigCell</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+          <t>the same for a big hit (was 8)</t>
         </is>
       </c>
     </row>
@@ -13010,17 +13000,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnDissolveTime</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
         </is>
       </c>
     </row>
@@ -13032,17 +13022,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnCutInTime</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
         </is>
       </c>
     </row>
@@ -13054,17 +13044,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnKillStop</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>the freeze when an enemy falls silent</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13066,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnEndTime</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+          <t>the win or lose banner stays this long</t>
         </is>
       </c>
     </row>
@@ -13098,15 +13088,59 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -2335,112 +2335,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  2.2b   6%   ELITE 100%  3.0b   8%   BOSS  100%  5.4b  13%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  2.2b   6%   ELITE 100%  3.0b   8%   BOSS  100%  5.3b  13%   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   8%   LATE  100%  4.5b  11%   ELITE 100%  5.5b  15%   BOSS  100%  9.9b  17%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   8%   LATE  100%  4.7b  11%   ELITE 100%  5.4b  15%   BOSS  100%  9.7b  16%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.1b  11%   LATE  100%  5.0b  14%   ELITE 100%  6.0b  16%   BOSS  100% 10.7b  16%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.2b  11%   LATE  100%  5.0b  14%   ELITE 100%  6.0b  16%   BOSS  100% 10.5b  16%   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  1.1b   3%   LATE  100%  2.0b   7%   ELITE 100%  2.0b   7%   BOSS  100%  3.7b  11%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  1.1b   3%   LATE  100%  2.0b   7%   ELITE 100%  2.0b   7%   BOSS  100%  3.7b  10%   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.2b  12%   LATE  100%  4.1b  16%   ELITE 100%  4.6b  17%   BOSS  100%  8.0b  22%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.1b  12%   LATE  100%  4.1b  16%   ELITE 100%  4.6b  16%   BOSS  100%  7.7b  23%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.7b  18%   LATE  100%  5.6b  22%   ELITE 100%  7.0b  23%   BOSS   99% 12.7b  25%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.7b  18%   LATE  100%  5.8b  21%   ELITE 100%  7.0b  22%   BOSS  100% 12.4b  24%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   5%   LATE  100%  2.2b  10%   ELITE 100%  2.4b  11%   BOSS  100%  4.1b  17%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   4%   LATE  100%  2.2b  10%   ELITE 100%  2.4b  11%   BOSS  100%  4.0b  17%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.5b  18%   LATE  100%  4.6b  22%   ELITE  99%  5.7b  23%   BOSS   96% 10.8b  38%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.6b  18%   LATE  100%  4.8b  23%   ELITE 100%  5.8b  24%   BOSS   96%  9.9b  34%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  5.9b  26%   LATE  100%  7.4b  27%   ELITE  95% 10.0b  37%   BOSS   73% 15.4b  54%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  5.9b  26%   LATE  100%  7.4b  26%   ELITE  97% 10.0b  33%   BOSS   70% 16.0b  57%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.8b   9%   LATE  100%  2.9b  18%   ELITE 100%  3.1b  20%   BOSS   98%  5.4b  34%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.7b   9%   LATE  100%  2.9b  18%   ELITE 100%  3.2b  20%   BOSS   99%  5.3b  32%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  99%  5.3b  31%   LATE   96%  7.9b  41%   ELITE  77% 10.6b  58%   BOSS   22% 11.3b  89%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY 100%  5.3b  32%   LATE   95%  7.5b  43%   ELITE  77% 10.2b  57%   BOSS   24% 11.4b  90%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  67%  9.5b  64%   LATE   38%  8.6b  84%   ELITE  13%  9.9b  94%   BOSS    0%  6.5b 100%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  62%  9.7b  69%   LATE   36%  9.4b  84%   ELITE  13% 10.0b  95%   BOSS    0%  6.9b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  29%   ELITE 100%  4.1b  30%   BOSS   65%  8.1b  72%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  30%   ELITE 100%  4.2b  31%   BOSS   77%  7.7b  68%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  81%  8.5b  61%   LATE   29%  8.3b  89%   ELITE   5%  9.1b  98%   BOSS    0%  6.3b  99%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  84%  8.4b  59%   LATE   33%  8.6b  88%   ELITE  10%  9.7b  96%   BOSS    0%  6.5b  99%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   1%  5.5b  99%   LATE    0%  3.7b 100%   ELITE   0%  4.5b 100%   BOSS    0%  3.4b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   3%  5.6b  99%   LATE    0%  4.0b 100%   ELITE   0%  4.6b 100%   BOSS    0%  3.5b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 13%  SKILLS 86%</t>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 12%  SKILLS 87%</t>
         </is>
       </c>
     </row>
@@ -2462,28 +2462,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    31 /  66 /   1 /   0   x1.65</t>
+          <t xml:space="preserve">  EXPERT    33 /  64 /   1 /   0   x1.66</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG     3 /  49 /  44 /   2   x1.39</t>
+          <t xml:space="preserve">  STRONG     3 /  49 /  44 /   2   x1.40</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE    0 /   4 /  63 /  31   x1.18</t>
+          <t xml:space="preserve">  AVERAGE    0 /   5 /  62 /  32   x1.18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   0 /  35 /  63   x1.09</t>
+          <t xml:space="preserve">  NEWCOMER   0 /   0 /  34 /  64   x1.09</t>
         </is>
       </c>
     </row>
@@ -2498,119 +2498,119 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   98%  7.1b    100%  4.8b    </t>
+          <t xml:space="preserve">  HUSH                   94%  7.7b    100%  4.8b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               96%  7.2b    100%  4.7b    </t>
+          <t xml:space="preserve">  DEAD AIR               92%  7.6b    100%  4.8b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               97%  7.8b    100%  4.9b    </t>
+          <t xml:space="preserve">  THE LULL               97%  7.8b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 92%  7.3b    100%  4.6b    </t>
+          <t xml:space="preserve">  STATIC                 94%  7.5b    100%  4.7b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         93%  10.1b    100%  5.9b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         92%  10.6b    100%  6.0b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            66%  8.5b    100%  5.4b    </t>
+          <t xml:space="preserve">  WHITE NOISE            64%  9.0b     99%  5.5b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  7.1b     67%  16.1b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  6.3b     63%  15.9b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     3%  10.6b     94%  14.6b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     5%  11.0b     94%  14.8b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  5.6b     43%  15.2b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  5.6b     57%  13.5b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              97%  7.5b    100%  4.9b    </t>
+          <t xml:space="preserve">  ROOM TONE              95%  7.2b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                96%  7.8b    100%  4.9b    </t>
+          <t xml:space="preserve">  THE CUE                95%  8.1b    100%  5.0b    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             94%  7.7b    100%  4.8b    </t>
+          <t xml:space="preserve">  THE DAMPER             93%  7.8b    100%  4.8b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                99%  7.0b    100%  4.4b    </t>
+          <t xml:space="preserve">  STUTTER                98%  6.9b    100%  4.5b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              76%  12.4b    100%  6.0b    </t>
+          <t xml:space="preserve">  THE ROUND              80%  12.1b    100%  5.9b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.8b     61%  19.6b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  5.8b     46%  18.6b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  7.0b     73%  17.3b    </t>
+          <t xml:space="preserve">  THE STAFF               0%  7.0b     63%  16.9b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.7b     77%  15.4b    </t>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.2b     61%  15.7b    </t>
         </is>
       </c>
     </row>
@@ -2632,35 +2632,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.2 / 4.8</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.1 / 4.7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    99%    0% / 0% / 0%    3.0 / 4.5 / 4.9</t>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%    3.0 / 4.5 / 5.0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    63%    0% / 8% / 28%    3.5 / 5.4 / 6.2</t>
+          <t xml:space="preserve">    STRONG    66%    0% / 7% / 26%    3.3 / 5.3 / 6.1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    8% / 89% / 2%    4.4 / 6.8 / 7.1</t>
+          <t xml:space="preserve">    AVERAGE    0%    8% / 88% / 3%    4.3 / 6.7 / 7.3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    70% / 29% / 0%    5.3 / 6.9 / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    69% / 30% / 0%    5.1 / 7.1 / -</t>
         </is>
       </c>
     </row>
@@ -2674,35 +2674,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.2 / 4.8</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.3 / 4.8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    84%    0% / 3% / 12%    3.3 / 5.0 / 5.6</t>
+          <t xml:space="preserve">    EXPERT    79%    0% / 4% / 16%    3.1 / 4.9 / 5.5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    2% / 65% / 32%    3.7 / 5.8 / 6.7</t>
+          <t xml:space="preserve">    STRONG     0%    0% / 65% / 34%    3.6 / 5.8 / 6.4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    53% / 46% / 0%    4.7 / 6.2 / -</t>
+          <t xml:space="preserve">    AVERAGE    0%    58% / 41% / 0%    4.5 / 6.3 / -</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    98% / 2% / 0%    5.0 / - / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%    4.9 / - / -</t>
         </is>
       </c>
     </row>
@@ -2717,21 +2717,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       60% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       67% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  68% / 0%</t>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  64% / 0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE METRONOME       63% / 0%</t>
+          <t xml:space="preserve">  THE METRONOME       59% / 0%</t>
         </is>
       </c>
     </row>
@@ -2746,35 +2746,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAGANINI    61% / 65%</t>
+          <t xml:space="preserve">  PAGANINI    65% / 67%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUANTZ      66% / 58%</t>
+          <t xml:space="preserve">  QUANTZ      68% / 63%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PFUNDT      66% / 58%</t>
+          <t xml:space="preserve">  PFUNDT      64% / 68%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DUPORT      59% / 70%</t>
+          <t xml:space="preserve">  DUPORT      65% / 68%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PUNTO       62% / 64%</t>
+          <t xml:space="preserve">  PUNTO       67% / 64%</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -10089,7 +10089,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{ 1.6, 3.8, 5.9 }</t>
+          <t>{ 1.6, 3.85, 6 }</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{ 1, 1.38, 1.7 }</t>
+          <t>{ 1, 1.39, 1.72 }</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PATH and SIGNATURE GROWS (Beta1 30 Oct) : was 1.6 / 2.1 / 2.7 and 1 / 1.2 / 1.4. The band</t>
+          <t>PATH, SIGNATURE GROWS and BONDS (Beta1 30 Oct) : was 1.6 / 2.1 / 2.7 and 1 / 1.2 / 1.4. The</t>
         </is>
       </c>
     </row>
@@ -11509,44 +11509,39 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>BONDS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TurnBreathControl</t>
+          <t>TurnBondScale</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Musician Traits in the turn battle</t>
+          <t>BONDS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TurnHandCut</t>
+          <t>TurnBondLineTime</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
+          <t>seconds a tied legend's line shows as the fight starts</t>
         </is>
       </c>
     </row>
@@ -11558,17 +11553,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TurnHandLeast</t>
+          <t>TurnBreathControl</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>never fewer notes left than this (its point is a long phrase,</t>
+          <t>BREATH CONTROL (QUANTZ) : more BREATH from their ATTACK</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11575,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TurnScarCrescendo</t>
+          <t>TurnHandCut</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11590,7 +11585,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
+          <t>TURN OF THE HAND (PFUNDT) : notes taken off the next attack of an enemy their skill hits</t>
         </is>
       </c>
     </row>
@@ -11602,17 +11597,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TurnHuntingCallScale</t>
+          <t>TurnHandLeast</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
+          <t>never fewer notes left than this (its point is a long phrase,</t>
         </is>
       </c>
     </row>
@@ -11624,17 +11619,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TurnLessonWindow</t>
+          <t>TurnScarCrescendo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
+          <t>THE SCAR (DUPORT) : CRESCENDO after each enemy attack that hurt them</t>
         </is>
       </c>
     </row>
@@ -11646,17 +11641,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TurnLessonShakes</t>
+          <t>TurnHuntingCallScale</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
+          <t>THE HUNTING CALL (PUNTO) : the musician who plays right after PUNTO in the bar</t>
         </is>
       </c>
     </row>
@@ -11668,17 +11663,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TurnLessonScale</t>
+          <t>TurnLessonWindow</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>and the skill plays this much harder</t>
+          <t>THE LESSON (QUANTZ's skill) : seconds added to the PERFECT window of the friend's next skill, never past GOOD</t>
         </is>
       </c>
     </row>
@@ -11690,17 +11685,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TurnShieldKeep</t>
+          <t>TurnLessonShakes</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
+          <t>a ROLL in it needs this many shakes fewer for PERFECT</t>
         </is>
       </c>
     </row>
@@ -11712,61 +11707,61 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TurnChakramRepeat</t>
+          <t>TurnLessonScale</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
+          <t>and the skill plays this much harder</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TurnBloodScale</t>
+          <t>TurnShieldKeep</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
+          <t>SHIELD (DUPORT's skill) : the share of a hit on the friend that DUPORT takes instead</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>Musician Traits in the turn battle</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TurnPactLife</t>
+          <t>TurnChakramRepeat</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>and costs this much life (never the last of it)</t>
+          <t>CHAKRAM (PUNTO's skill) : an enemy the same throw already hit takes this share</t>
         </is>
       </c>
     </row>
@@ -11778,17 +11773,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TurnLastCutScale</t>
+          <t>TurnBloodScale</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CAPRICE No. 24 (PAGANINI) : the last cut of CAPRICE</t>
+          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
         </is>
       </c>
     </row>
@@ -11800,17 +11795,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TurnLessonStrong</t>
+          <t>TurnPactLife</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
+          <t>and costs this much life (never the last of it)</t>
         </is>
       </c>
     </row>
@@ -11822,17 +11817,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TurnLessonEcho</t>
+          <t>TurnLastCutScale</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
+          <t>CAPRICE No. 24 (PAGANINI) : the last cut of CAPRICE</t>
         </is>
       </c>
     </row>
@@ -11844,17 +11839,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TurnShieldThird</t>
+          <t>TurnLessonStrong</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
+          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
         </is>
       </c>
     </row>
@@ -11866,17 +11861,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TurnCallStrong</t>
+          <t>TurnLessonEcho</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
+          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
         </is>
       </c>
     </row>
@@ -11888,17 +11883,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TurnHandOneLeast</t>
+          <t>TurnShieldThird</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
+          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
         </is>
       </c>
     </row>
@@ -11910,95 +11905,95 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TurnHandPaukenCut</t>
+          <t>TurnCallStrong</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
+          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TurnInspiredNeed</t>
+          <t>TurnHandOneLeast</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TurnInspiredBreath</t>
+          <t>TurnHandPaukenCut</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnByEarScale</t>
+          <t>TurnInspiredNeed</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>The hidden musicians</t>
+          <t>INSPIRED</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnHeldNoteShare</t>
+          <t>TurnInspiredBreath</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -12010,17 +12005,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TurnStepBetterScale</t>
+          <t>TurnByEarScale</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
+          <t>BY EAR (MALI) : against an enemy that is OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -12032,17 +12027,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TurnLongNotes</t>
+          <t>TurnHeldNoteShare</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
+          <t>HELD NOTE (CHAI) : his ATTACK hits again for this share</t>
         </is>
       </c>
     </row>
@@ -12054,29 +12049,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TurnThunderSoften</t>
+          <t>TurnStepBetterScale</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
+          <t>ONE STEP BETTER (NUAN) : against an enemy whose next attack is long</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EchoesPerWin</t>
+          <t>TurnLongNotes</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -12086,29 +12081,29 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>each fight won</t>
+          <t>long = this many notes or more (Beta1 29 Oct : was an f note)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ARCHIVE</t>
+          <t>The hidden musicians</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EchoesPerFloor</t>
+          <t>TurnThunderSoften</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>each floor cleared</t>
+          <t>THE WHOLE FLOOR (BORIS) : taken off each note of the enemy's next attack</t>
         </is>
       </c>
     </row>
@@ -12120,17 +12115,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EchoesRunWon</t>
+          <t>EchoesPerWin</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>the whole run won</t>
+          <t>each fight won</t>
         </is>
       </c>
     </row>
@@ -12142,17 +12137,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EchoesMaestro</t>
+          <t>EchoesPerFloor</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MAESTRO pays more</t>
+          <t>each floor cleared</t>
         </is>
       </c>
     </row>
@@ -12164,17 +12159,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ArchiveLifePerLevel</t>
+          <t>EchoesRunWon</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>STRONGER BAND</t>
+          <t>the whole run won</t>
         </is>
       </c>
     </row>
@@ -12186,17 +12181,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ArchiveBreathPerLevel</t>
+          <t>EchoesMaestro</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DEEP BREATH</t>
+          <t>MAESTRO pays more</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12203,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ArchiveSignaturePerLevel</t>
+          <t>ArchiveLifePerLevel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -12218,7 +12213,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>WARM UP</t>
+          <t>STRONGER BAND</t>
         </is>
       </c>
     </row>
@@ -12230,17 +12225,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ArchiveShardsPerLevel</t>
+          <t>ArchiveBreathPerLevel</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SAVINGS</t>
+          <t>DEEP BREATH</t>
         </is>
       </c>
     </row>
@@ -12252,61 +12247,61 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ArchiveFirstChairTier</t>
+          <t>ArchiveSignaturePerLevel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
+          <t>WARM UP</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TurnReedCaseHeal</t>
+          <t>ArchiveShardsPerLevel</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>REED CASE : wind players' healing</t>
+          <t>SAVINGS</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Turn Motifs</t>
+          <t>ARCHIVE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TurnSpareSticksOffBeat</t>
+          <t>ArchiveFirstChairTier</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
+          <t>FIRST CHAIR (29 Oct, was FULL STAGE) : the first musician picked starts with their weapon this many tiers up</t>
         </is>
       </c>
     </row>
@@ -12318,17 +12313,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TurnPianissimoBreath</t>
+          <t>TurnReedCaseHeal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
+          <t>REED CASE : wind players' healing</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12335,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TurnBreathMarkStart</t>
+          <t>TurnSpareSticksOffBeat</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>BREATH MARK : more breath at the start of a fight</t>
+          <t>SPARE STICKS : percussion skills' OFF-BEAT</t>
         </is>
       </c>
     </row>
@@ -12362,17 +12357,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TurnTuttiScale</t>
+          <t>TurnPianissimoBreath</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TUTTI : skills that reach everyone</t>
+          <t>PIANISSIMO : more breath for the first note of an attack parried PERFECT (was a p note)</t>
         </is>
       </c>
     </row>
@@ -12384,17 +12379,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TurnRubatoMiss</t>
+          <t>TurnBreathMarkStart</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
+          <t>BREATH MARK : more breath at the start of a fight</t>
         </is>
       </c>
     </row>
@@ -12406,17 +12401,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TurnCrescendoStart</t>
+          <t>TurnTuttiScale</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>CRESCENDO : stacks on every musician at the start</t>
+          <t>TUTTI : skills that reach everyone</t>
         </is>
       </c>
     </row>
@@ -12428,17 +12423,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TurnSforzandoScale</t>
+          <t>TurnRubatoMiss</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
+          <t>RUBATO : a skill note you MISS still plays at this (step 12)</t>
         </is>
       </c>
     </row>
@@ -12450,17 +12445,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TurnOvertureScale</t>
+          <t>TurnCrescendoStart</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>OVERTURE : the band's first hit of a fight</t>
+          <t>CRESCENDO : stacks on every musician at the start</t>
         </is>
       </c>
     </row>
@@ -12472,17 +12467,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TurnCounterpointScale</t>
+          <t>TurnSforzandoScale</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>COUNTERPOINT : the COUNTER</t>
+          <t>SFORZANDO : the PERFECT last note of a skill (was an f note)</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12489,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TurnAccelerandoShakes</t>
+          <t>TurnOvertureScale</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12504,7 +12499,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ACCELERANDO : each shake of a roll counts this many</t>
+          <t>OVERTURE : the band's first hit of a fight</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12511,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TurnGraceTimes</t>
+          <t>TurnCounterpointScale</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -12526,7 +12521,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
+          <t>COUNTERPOINT : the COUNTER</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12533,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TurnMarcatoOffBeat</t>
+          <t>TurnAccelerandoShakes</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12548,7 +12543,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
+          <t>ACCELERANDO : each shake of a roll counts this many</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12555,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TurnConBrioNeed</t>
+          <t>TurnGraceTimes</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
+          <t>GRACE NOTE : a spark that lands does its skill this many times</t>
         </is>
       </c>
     </row>
@@ -12582,17 +12577,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TurnCodaBelow</t>
+          <t>TurnMarcatoOffBeat</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CODA : an enemy under this share of its life</t>
+          <t>MARCATO : a PERFECT attack's OFF-BEAT, times this</t>
         </is>
       </c>
     </row>
@@ -12604,61 +12599,61 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TurnCodaScale</t>
+          <t>TurnConBrioNeed</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>takes this much more</t>
+          <t>CON BRIO : PERFECTs the SIGNATURE needs instead</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TurnDownbeatScale</t>
+          <t>TurnCodaBelow</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DOWNBEAT : the first move of a bar</t>
+          <t>CODA : an enemy under this share of its life</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ONE BAR motifs</t>
+          <t>Turn Motifs</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TurnEntranceScale</t>
+          <t>TurnCodaScale</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
+          <t>takes this much more</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12665,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TurnGreenRoomHeal</t>
+          <t>TurnDownbeatScale</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
+          <t>DOWNBEAT : the first move of a bar</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12687,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TurnUnisonScale</t>
+          <t>TurnEntranceScale</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -12702,51 +12697,51 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
+          <t>ENTRANCE (29 Oct, CALL is gone) : each musician's first move of a fight. Was : a called musician's first bar</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnGreenRoomHeal</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>GREEN ROOM (29 Oct, the BENCH is gone) : life back for the most hurt musician standing at the end of a</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>ONE BAR motifs</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TurnLateReveal</t>
+          <t>TurnUnisonScale</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
+          <t>UNISON : the last ATTACK of a bar that all goes at one enemy</t>
         </is>
       </c>
     </row>
@@ -12758,17 +12753,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -12780,17 +12775,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnLateReveal</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12797,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12812,7 +12807,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -12824,17 +12819,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -12846,17 +12841,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -12868,17 +12863,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -12890,17 +12885,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12907,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TurnNumberTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -12934,17 +12929,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TurnBigHit</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>from this much damage it is drawn bigger</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -12956,17 +12951,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TurnNumberCell</t>
+          <t>TurnNumberTime</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
@@ -12978,17 +12973,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TurnNumberBigCell</t>
+          <t>TurnBigHit</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>the same for a big hit (was 8)</t>
+          <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
@@ -13000,17 +12995,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TurnDissolveTime</t>
+          <t>TurnNumberCell</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
@@ -13022,17 +13017,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TurnCutInTime</t>
+          <t>TurnNumberBigCell</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+          <t>the same for a big hit (was 8)</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13039,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnDissolveTime</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
         </is>
       </c>
     </row>
@@ -13066,17 +13061,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnCutInTime</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
         </is>
       </c>
     </row>
@@ -13088,17 +13083,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnKillStop</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>the freeze when an enemy falls silent</t>
         </is>
       </c>
     </row>
@@ -13110,17 +13105,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnEndTime</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+          <t>the win or lose banner stays this long</t>
         </is>
       </c>
     </row>
@@ -13132,15 +13127,59 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -2335,112 +2335,112 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  2.2b   6%   ELITE 100%  3.0b   8%   BOSS  100%  5.3b  13%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 1  EARLY 100%  2.0b   0%   LATE  100%  3.1b   0%   ELITE 100%  3.3b   0%   BOSS  100%  6.3b   0%   </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  3.0b   8%   LATE  100%  4.7b  11%   ELITE 100%  5.4b  15%   BOSS  100%  9.7b  16%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 2  EARLY 100%  5.5b   0%   LATE  100%  6.6b   2%   ELITE 100%  8.5b   0%   BOSS  100% 14.7b   2%   </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  4.2b  11%   LATE  100%  5.0b  14%   ELITE 100%  6.0b  16%   BOSS  100% 10.5b  16%   </t>
+          <t xml:space="preserve">  FLAWLESS  FLOOR 3  EARLY 100%  8.3b   3%   LATE  100%  9.5b   2%   ELITE 100% 12.9b   2%   BOSS  100% 21.1b   3%   </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  1.1b   3%   LATE  100%  2.0b   7%   ELITE 100%  2.0b   7%   BOSS  100%  3.7b  10%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 1  EARLY 100%  2.1b   1%   LATE  100%  3.3b   4%   ELITE 100%  3.8b   4%   BOSS  100%  7.1b  10%   </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  3.1b  12%   LATE  100%  4.1b  16%   ELITE 100%  4.6b  16%   BOSS  100%  7.7b  23%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 2  EARLY 100%  6.1b   9%   LATE  100%  7.6b  14%   ELITE 100%  9.6b  16%   BOSS   99% 16.3b  32%   </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  4.7b  18%   LATE  100%  5.8b  21%   ELITE 100%  7.0b  22%   BOSS  100% 12.4b  24%   </t>
+          <t xml:space="preserve">  EXPERT    FLOOR 3  EARLY 100%  9.4b  19%   LATE  100% 10.2b  23%   ELITE 100% 14.4b  27%   BOSS   82% 22.4b  53%   </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  1.3b   4%   LATE  100%  2.2b  10%   ELITE 100%  2.4b  11%   BOSS  100%  4.0b  17%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 1  EARLY 100%  2.3b   3%   LATE  100%  3.8b   9%   ELITE 100%  4.4b   9%   BOSS  100%  8.2b  24%   </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  3.6b  18%   LATE  100%  4.8b  23%   ELITE 100%  5.8b  24%   BOSS   96%  9.9b  34%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 2  EARLY 100%  7.1b  21%   LATE  100%  9.3b  28%   ELITE  97% 12.5b  36%   BOSS   47% 17.1b  79%   </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY 100%  5.9b  26%   LATE  100%  7.4b  26%   ELITE  97% 10.0b  33%   BOSS   70% 16.0b  57%   </t>
+          <t xml:space="preserve">  STRONG    FLOOR 3  EARLY  97% 11.7b  38%   LATE   89% 13.0b  51%   ELITE  52% 16.6b  76%   BOSS    5% 12.2b  97%   </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  1.7b   9%   LATE  100%  2.9b  18%   ELITE 100%  3.2b  20%   BOSS   99%  5.3b  32%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 1  EARLY 100%  2.9b   8%   LATE  100%  5.1b  22%   ELITE 100%  6.2b  23%   BOSS   77% 11.4b  63%   </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY 100%  5.3b  32%   LATE   95%  7.5b  43%   ELITE  77% 10.2b  57%   BOSS   24% 11.4b  90%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 2  EARLY  89% 10.9b  53%   LATE   43% 11.3b  82%   ELITE  13% 13.4b  95%   BOSS    0%  8.4b  99%   </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY  62%  9.7b  69%   LATE   36%  9.4b  84%   ELITE  13% 10.0b  95%   BOSS    0%  6.9b 100%   </t>
+          <t xml:space="preserve">  AVERAGE   FLOOR 3  EARLY   5%  7.7b  98%   LATE    0%  5.2b  99%   ELITE   0%  5.7b 100%   BOSS    0%  4.7b 100%   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  2.1b  14%   LATE  100%  3.8b  30%   ELITE 100%  4.2b  31%   BOSS   77%  7.7b  68%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 1  EARLY 100%  3.6b  14%   LATE   98%  6.8b  41%   ELITE  90%  9.2b  49%   BOSS   16% 10.5b  94%   </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  84%  8.4b  59%   LATE   33%  8.6b  88%   ELITE  10%  9.7b  96%   BOSS    0%  6.5b  99%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 2  EARLY  21%  9.7b  93%   LATE    1%  5.8b  99%   ELITE   0%  6.5b 100%   BOSS    0%  4.7b 100%   </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   3%  5.6b  99%   LATE    0%  4.0b 100%   ELITE   0%  4.6b 100%   BOSS    0%  3.5b 100%   </t>
+          <t xml:space="preserve">  NEWCOMER  FLOOR 3  EARLY   0%  4.3b 100%   LATE    0%  3.4b 100%   ELITE   0%  3.5b 100%   BOSS    0%  3.0b 100%   </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 12%  SKILLS 87%</t>
+          <t xml:space="preserve">  DAMAGE SHARE in all of the fights above : ATTACK 20%  SKILLS 79%</t>
         </is>
       </c>
     </row>
@@ -2462,28 +2462,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EXPERT    33 /  64 /   1 /   0   x1.66</t>
+          <t xml:space="preserve">  EXPERT    35 /  55 /   8 /   0   x1.65</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG     3 /  49 /  44 /   2   x1.40</t>
+          <t xml:space="preserve">  STRONG     6 /  35 /  47 /  10   x1.36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AVERAGE    0 /   5 /  62 /  32   x1.18</t>
+          <t xml:space="preserve">  AVERAGE    1 /  11 /  48 /  39   x1.19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NEWCOMER   0 /   0 /  34 /  64   x1.09</t>
+          <t xml:space="preserve">  NEWCOMER   0 /   4 /  30 /  64   x1.10</t>
         </is>
       </c>
     </row>
@@ -2498,119 +2498,119 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  HUSH                   94%  7.7b    100%  4.8b    </t>
+          <t xml:space="preserve">  HUSH                   39%  10.6b    100%  9.0b    </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DEAD AIR               92%  7.6b    100%  4.8b    </t>
+          <t xml:space="preserve">  DEAD AIR               54%  11.2b    100%  9.2b    </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE LULL               97%  7.8b    100%  5.0b    </t>
+          <t xml:space="preserve">  THE LULL               48%  12.3b    100%  9.8b    </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STATIC                 94%  7.5b    100%  4.7b    </t>
+          <t xml:space="preserve">  STATIC                 40%  10.8b    100%  9.1b    </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE MUTE CHOIR         92%  10.6b    100%  6.0b    </t>
+          <t xml:space="preserve">  THE MUTE CHOIR         24%  15.4b    100%  13.0b    </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  WHITE NOISE            64%  9.0b     99%  5.5b    </t>
+          <t xml:space="preserve">  WHITE NOISE             3%  8.1b     95%  11.0b    </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REQUIEM                 0%  6.3b     63%  15.9b    </t>
+          <t xml:space="preserve">  REQUIEM                 0%  4.2b      0%  11.6b    </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE NAMELESS MASTER     5%  11.0b     94%  14.8b    </t>
+          <t xml:space="preserve">  THE NAMELESS MASTER     0%  5.6b     28%  20.9b    </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEVIL'S STRING      0%  5.6b     57%  13.5b    </t>
+          <t xml:space="preserve">  THE DEVIL'S STRING      0%  3.9b      0%  9.9b    </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ROOM TONE              95%  7.2b    100%  5.0b    </t>
+          <t xml:space="preserve">  ROOM TONE              47%  11.1b    100%  9.5b    </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE CUE                95%  8.1b    100%  5.0b    </t>
+          <t xml:space="preserve">  THE CUE                56%  11.9b    100%  9.3b    </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DAMPER             93%  7.8b    100%  4.8b    </t>
+          <t xml:space="preserve">  THE DAMPER             42%  11.3b    100%  9.5b    </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STUTTER                98%  6.9b    100%  4.5b    </t>
+          <t xml:space="preserve">  STUTTER                55%  11.2b    100%  8.6b    </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE ROUND              80%  12.1b    100%  5.9b    </t>
+          <t xml:space="preserve">  THE ROUND              17%  15.7b     99%  12.7b    </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE DEAF CROWN          0%  5.8b     46%  18.6b    </t>
+          <t xml:space="preserve">  THE DEAF CROWN          0%  4.1b      0%  11.2b    </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE STAFF               0%  7.0b     63%  16.9b    </t>
+          <t xml:space="preserve">  THE STAFF               0%  4.5b      2%  12.8b    </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE BLIND CANTOR        0%  6.2b     61%  15.7b    </t>
+          <t xml:space="preserve">  THE BLIND CANTOR        0%  4.2b      1%  11.7b    </t>
         </is>
       </c>
     </row>
@@ -2632,35 +2632,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.1 / 4.7</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.2 / 5.2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%    3.0 / 4.5 / 5.0</t>
+          <t xml:space="preserve">    EXPERT   100%    0% / 0% / 0%    3.0 / 4.7 / 5.6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG    66%    0% / 7% / 26%    3.3 / 5.3 / 6.1</t>
+          <t xml:space="preserve">    STRONG    60%    0% / 4% / 36%    3.3 / 5.4 / 6.5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    8% / 88% / 3%    4.3 / 6.7 / 7.3</t>
+          <t xml:space="preserve">    AVERAGE    0%    9% / 85% / 5%    4.3 / 6.5 / 9.3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    69% / 30% / 0%    5.1 / 7.1 / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    63% / 36% / 0%    5.0 / 6.4 / -</t>
         </is>
       </c>
     </row>
@@ -2674,35 +2674,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.7 / 4.3 / 4.8</t>
+          <t xml:space="preserve">    FLAWLESS 100%    0% / 0% / 0%    2.8 / 4.2 / 5.1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    EXPERT    79%    0% / 4% / 16%    3.1 / 4.9 / 5.5</t>
+          <t xml:space="preserve">    EXPERT    81%    0% / 3% / 15%    3.2 / 5.1 / 5.9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    STRONG     0%    0% / 65% / 34%    3.6 / 5.8 / 6.4</t>
+          <t xml:space="preserve">    STRONG     1%    3% / 61% / 34%    3.7 / 5.8 / 6.9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    AVERAGE    0%    58% / 41% / 0%    4.5 / 6.3 / -</t>
+          <t xml:space="preserve">    AVERAGE    0%    51% / 49% / 0%    4.4 / 5.9 / -</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NEWCOMER   0%    98% / 1% / 0%    4.9 / - / -</t>
+          <t xml:space="preserve">    NEWCOMER   0%    96% / 3% / 0%    4.8 / 7.0 / -</t>
         </is>
       </c>
     </row>
@@ -2717,14 +2717,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">  THE UNHEARING       67% / 0%</t>
+          <t xml:space="preserve">  THE UNHEARING       61% / 0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  64% / 0%</t>
+          <t xml:space="preserve">  FANNY MENDELSSOHN AND ???  62% / 0%</t>
         </is>
       </c>
     </row>
@@ -2746,35 +2746,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PAGANINI    65% / 67%</t>
+          <t xml:space="preserve">  PAGANINI    56% / 65%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">  QUANTZ      68% / 63%</t>
+          <t xml:space="preserve">  QUANTZ      64% / 53%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PFUNDT      64% / 68%</t>
+          <t xml:space="preserve">  PFUNDT      62% / 56%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DUPORT      65% / 68%</t>
+          <t xml:space="preserve">  DUPORT      63% / 54%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PUNTO       67% / 64%</t>
+          <t xml:space="preserve">  PUNTO       53% / 70%</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11768,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11783,14 +11783,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>THE PACT (PAGANINI) : every skill of theirs plays this much harder</t>
+          <t>THE PACT (PAGANINI, no star gives it now) : every skill of theirs plays this much harder</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11849,14 +11849,14 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>THE METHOD (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
+          <t>THE LESSON's first star (QUANTZ) : a LESSON plays this much harder (TurnLessonScale without it)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11871,14 +11871,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EVERY EVENING (QUANTZ) : a friend taught plays their next move again at this</t>
+          <t>KING'S LESSON (QUANTZ) : a friend taught plays their next move again at this</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11893,14 +11893,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>STRADIVARIUS (DUPORT) : the share of a blow DUPORT takes for a friend (TurnShieldKeep without it)</t>
+          <t>SHIELD's and THUNDER CALL's second stars : the share of a blow DUPORT takes for a friend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11915,14 +11915,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>TALLY-HO (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
+          <t>FANFARE's second star (PUNTO) : THE HUNTING CALL (TurnHuntingCallScale without it)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11937,14 +11937,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ONE TURN (PFUNDT) : TURN OF THE HAND leaves this many notes at least (TurnHandLeast without it)</t>
+          <t>ONE TURN (PFUNDT, no star gives it now) : TURN OF THE HAND leaves this many notes at least</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11959,41 +11959,51 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DIE PAUKEN (PFUNDT) : TURN OF THE HAND takes this many notes (TurnHandCut without it)</t>
+          <t>DIE PAUKEN (PFUNDT) : THUNDER CALL takes this many notes off every enemy (TurnHandCut without it)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TurnInspiredNeed</t>
+          <t>TurnAttackDissonance</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DIABOLUS IN MUSICA (PAGANINI's ATTACK, third star) : DISSONANCE their ATTACK adds</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INSPIRED</t>
+          <t>REHEARSAL</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TurnInspiredBreath</t>
+          <t>TurnAttackHeal</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EVENING CONCERT (QUANTZ's ATTACK, third star) : life back for the band's most hurt musician</t>
         </is>
       </c>
     </row>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -9601,7 +9601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="33" min="1" max="1"/>
@@ -12758,154 +12758,154 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TurnRingTime</t>
+          <t>TurnCampanellaAdd</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>from a note showing to the moment to swipe</t>
+          <t>LA CAMPANELLA : DISSONANCE a hit adds to an enemy that has some</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TurnLateReveal</t>
+          <t>TurnSnapDamage</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
+          <t>SNAPPED STRINGS : the crack at TurnDissonanceMost DISSONANCE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MaestroTurnRingTime</t>
+          <t>TurnThunderSheetShare</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MAESTRO</t>
+          <t>THUNDER SHEET : the share of its life an enemy thrown OFF-BEAT loses</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TurnNoteGap</t>
+          <t>TurnHardCase</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>between the notes of one enemy attack</t>
+          <t>HARD CASE : less from every enemy note on DUPORT (1 at least)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TurnPause</t>
+          <t>TurnSilverHornMost</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>after a turn, before the next one starts</t>
+          <t>THE SILVER HORN : CRESCENDO stacks this high (TurnCrescendoMost without it)</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TurnHitStop</t>
+          <t>TurnHallaliScale</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>the band and TACET freeze for a moment on a PERFECT</t>
+          <t>HALLALI : the hit at full CRESCENDO</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Turn Feel</t>
+          <t>GIFTS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>TurnStrikeTime</t>
+          <t>TurnLuckyBowScale</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
+          <t>LUCKY BOW : the first note of every skill</t>
         </is>
       </c>
     </row>
@@ -12917,17 +12917,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TurnStrikeImpact</t>
+          <t>TurnRingTime</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>when in it the hit lands</t>
+          <t>from a note showing to the moment to swipe</t>
         </is>
       </c>
     </row>
@@ -12939,17 +12939,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>TurnStrikeStop</t>
+          <t>TurnLateReveal</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>the freeze when it lands</t>
+          <t>FALSE NOTES (STATIC) : its hidden note shows its arrow once the ring is this far closed</t>
         </is>
       </c>
     </row>
@@ -12961,17 +12961,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TurnNumberTime</t>
+          <t>MaestroTurnRingTime</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
+          <t>MAESTRO</t>
         </is>
       </c>
     </row>
@@ -12983,17 +12983,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TurnBigHit</t>
+          <t>TurnNoteGap</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>from this much damage it is drawn bigger</t>
+          <t>between the notes of one enemy attack</t>
         </is>
       </c>
     </row>
@@ -13005,17 +13005,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TurnNumberCell</t>
+          <t>TurnPause</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
+          <t>after a turn, before the next one starts</t>
         </is>
       </c>
     </row>
@@ -13027,17 +13027,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TurnNumberBigCell</t>
+          <t>TurnHitStop</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>the same for a big hit (was 8)</t>
+          <t>the band and TACET freeze for a moment on a PERFECT</t>
         </is>
       </c>
     </row>
@@ -13049,17 +13049,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TurnDissolveTime</t>
+          <t>TurnStrikeTime</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+          <t>ONE BAR : how long an ATTACK's lunge takes, there and back (Beta1 : slower, smoother)</t>
         </is>
       </c>
     </row>
@@ -13071,17 +13071,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TurnCutInTime</t>
+          <t>TurnStrikeImpact</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+          <t>when in it the hit lands</t>
         </is>
       </c>
     </row>
@@ -13093,17 +13093,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>TurnKillStop</t>
+          <t>TurnStrikeStop</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>the freeze when an enemy falls silent</t>
+          <t>the freeze when it lands</t>
         </is>
       </c>
     </row>
@@ -13115,17 +13115,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TurnEndTime</t>
+          <t>TurnNumberTime</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>the win or lose banner stays this long</t>
+          <t>a damage number stays this long (Beta1 round 4, pixel numbers)</t>
         </is>
       </c>
     </row>
@@ -13137,17 +13137,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TurnSparkGap</t>
+          <t>TurnBigHit</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>a spark comes this soon after the note before it</t>
+          <t>from this much damage it is drawn bigger</t>
         </is>
       </c>
     </row>
@@ -13159,17 +13159,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TurnHoldTime</t>
+          <t>TurnNumberCell</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+          <t>one cell of a digit (5 x 7 cells) in pixels (round 4 : 25% smaller, was 6)</t>
         </is>
       </c>
     </row>
@@ -13181,15 +13181,169 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>TurnNumberBigCell</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>the same for a big hit (was 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>TurnDissolveTime</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>an enemy SILENCED dissolves into TACET's hole in this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>TurnCutInTime</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>the SIGNATURE's CUT-IN, before its strokes (Beta1 round 4, the old duel's picture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TurnKillStop</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>the freeze when an enemy falls silent</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>TurnEndTime</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>the win or lose banner stays this long</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>TurnSparkGap</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>a spark comes this soon after the note before it</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>TurnHoldTime</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>how long a HOLD note wants holding (the button kept down, the baton may move : Beta1 29 Oct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Turn Feel</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
           <t>TurnRollTime</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>how long a ROLL note lasts</t>
         </is>

--- a/docs/TACET_Balance.xlsx
+++ b/docs/TACET_Balance.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4 quick cuts. Each adds 1 DISSONANCE.</t>
+          <t>4 quick cuts. Each adds 1 BURN.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>One big held shot. Hold it = harder. Goes through GUARD.</t>
+          <t>One big held shot. Hold it = harder. Goes through ARMOR.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>A friend's next skill : wider PERFECT, harder hits.</t>
+          <t>A friend gets FOCUS for their next skill.</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Shake fast. Big OFF-BEAT. Breaks a CHARGE.</t>
+          <t>Shake fast. Big STUN. Breaks a CHARGE.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Enemies aim at PFUNDT, who takes half damage.</t>
+          <t>Every enemy aims at PFUNDT, who gets GUARD.</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Guard a friend : their hits land on DUPORT, halved.</t>
+          <t>Protect a friend : their hits land on DUPORT, halved.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>THE SCAR : Every attack that hurts them gives 1 CRESCENDO.</t>
+          <t>THE SCAR : Every attack that hurts them gives 1 VOLUME.</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>The band hits harder : 1 CRESCENDO per note.</t>
+          <t>Every musician gets 1 VOLUME per note.</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>THE HUNTING CALL : The musician who plays right after them in the bar hits harder.</t>
+          <t>THE HUNTING CALL : The musician who plays right after them in the turn hits harder.</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>A hit and a spark. Each adds 1 DISSONANCE.</t>
+          <t>A hit and a spark. Each adds 1 BURN.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>BY EAR : Hits 50 percent harder against an enemy that is OFF-BEAT.</t>
+          <t>BY EAR : Hits 50 percent harder against an enemy that is STUNNED.</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4 notes up and down. Each adds 1 DISSONANCE.</t>
+          <t>4 notes up and down. Each adds 1 BURN.</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3 big hits. OFF-BEAT each.</t>
+          <t>3 big hits. Each adds STUN.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>A big hit and a spark. OFF-BEAT each.</t>
+          <t>A big hit and a spark. Each adds STUN.</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2 big hits and a roll. Big OFF-BEAT.</t>
+          <t>2 big hits and a roll. Big STUN.</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G2" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : every musician's next move plays twice. Better strokes, louder echo. Grows at each boss.</t>
+          <t>4 swipes : every musician gets ECHO, their next move plays again. Better swipes, stronger ECHO. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="G3" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : strikes every enemy and throws it OFF-BEAT. Better strokes, bigger strike. Grows at each boss.</t>
+          <t>4 swipes : strikes every enemy and fills its STUN bar. Better swipes, bigger strike. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="G4" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : two free ATTACKs at the end of the bar per stroke that lands.</t>
+          <t>4 swipes : two free ATTACKs at the end of the turn per swipe that lands.</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G5" s="68" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 4/4 shape : for two turns per stroke that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays </t>
+          <t xml:space="preserve">4 swipes : for two turns per swipe that lands, a MISS is GOOD and a GOOD is PERFECT. Then every musician pays </t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G6" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : life back for every musician, and DISSONANCE and MUTE are gone. Better strokes, more life.</t>
+          <t>4 swipes : life back for every musician, and BURN and MUTED are gone. Better swipes, more life.</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G7" s="68" t="inlineStr">
         <is>
-          <t>The 4/4 shape : FANNY strikes every enemy while ??? heals every musician. Grows at each boss.</t>
+          <t>4 swipes : FANNY strikes every enemy while ??? heals every musician. Grows at each boss.</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Each note that gets through adds 1 DISSONANCE.</t>
+          <t>Each note that gets through adds 1 BURN.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A note you miss takes the target's skills away for a turn.</t>
+          <t>A note you miss leaves the target MUTED for a turn.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -14028,12 +14028,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TWICE A BAR (2)</t>
+          <t>TWICE A TURN (2)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It cuts in twice a bar, after the 1st and the 3rd move, one note each time.</t>
+          <t>It cuts in twice a turn, after the 1st and the 3rd move, one note each time.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>It always strikes the musician who plays first in the bar.</t>
+          <t>It always strikes the musician who plays first in the turn.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Each bar it forbids SKILLS or ATTACKS, and breaking it hurts. It never takes a COUNTER.</t>
+          <t>Each turn it bans SKILLS or ATTACKS, and breaking the ban hurts. It never takes a COUNTER.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
